--- a/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
@@ -4794,7 +4794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M43"/>
+  <dimension ref="B2:M45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -4857,6 +4857,20 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>S&amp;M AI thesis: SG&amp;A margin compressed ~500bps of revenue by Y3 in forecast (see ZI_* tabs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Assumptions list (all tabs): LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.md|.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14082,7 @@
     <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Discounted Cash Flow Model for BMC</t>
+          <t>Discounted Cash Flow Model for ZoomInfo (GTM) — LBOMODEL1</t>
         </is>
       </c>
       <c r="C2" s="305" t="n"/>
@@ -14105,7 +14119,7 @@
         </is>
       </c>
       <c r="C6" s="511" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="7">
@@ -14115,7 +14129,7 @@
         </is>
       </c>
       <c r="C7" s="84" t="n">
-        <v>41400</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="8">
@@ -14125,7 +14139,7 @@
         </is>
       </c>
       <c r="C8" s="512" t="n">
-        <v>143.973</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="9">
@@ -14135,7 +14149,7 @@
         </is>
       </c>
       <c r="C9" s="513" t="n">
-        <v>0.06990222994664612</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="244" thickBot="1">
@@ -14160,28 +14174,28 @@
         </is>
       </c>
       <c r="C12" s="270" t="n">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="270" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="E12" s="270" t="n">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="F12" s="157" t="n">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="G12" s="157" t="n">
-        <v>2015</v>
+        <v>2027</v>
       </c>
       <c r="H12" s="157" t="n">
-        <v>2016</v>
+        <v>2028</v>
       </c>
       <c r="I12" s="157" t="n">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="J12" s="157" t="n">
-        <v>2018</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="13">
@@ -14191,28 +14205,28 @@
         </is>
       </c>
       <c r="C13" s="39" t="n">
-        <v>40633</v>
+        <v>45291</v>
       </c>
       <c r="D13" s="39" t="n">
-        <v>40999</v>
+        <v>45657</v>
       </c>
       <c r="E13" s="39" t="n">
-        <v>41364</v>
+        <v>46022</v>
       </c>
       <c r="F13" s="39" t="n">
-        <v>41729</v>
+        <v>46387</v>
       </c>
       <c r="G13" s="39" t="n">
-        <v>42094</v>
+        <v>46752</v>
       </c>
       <c r="H13" s="39" t="n">
-        <v>42460</v>
+        <v>47118</v>
       </c>
       <c r="I13" s="39" t="n">
-        <v>42825</v>
+        <v>47483</v>
       </c>
       <c r="J13" s="39" t="n">
-        <v>43190</v>
+        <v>47848</v>
       </c>
     </row>
     <row r="14">
@@ -14230,28 +14244,28 @@
         </is>
       </c>
       <c r="C15" s="162" t="n">
-        <v>843.6000000000003</v>
+        <v>340.1</v>
       </c>
       <c r="D15" s="162" t="n">
-        <v>906.4999999999999</v>
+        <v>183.1</v>
       </c>
       <c r="E15" s="162" t="n">
-        <v>882.7000000000003</v>
+        <v>314.5</v>
       </c>
       <c r="F15" s="162" t="n">
-        <v>947.6792413199889</v>
+        <v>359.6</v>
       </c>
       <c r="G15" s="162" t="n">
-        <v>1000.484484594448</v>
+        <v>398</v>
       </c>
       <c r="H15" s="162" t="n">
-        <v>1078.88768747765</v>
+        <v>439.4</v>
       </c>
       <c r="I15" s="162" t="n">
-        <v>1150.07160606407</v>
+        <v>464.4</v>
       </c>
       <c r="J15" s="162" t="n">
-        <v>1226.874119002437</v>
+        <v>478.4</v>
       </c>
     </row>
     <row r="16">
@@ -14261,28 +14275,28 @@
         </is>
       </c>
       <c r="C16" s="162" t="n">
-        <v>532.8000000000003</v>
+        <v>259.5</v>
       </c>
       <c r="D16" s="162" t="n">
-        <v>543.8999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="E16" s="162" t="n">
-        <v>465.4000000000003</v>
+        <v>225.7</v>
       </c>
       <c r="F16" s="162" t="n">
-        <v>493.6803141804108</v>
+        <v>267.2</v>
       </c>
       <c r="G16" s="162" t="n">
-        <v>559.8040395999167</v>
+        <v>301</v>
       </c>
       <c r="H16" s="162" t="n">
-        <v>634.7919640514119</v>
+        <v>337.6</v>
       </c>
       <c r="I16" s="162" t="n">
-        <v>709.3122632461741</v>
+        <v>358.5</v>
       </c>
       <c r="J16" s="162" t="n">
-        <v>787.9602383046408</v>
+        <v>369.3</v>
       </c>
     </row>
     <row r="17">
@@ -14292,28 +14306,28 @@
         </is>
       </c>
       <c r="C17" s="514" t="n">
-        <v>0.1413514022209673</v>
+        <v>0.21</v>
       </c>
       <c r="D17" s="514" t="n">
-        <v>0.2433962264150944</v>
+        <v>0.21</v>
       </c>
       <c r="E17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="F17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="G17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="H17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="I17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="J17" s="514" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="18">
@@ -14323,28 +14337,28 @@
         </is>
       </c>
       <c r="C18" s="71" t="n">
-        <v>457.4879728966689</v>
+        <v>205</v>
       </c>
       <c r="D18" s="71" t="n">
-        <v>411.51679245283</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E18" s="71" t="n">
-        <v>360.007945781725</v>
+        <v>178.3</v>
       </c>
       <c r="F18" s="71" t="n">
-        <v>381.8840476600047</v>
+        <v>211.1</v>
       </c>
       <c r="G18" s="71" t="n">
-        <v>433.0337394427961</v>
+        <v>237.8</v>
       </c>
       <c r="H18" s="71" t="n">
-        <v>491.0402900234106</v>
+        <v>266.7</v>
       </c>
       <c r="I18" s="71" t="n">
-        <v>548.6851113215323</v>
+        <v>283.2</v>
       </c>
       <c r="J18" s="71" t="n">
-        <v>609.522876557224</v>
+        <v>291.7</v>
       </c>
     </row>
     <row r="19">
@@ -14659,7 +14673,7 @@
         </is>
       </c>
       <c r="J36" s="140" t="n">
-        <v>1226.874119002437</v>
+        <v>478.4</v>
       </c>
     </row>
     <row r="37">
@@ -14677,7 +14691,7 @@
         </is>
       </c>
       <c r="J37" s="412" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="K37" s="411" t="n"/>
     </row>
@@ -14804,7 +14818,7 @@
         </is>
       </c>
       <c r="C45" s="162" t="n">
-        <v>179.9999999999991</v>
+        <v>75</v>
       </c>
       <c r="H45" s="400" t="inlineStr">
         <is>
@@ -14829,7 +14843,7 @@
         </is>
       </c>
       <c r="C46" s="162" t="n">
-        <v>5190.276000000002</v>
+        <v>1572.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -14851,7 +14865,7 @@
         </is>
       </c>
       <c r="C47" s="71" t="n">
-        <v>5010.276000000003</v>
+        <v>1497.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -14875,7 +14889,7 @@
       <c r="F48" s="383" t="n"/>
       <c r="G48" s="383" t="n"/>
       <c r="H48" s="399" t="n">
-        <v>6741.92625</v>
+        <v>1574.8</v>
       </c>
       <c r="I48" s="57" t="n">
         <v>7372.933086845563</v>
@@ -14897,13 +14911,13 @@
         </is>
       </c>
       <c r="H49" s="512" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="I49" s="517" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
       <c r="J49" s="517" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="50">
@@ -14913,7 +14927,7 @@
         </is>
       </c>
       <c r="C50" s="518" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E50" s="383" t="inlineStr">
         <is>
@@ -14921,7 +14935,7 @@
         </is>
       </c>
       <c r="H50" s="519" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
       <c r="I50" s="519" t="n">
         <v>50.57874302119625</v>
@@ -14937,7 +14951,7 @@
         </is>
       </c>
       <c r="C51" s="418" t="n">
-        <v>0.2264547791540078</v>
+        <v>0.21</v>
       </c>
       <c r="E51" s="100" t="inlineStr">
         <is>
@@ -14963,7 +14977,7 @@
         </is>
       </c>
       <c r="C52" s="140" t="n">
-        <v>5010.276000000003</v>
+        <v>1497.5</v>
       </c>
     </row>
     <row r="53">
@@ -14973,7 +14987,7 @@
         </is>
       </c>
       <c r="C53" s="521" t="n">
-        <v>0.7748616857223557</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="55">
@@ -14983,7 +14997,7 @@
         </is>
       </c>
       <c r="C55" s="414" t="n">
-        <v>0.025</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="56">
@@ -14993,7 +15007,7 @@
         </is>
       </c>
       <c r="C56" s="135" t="n">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="57">
@@ -15013,7 +15027,7 @@
         </is>
       </c>
       <c r="C58" s="418" t="n">
-        <v>0.2251383142776443</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="59">
@@ -15023,7 +15037,7 @@
         </is>
       </c>
       <c r="C59" s="418" t="n">
-        <v>0.06990222994664612</v>
+        <v>0.0815</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="244" thickBot="1">
@@ -15691,7 +15705,7 @@
     <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Diluted shares for BMC</t>
+          <t>Diluted shares for ZoomInfo (GTM) — LBOMODEL1</t>
         </is>
       </c>
       <c r="C2" s="305" t="n"/>
@@ -15715,7 +15729,7 @@
         </is>
       </c>
       <c r="E5" s="496" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="6">
@@ -15725,7 +15739,7 @@
         </is>
       </c>
       <c r="E6" s="537" t="n">
-        <v>46.25</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="7">
@@ -15735,7 +15749,7 @@
         </is>
       </c>
       <c r="E7" s="505" t="n">
-        <v>143.973</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="8">
@@ -15745,7 +15759,7 @@
         </is>
       </c>
       <c r="E8" s="504" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15755,7 +15769,7 @@
         </is>
       </c>
       <c r="E9" s="444" t="n">
-        <v>411.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15765,7 +15779,7 @@
         </is>
       </c>
       <c r="E10" s="444" t="n">
-        <v>8.901621621621622</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15775,7 +15789,7 @@
         </is>
       </c>
       <c r="E11" s="444" t="n">
-        <v>1.798378378378377</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15800,7 +15814,7 @@
       </c>
       <c r="D14" s="417" t="n"/>
       <c r="E14" s="444" t="n">
-        <v>145.7713783783784</v>
+        <v>292.312</v>
       </c>
     </row>
     <row r="15">
@@ -15840,13 +15854,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="298" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="298" t="n">
         <v>15</v>
       </c>
       <c r="E18" s="299" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15854,13 +15868,13 @@
         <v>2</v>
       </c>
       <c r="C19" s="298" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="D19" s="298" t="n">
         <v>18</v>
       </c>
       <c r="E19" s="299" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15868,13 +15882,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="298" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="298" t="n">
         <v>22</v>
       </c>
       <c r="E20" s="299" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -15882,13 +15896,13 @@
         <v>4</v>
       </c>
       <c r="C21" s="298" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D21" s="298" t="n">
         <v>28</v>
       </c>
       <c r="E21" s="299" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -15896,13 +15910,13 @@
         <v>5</v>
       </c>
       <c r="C22" s="298" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="298" t="n">
         <v>32</v>
       </c>
       <c r="E22" s="299" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -15910,13 +15924,13 @@
         <v>6</v>
       </c>
       <c r="C23" s="298" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D23" s="298" t="n">
         <v>36</v>
       </c>
       <c r="E23" s="299" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -15924,13 +15938,13 @@
         <v>7</v>
       </c>
       <c r="C24" s="298" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="D24" s="298" t="n">
         <v>39</v>
       </c>
       <c r="E24" s="299" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -15938,20 +15952,22 @@
         <v>8</v>
       </c>
       <c r="C25" s="298" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="D25" s="298" t="n">
         <v>42</v>
       </c>
       <c r="E25" s="299" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="538" t="n">
         <v>9</v>
       </c>
-      <c r="C26" s="298" t="n"/>
+      <c r="C26" s="298" t="n">
+        <v>0</v>
+      </c>
       <c r="D26" s="298" t="n"/>
       <c r="E26" s="299" t="n">
         <v>0</v>
@@ -15961,7 +15977,9 @@
       <c r="B27" s="538" t="n">
         <v>10</v>
       </c>
-      <c r="C27" s="298" t="n"/>
+      <c r="C27" s="298" t="n">
+        <v>0</v>
+      </c>
       <c r="D27" s="298" t="n"/>
       <c r="E27" s="300" t="n">
         <v>0</v>
@@ -15969,7 +15987,7 @@
     </row>
     <row r="28">
       <c r="E28" s="301" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15996,7 +16014,7 @@
     <row r="2" ht="18" customHeight="1" s="244" thickBot="1">
       <c r="A2" s="101" t="inlineStr">
         <is>
-          <t>52 week high low</t>
+          <t>52 week high low — NOTE: tape still sample/legacy; LBOMODEL1 uses GTM $4.31 spot on LBO!D8</t>
         </is>
       </c>
       <c r="B2" s="93" t="n"/>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
@@ -7,20 +7,31 @@
   </bookViews>
   <sheets>
     <sheet name="Coversheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LBO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DCF" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Shares" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="52wkHL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="ZI_Cover" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ZI_01_10K_Source" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ZI_02_SM_Isolation" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ZI_03_Headcount_AI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ZI_04_EBITDA_Bridge" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ZI_05_Sensitivity" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="00_Assumptions_List" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Assumptions_Coversheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Assumptions_LBO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Assumptions_DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions_Shares" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions_52wkHL" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Assumptions_ZI_01_10K_Source" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Assumptions_ZI_02_SM_Isolation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Assumptions_ZI_03_Headcount_AI" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Assumptions_ZI_04_EBITDA_Bridge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Assumptions_ZI_05_Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="LBO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DCF" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Shares" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="52wkHL" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ZI_Cover" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ZI_01_10K_Source" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ZI_02_SM_Isolation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="ZI_03_Headcount_AI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="ZI_04_EBITDA_Bridge" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="ZI_05_Sensitivity" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId12"/>
-    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId23"/>
+    <externalReference r:id="rId24"/>
   </externalReferences>
   <definedNames>
     <definedName name="CIQWBGuid" hidden="1">"a611639b-bab1-425e-aaa5-008c326fdfdb"</definedName>
@@ -60,6 +71,7 @@
     <definedName name="Products">[2]Array0!$B$5:$C$7</definedName>
     <definedName name="Rev">'[1]Forecast Drivers'!$E$25:$S$25</definedName>
     <definedName name="CIQWBGuid" localSheetId="0" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Assumptions_List'!$B$6:$J$57</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1" iterate="1"/>
 </workbook>
@@ -150,7 +162,7 @@
     <numFmt numFmtId="243" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
     <numFmt numFmtId="244" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="105">
+  <fonts count="108">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -835,6 +847,22 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1766,7 +1794,7 @@
     <xf numFmtId="244" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="238" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="558">
+  <cellXfs count="561">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2746,6 +2774,15 @@
     <xf numFmtId="182" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="190" fontId="103" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="190" fontId="102" fillId="35" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4794,7 +4831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M45"/>
+  <dimension ref="B2:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -4861,16 +4898,30 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Assumptions list (all tabs): LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.md|.pdf</t>
+      <c r="B44" s="544" t="inlineStr">
+        <is>
+          <t>IN-WORKBOOK ASSUMPTIONS LIST</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
+          <t>See sheet 00_Assumptions_List (all tabs) and Assumptions_* sheets (one per tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>51 assumptions · What / How / Why / Source · filterable on 00_Assumptions_List</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Also exported: LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf|.md|.csv</t>
         </is>
       </c>
     </row>
@@ -4890,304 +4941,272 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="55" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="12" customWidth="1" style="244" min="4" max="4"/>
-    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>EBITDA margin expansion bridge (target ≥500 bps)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="542" t="inlineStr">
-        <is>
-          <t>FY2025 baseline Revenue ($m)</t>
-        </is>
-      </c>
-      <c r="C4" s="557">
-        <f>'ZI_01_10K_Source'!E5</f>
-        <v/>
+          <t>Assumptions — ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_03_Headcount_AI` only.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>FY2025 GAAP EBITDA proxy ($m)</t>
-        </is>
-      </c>
-      <c r="C5" s="557">
-        <f>'ZI_01_10K_Source'!E20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>Baseline EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C6" s="546">
-        <f>C5/C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="542" t="inlineStr">
-        <is>
-          <t>Target margin expansion (bps)</t>
-        </is>
-      </c>
-      <c r="C7" s="548" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="542" t="inlineStr">
-        <is>
-          <t>Required incremental EBITDA ($m)</t>
-        </is>
-      </c>
-      <c r="C8" s="557">
-        <f>C4*C7/10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="542" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C10" s="541" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="541" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E10" s="541" t="n">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="542" t="inlineStr">
-        <is>
-          <t>Revenue (flat case for margin math)</t>
-        </is>
-      </c>
-      <c r="C11" s="557">
-        <f>$C$4</f>
-        <v/>
-      </c>
-      <c r="D11" s="557">
-        <f>$C$4</f>
-        <v/>
-      </c>
-      <c r="E11" s="557">
-        <f>$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="542" t="inlineStr">
-        <is>
-          <t>Net EBITDA benefit from program</t>
-        </is>
-      </c>
-      <c r="C12" s="557">
-        <f>'ZI_03_Headcount_AI'!C39</f>
-        <v/>
-      </c>
-      <c r="D12" s="557">
-        <f>'ZI_03_Headcount_AI'!D39</f>
-        <v/>
-      </c>
-      <c r="E12" s="557">
-        <f>'ZI_03_Headcount_AI'!E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="542" t="inlineStr">
-        <is>
-          <t>Run-rate benefit (ex one-time)</t>
-        </is>
-      </c>
-      <c r="C13" s="557">
-        <f>'ZI_03_Headcount_AI'!C40</f>
-        <v/>
-      </c>
-      <c r="D13" s="557">
-        <f>'ZI_03_Headcount_AI'!D40</f>
-        <v/>
-      </c>
-      <c r="E13" s="557">
-        <f>'ZI_03_Headcount_AI'!E40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="542" t="inlineStr">
-        <is>
-          <t>Pro forma EBITDA</t>
-        </is>
-      </c>
-      <c r="C14" s="557">
-        <f>$C$5+C12</f>
-        <v/>
-      </c>
-      <c r="D14" s="557">
-        <f>$C$5+D12</f>
-        <v/>
-      </c>
-      <c r="E14" s="557">
-        <f>$C$5+E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="542" t="inlineStr">
-        <is>
-          <t>Pro forma EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C15" s="546">
-        <f>C14/C11</f>
-        <v/>
-      </c>
-      <c r="D15" s="546">
-        <f>D14/D11</f>
-        <v/>
-      </c>
-      <c r="E15" s="546">
-        <f>E14/E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="544" t="inlineStr">
-        <is>
-          <t>Margin expansion (bps)</t>
-        </is>
-      </c>
-      <c r="C16" s="557">
-        <f>(C15-$C$6)*10000</f>
-        <v/>
-      </c>
-      <c r="D16" s="557">
-        <f>(D15-$C$6)*10000</f>
-        <v/>
-      </c>
-      <c r="E16" s="557">
-        <f>(E15-$C$6)*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="544" t="inlineStr">
-        <is>
-          <t>Run-rate expansion (bps)</t>
-        </is>
-      </c>
-      <c r="C17" s="557">
-        <f>(C13/$C$4)*10000</f>
-        <v/>
-      </c>
-      <c r="D17" s="557">
-        <f>(D13/$C$4)*10000</f>
-        <v/>
-      </c>
-      <c r="E17" s="557">
-        <f>(E13/$C$4)*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="542" t="inlineStr">
-        <is>
-          <t>Hits ≥500 bps run-rate?</t>
-        </is>
-      </c>
-      <c r="C18" s="554">
-        <f>IF(C17&gt;=$C$7,"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="D18" s="554">
-        <f>IF(D17&gt;=$C$7,"YES","NO")</f>
-        <v/>
-      </c>
-      <c r="E18" s="554">
-        <f>IF(E17&gt;=$C$7,"YES","NO")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M % revenue bridge</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="542" t="inlineStr">
-        <is>
-          <t>Baseline S&amp;M %</t>
-        </is>
-      </c>
-      <c r="C21" s="546">
-        <f>'ZI_02_SM_Isolation'!C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="542" t="inlineStr">
-        <is>
-          <t>PF S&amp;M $ (baseline − SDR save + AI/oversight)</t>
-        </is>
-      </c>
-      <c r="C22" s="557">
-        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!C34+'ZI_03_Headcount_AI'!C35+'ZI_03_Headcount_AI'!C36</f>
-        <v/>
-      </c>
-      <c r="D22" s="557">
-        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!D34+'ZI_03_Headcount_AI'!D35+'ZI_03_Headcount_AI'!D36</f>
-        <v/>
-      </c>
-      <c r="E22" s="557">
-        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!E34+'ZI_03_Headcount_AI'!E35+'ZI_03_Headcount_AI'!E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="542" t="inlineStr">
-        <is>
-          <t>PF S&amp;M % revenue</t>
-        </is>
-      </c>
-      <c r="C23" s="546">
-        <f>C22/$C$4</f>
-        <v/>
-      </c>
-      <c r="D23" s="546">
-        <f>D22/$C$4</f>
-        <v/>
-      </c>
-      <c r="E23" s="546">
-        <f>E22/$C$4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Yellow cells on 03_Headcount_AI drive the bridge. Base case sized to clear 500 bps by Y3 run-rate: 40% of S&amp;M = outbound SDRs; 95% replaced; $155k/SDR vs $15k AI seat + oversight. 500 bps on $1,249.5m revenue needs ~$62.5m run-rate EBITDA.</t>
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>% of S&amp;M that are outbound SDR/BDR</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Share of S&amp;M headcount treated as AI-replaceable SDRs.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input × 1,370.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>10-K does not disclose SDR count — explicit model assumption.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Fully loaded cost / SDR / yr</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$155k</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Cash cost per outbound SDR.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Below blended residual S&amp;M $/employee (commissions/ads stay).</t>
+        </is>
+      </c>
+      <c r="I7" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>C13/C15</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>AI seat / oversight cost</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>$15k per seat; $150k per oversight FTE</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Replacement opex for AI agents + humans.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs; 1 oversight FTE / 20 seats.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Net savings must clear AI + oversight to hit margin target.</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>C21:E21</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>Cumulative % SDRs replaced</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>45% / 80% / 95% (2026–28)</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>Headcount reduction schedule.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Yellow cumulative exit fractions.</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Phased cut to avoid one-year cliff risk.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>C16/C17</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>Severance / AI build</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>$25k per SDR; $8m Y1 build</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>One-time costs.</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs in P&amp;L impact.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>Hits in-year EBITDA but excluded from run-rate bps.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
         </is>
       </c>
     </row>
@@ -5202,295 +5221,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" style="244" min="2" max="2"/>
-    <col width="10" customWidth="1" style="244" min="3" max="3"/>
-    <col width="10" customWidth="1" style="244" min="4" max="4"/>
-    <col width="10" customWidth="1" style="244" min="5" max="5"/>
-    <col width="10" customWidth="1" style="244" min="6" max="6"/>
-    <col width="10" customWidth="1" style="244" min="7" max="7"/>
-    <col width="10" customWidth="1" style="244" min="8" max="8"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>Sensitivity — Y3 run-rate margin expansion (bps)</t>
+          <t>Assumptions — ZI_04_EBITDA_Bridge</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rows = cumulative % SDRs replaced; Cols = AI $/seat-yr ($000s). Other inputs from 03_Headcount_AI.</t>
+          <t>Subset of 00_Assumptions_List for tab `ZI_04_EBITDA_Bridge` only.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>SDR0</t>
-        </is>
-      </c>
-      <c r="C5" s="549">
-        <f>'ZI_03_Headcount_AI'!C7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>SDR cost $k</t>
-        </is>
-      </c>
-      <c r="C6" s="557">
-        <f>'ZI_03_Headcount_AI'!C8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="542" t="inlineStr">
-        <is>
-          <t>Seats/SDR</t>
-        </is>
-      </c>
-      <c r="C7" s="555">
-        <f>'ZI_03_Headcount_AI'!C12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="542" t="inlineStr">
-        <is>
-          <t>Oversight $k</t>
-        </is>
-      </c>
-      <c r="C8" s="557">
-        <f>'ZI_03_Headcount_AI'!C15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="542" t="inlineStr">
-        <is>
-          <t>Revenue $m</t>
-        </is>
-      </c>
-      <c r="C9" s="557">
-        <f>'ZI_01_10K_Source'!E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>bps \ AI $k</t>
-        </is>
-      </c>
-      <c r="C11" s="548" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="548" t="n">
-        <v>12</v>
-      </c>
-      <c r="E11" s="548" t="n">
-        <v>18</v>
-      </c>
-      <c r="F11" s="548" t="n">
-        <v>24</v>
-      </c>
-      <c r="G11" s="548" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="548" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="553" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*8/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*12/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*18/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*24/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*30/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H12" s="549">
-        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*40/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="553" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*8/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*12/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*18/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*24/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*30/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H13" s="549">
-        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*40/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="553" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*8/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*12/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*18/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*24/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*30/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H14" s="549">
-        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*40/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="553" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="C15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*8/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*12/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*18/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*24/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*30/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H15" s="549">
-        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*40/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="553" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*8/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*12/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*18/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*24/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*30/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H16" s="549">
-        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*40/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="553" t="n">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*8/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="D17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*12/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="E17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*18/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="F17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*24/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="G17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*30/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-      <c r="H17" s="549">
-        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*40/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="542" t="inlineStr">
-        <is>
-          <t>Base case Y3 run-rate bps (from bridge)</t>
-        </is>
-      </c>
-      <c r="C20" s="557">
-        <f>'ZI_04_EBITDA_Bridge'!E17</f>
-        <v/>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Target margin expansion</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>500 bps</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Minimum success hurdle for the AI program.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input; YES/NO vs run-rate bps.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> equates to ~$62.5m EBITDA on $1,249.5m revenue.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>User thesis requirement</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5498,14 +5335,134 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — ZI_05_Sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_05_Sensitivity` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>B12:H17</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Sensitivity grid</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>Replace-% × AI $/seat → bps</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Y3 run-rate bps under alternate AI costs / cut depths.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Algebra on SDR0 &amp; unit costs.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Shows what it takes to stay above 500 bps if AI is more expensive.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>Derived from ZI_03 inputs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:R393"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="44.140625" customWidth="1" style="244" min="2" max="2"/>
@@ -14057,14 +14014,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:K118"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="40.28515625" customWidth="1" style="244" min="2" max="2"/>
@@ -15687,14 +15644,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
     <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
@@ -15996,14 +15953,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:F268"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="19.42578125" bestFit="1" customWidth="1" style="244" min="1" max="1"/>
     <col width="9.28515625" bestFit="1" customWidth="1" style="244" min="2" max="5"/>
@@ -21300,14 +21257,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="244" min="2" max="2"/>
     <col width="100" customWidth="1" style="244" min="3" max="3"/>
@@ -21464,6 +21421,6036 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="42" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12" customWidth="1" style="244" min="3" max="3"/>
+    <col width="12" customWidth="1" style="244" min="4" max="4"/>
+    <col width="14" customWidth="1" style="244" min="5" max="5"/>
+    <col width="70" customWidth="1" style="244" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>FY2025 10-K source financials ($ millions unless noted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="541" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="C4" s="541" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="D4" s="541" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="E4" s="541" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="F4" s="541" t="inlineStr">
+        <is>
+          <t>XBRL / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="556" t="n">
+        <v>1239.5</v>
+      </c>
+      <c r="D5" s="556" t="n">
+        <v>1214.3</v>
+      </c>
+      <c r="E5" s="556" t="n">
+        <v>1249.5</v>
+      </c>
+      <c r="F5" s="542" t="inlineStr">
+        <is>
+          <t>RevenueFromContractWithCustomerExcludingAssessedTax</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>Selling &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="C6" s="556" t="n">
+        <v>408.5</v>
+      </c>
+      <c r="D6" s="556" t="n">
+        <v>414.1</v>
+      </c>
+      <c r="E6" s="556" t="n">
+        <v>414.6</v>
+      </c>
+      <c r="F6" s="542" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="542" t="inlineStr">
+        <is>
+          <t>Research &amp; Development</t>
+        </is>
+      </c>
+      <c r="C7" s="556" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="D7" s="556" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="E7" s="556" t="n">
+        <v>182</v>
+      </c>
+      <c r="F7" s="542" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopmentExpense</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="542" t="inlineStr">
+        <is>
+          <t>General &amp; Administrative</t>
+        </is>
+      </c>
+      <c r="C8" s="556" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="D8" s="556" t="n">
+        <v>295.3</v>
+      </c>
+      <c r="E8" s="556" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="F8" s="542" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="542" t="inlineStr">
+        <is>
+          <t>Operating expenses (ex-COGS)</t>
+        </is>
+      </c>
+      <c r="E9" s="556" t="n">
+        <v>824.2</v>
+      </c>
+      <c r="F9" s="542" t="inlineStr">
+        <is>
+          <t>OperatingExpenses</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="542" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="C10" s="556" t="n">
+        <v>259.5</v>
+      </c>
+      <c r="D10" s="556" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="E10" s="556" t="n">
+        <v>225.7</v>
+      </c>
+      <c r="F10" s="542" t="inlineStr">
+        <is>
+          <t>OperatingIncomeLoss</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="542" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="C11" s="556" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="D11" s="556" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E11" s="556" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="F11" s="542" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="542" t="inlineStr">
+        <is>
+          <t>Amort. of intangibles</t>
+        </is>
+      </c>
+      <c r="C12" s="556" t="n">
+        <v>61</v>
+      </c>
+      <c r="D12" s="556" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E12" s="556" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="F12" s="542" t="inlineStr">
+        <is>
+          <t>AmortizationOfIntangibleAssets</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="542" t="inlineStr">
+        <is>
+          <t>Total D&amp;A (dep+intang)</t>
+        </is>
+      </c>
+      <c r="C13" s="556" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D13" s="556" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="E13" s="556" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="F13" s="542" t="inlineStr">
+        <is>
+          <t>OtherDepreciationAndAmortization</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="542" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="C14" s="556" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="D14" s="556" t="n">
+        <v>138</v>
+      </c>
+      <c r="E14" s="556" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="F14" s="542" t="inlineStr">
+        <is>
+          <t>ShareBasedCompensation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="542" t="inlineStr">
+        <is>
+          <t>Advertising expense</t>
+        </is>
+      </c>
+      <c r="E15" s="556" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="F15" s="542" t="inlineStr">
+        <is>
+          <t>AdvertisingExpense</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="542" t="inlineStr">
+        <is>
+          <t>Amort. deferred commissions</t>
+        </is>
+      </c>
+      <c r="C16" s="556" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="D16" s="556" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="E16" s="556" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="F16" s="542" t="inlineStr">
+        <is>
+          <t>AmortizationOfDeferredSalesCommissions</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="542" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="C17" s="556" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="D17" s="556" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E17" s="556" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="F17" s="542" t="inlineStr">
+        <is>
+          <t>NetIncomeLoss</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="544" t="inlineStr">
+        <is>
+          <t>Implied COGS (Rev − OpEx − OpInc)</t>
+        </is>
+      </c>
+      <c r="E19" s="557">
+        <f>E5-E9-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="544" t="inlineStr">
+        <is>
+          <t>GAAP EBITDA proxy (OpInc + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="E20" s="557">
+        <f>E10+E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="542" t="inlineStr">
+        <is>
+          <t>GAAP EBITDA margin</t>
+        </is>
+      </c>
+      <c r="E21" s="546">
+        <f>E20/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="544" t="inlineStr">
+        <is>
+          <t>Adj. EBITDA proxy (+SBC)</t>
+        </is>
+      </c>
+      <c r="E22" s="557">
+        <f>E20+E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="542" t="inlineStr">
+        <is>
+          <t>Adj. EBITDA margin</t>
+        </is>
+      </c>
+      <c r="E23" s="546">
+        <f>E22/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="547" t="inlineStr">
+        <is>
+          <t>HUMAN CAPITAL (10-K Item 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="542" t="inlineStr">
+        <is>
+          <t>Total employees (12/31/2025)</t>
+        </is>
+      </c>
+      <c r="E26" s="548" t="n">
+        <v>3180</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="542" t="inlineStr">
+        <is>
+          <t>Cost of service employees</t>
+        </is>
+      </c>
+      <c r="E27" s="548" t="n">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="542" t="inlineStr">
+        <is>
+          <t>Sales &amp; Marketing employees</t>
+        </is>
+      </c>
+      <c r="E28" s="548" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="542" t="inlineStr">
+        <is>
+          <t>R&amp;D employees</t>
+        </is>
+      </c>
+      <c r="E29" s="548" t="n">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="542" t="inlineStr">
+        <is>
+          <t>G&amp;A employees</t>
+        </is>
+      </c>
+      <c r="E30" s="548" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="542" t="inlineStr">
+        <is>
+          <t>Headcount check (sum)</t>
+        </is>
+      </c>
+      <c r="E31" s="549">
+        <f>E27+E28+E29+E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M $ / S&amp;M employee ($000s)</t>
+        </is>
+      </c>
+      <c r="E32" s="557">
+        <f>E6*1000/E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M % of revenue</t>
+        </is>
+      </c>
+      <c r="E33" s="546">
+        <f>E6/E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="542" t="inlineStr">
+        <is>
+          <t>Quote — Human Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="550" t="inlineStr">
+        <is>
+          <t>As of December 31, 2025, we had 3,180 employees, consisting of 662 in cost of service, 1,370 in sales and marketing, 763 in research and development, and 385 in general and administrative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B36:F38"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="48" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Isolate bloated Sales &amp; Marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="542" t="inlineStr">
+        <is>
+          <t>FY2025 Revenue ($m)</t>
+        </is>
+      </c>
+      <c r="C4" s="557">
+        <f>'ZI_01_10K_Source'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>FY2025 S&amp;M ($m)</t>
+        </is>
+      </c>
+      <c r="C5" s="557">
+        <f>'ZI_01_10K_Source'!E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M % revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="546">
+        <f>C5/C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="547" t="inlineStr">
+        <is>
+          <t>S&amp;M STACK (FY2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="542" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="C9" s="557">
+        <f>'ZI_01_10K_Source'!E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="542" t="inlineStr">
+        <is>
+          <t>Deferred commission amortization</t>
+        </is>
+      </c>
+      <c r="C10" s="557">
+        <f>'ZI_01_10K_Source'!E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="542" t="inlineStr">
+        <is>
+          <t>Residual S&amp;M (people + other)</t>
+        </is>
+      </c>
+      <c r="C11" s="557">
+        <f>C5-C9-C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="542" t="inlineStr">
+        <is>
+          <t>Residual as % of S&amp;M</t>
+        </is>
+      </c>
+      <c r="C12" s="546">
+        <f>C11/C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="542" t="inlineStr">
+        <is>
+          <t>Residual $ / S&amp;M employee ($000s)</t>
+        </is>
+      </c>
+      <c r="C13" s="557">
+        <f>C11*1000/'ZI_01_10K_Source'!E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="547" t="inlineStr">
+        <is>
+          <t>BENCHMARK / THESIS INPUTS (edit yellow)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="542" t="inlineStr">
+        <is>
+          <t>Target mature SaaS S&amp;M % rev</t>
+        </is>
+      </c>
+      <c r="C16" s="551" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M bloat vs target ($m)</t>
+        </is>
+      </c>
+      <c r="C17" s="557">
+        <f>MAX(0,C5-C4*C16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="542" t="inlineStr">
+        <is>
+          <t>Bloat as % of revenue</t>
+        </is>
+      </c>
+      <c r="C18" s="546">
+        <f>C17/C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="542" t="inlineStr">
+        <is>
+          <t>Bloat in basis points</t>
+        </is>
+      </c>
+      <c r="C19" s="549">
+        <f>C18*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>10-K: 1,370 S&amp;M employees; S&amp;M is ~33% of revenue. Model treats outbound SDR/BDR capacity as the AI-replaceable slice (yellow % on next sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="22" customWidth="1" style="244" min="3" max="3"/>
+    <col width="14" customWidth="1" style="244" min="4" max="4"/>
+    <col width="32" customWidth="1" style="244" min="5" max="5"/>
+    <col width="28" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="36" customWidth="1" style="244" min="8" max="8"/>
+    <col width="40" customWidth="1" style="244" min="9" max="9"/>
+    <col width="55" customWidth="1" style="244" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — Assumptions List (every tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Plain in-workbook list. Every row: Tab · Cell · Name · Value · What · How · Why · Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ticker: GTM (ZoomInfo Technologies Inc.). Educational / research use only — not investment advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="244">
+      <c r="B6" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C6" s="558" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="D6" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="E6" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="F6" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="G6" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="H6" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="I6" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="J6" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>Coversheet</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>Model identity</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — ZoomInfo (GTM)</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Name of this LBO case.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Set on Coversheet and LBO!B2.</t>
+        </is>
+      </c>
+      <c r="I7" s="559" t="inlineStr">
+        <is>
+          <t>Separates ZoomInfo LBOMODEL1 from the blank WSP BMC sample.</t>
+        </is>
+      </c>
+      <c r="J7" s="560" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/vengeanceaiUSC_LBOMODEL1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>Coversheet</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>$ millions except per share / rates / multiples</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Unit convention for the workbook.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Stated on LBO!B3 / DCF!B3.</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Matches WSP template convention and SEC $ presentation scaled to millions.</t>
+        </is>
+      </c>
+      <c r="J8" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>D6/D7</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>Company / ticker</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc. / GTM</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Target company identity.</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded inputs on LBO general inputs.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Public GTM (legacy ZI) is the LBOMODEL1 case company.</t>
+        </is>
+      </c>
+      <c r="J9" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>$4.31</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>Spot equity price used for premium math.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D8 market input.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Latest available GTM print used when MODEL1 was built (~2026-08-12).</t>
+        </is>
+      </c>
+      <c r="J10" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D11" s="559" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="E11" s="559" t="inlineStr">
+        <is>
+          <t>Price date</t>
+        </is>
+      </c>
+      <c r="F11" s="559" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G11" s="559" t="inlineStr">
+        <is>
+          <t>As-of date for the spot price.</t>
+        </is>
+      </c>
+      <c r="H11" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D9.</t>
+        </is>
+      </c>
+      <c r="I11" s="559" t="inlineStr">
+        <is>
+          <t>Timestamps the market input for auditability.</t>
+        </is>
+      </c>
+      <c r="J11" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D12" s="559" t="inlineStr">
+        <is>
+          <t>H21</t>
+        </is>
+      </c>
+      <c r="E12" s="559" t="inlineStr">
+        <is>
+          <t>Acquisition premium</t>
+        </is>
+      </c>
+      <c r="F12" s="559" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G12" s="559" t="inlineStr">
+        <is>
+          <t>Premium of offer price over spot.</t>
+        </is>
+      </c>
+      <c r="H12" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh = D8×(1+premium).</t>
+        </is>
+      </c>
+      <c r="I12" s="559" t="inlineStr">
+        <is>
+          <t>Standard illustrative take-private premium; editable deal assumption.</t>
+        </is>
+      </c>
+      <c r="J12" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D13" s="559" t="inlineStr">
+        <is>
+          <t>H20</t>
+        </is>
+      </c>
+      <c r="E13" s="559" t="inlineStr">
+        <is>
+          <t>Offer price / share</t>
+        </is>
+      </c>
+      <c r="F13" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="G13" s="559" t="inlineStr">
+        <is>
+          <t>Implied takeout price per share.</t>
+        </is>
+      </c>
+      <c r="H13" s="559" t="inlineStr">
+        <is>
+          <t>D8 × 1.25.</t>
+        </is>
+      </c>
+      <c r="I13" s="559" t="inlineStr">
+        <is>
+          <t>Drives equity purchase price in Uses.</t>
+        </is>
+      </c>
+      <c r="J13" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption + market price</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="559" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D14" s="559" t="inlineStr">
+        <is>
+          <t>H18</t>
+        </is>
+      </c>
+      <c r="E14" s="559" t="inlineStr">
+        <is>
+          <t>Diluted shares (millions)</t>
+        </is>
+      </c>
+      <c r="F14" s="559" t="inlineStr">
+        <is>
+          <t>292.312</t>
+        </is>
+      </c>
+      <c r="G14" s="559" t="inlineStr">
+        <is>
+          <t>Share count for equity value.</t>
+        </is>
+      </c>
+      <c r="H14" s="559" t="inlineStr">
+        <is>
+          <t>From latest shares outstanding.</t>
+        </is>
+      </c>
+      <c r="I14" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30 common shares outstanding used as diluted proxy (options ladder not fully modeled).</t>
+        </is>
+      </c>
+      <c r="J14" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="244">
+      <c r="B15" s="559" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D15" s="559" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="E15" s="559" t="inlineStr">
+        <is>
+          <t>Equity purchase price</t>
+        </is>
+      </c>
+      <c r="F15" s="559" t="inlineStr">
+        <is>
+          <t>$1,574.8m</t>
+        </is>
+      </c>
+      <c r="G15" s="559" t="inlineStr">
+        <is>
+          <t>Cash to buy equity.</t>
+        </is>
+      </c>
+      <c r="H15" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh × shares.</t>
+        </is>
+      </c>
+      <c r="I15" s="559" t="inlineStr">
+        <is>
+          <t>Primary Use of funds line.</t>
+        </is>
+      </c>
+      <c r="J15" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="244">
+      <c r="B16" s="559" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D16" s="559" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="E16" s="559" t="inlineStr">
+        <is>
+          <t>LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="F16" s="559" t="inlineStr">
+        <is>
+          <t>$314.5m</t>
+        </is>
+      </c>
+      <c r="G16" s="559" t="inlineStr">
+        <is>
+          <t>Entry EBITDA for leverage / multiple math.</t>
+        </is>
+      </c>
+      <c r="H16" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 OpInc $225.7m + D&amp;A $88.8m.</t>
+        </is>
+      </c>
+      <c r="I16" s="559" t="inlineStr">
+        <is>
+          <t>GAAP EBITDA proxy from latest annual 10-K (not adjusted EBITDA).</t>
+        </is>
+      </c>
+      <c r="J16" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="244">
+      <c r="B17" s="559" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D17" s="559" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="E17" s="559" t="inlineStr">
+        <is>
+          <t>Gross debt</t>
+        </is>
+      </c>
+      <c r="F17" s="559" t="inlineStr">
+        <is>
+          <t>−$1,269.9m</t>
+        </is>
+      </c>
+      <c r="G17" s="559" t="inlineStr">
+        <is>
+          <t>Debt refinanced at close (entered as negative in template).</t>
+        </is>
+      </c>
+      <c r="H17" s="559" t="inlineStr">
+        <is>
+          <t>LT debt + current maturities.</t>
+        </is>
+      </c>
+      <c r="I17" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30: LongTermDebt + LongTermDebtCurrent.</t>
+        </is>
+      </c>
+      <c r="J17" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="244">
+      <c r="B18" s="559" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D18" s="559" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="E18" s="559" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F18" s="559" t="inlineStr">
+        <is>
+          <t>$150.1m</t>
+        </is>
+      </c>
+      <c r="G18" s="559" t="inlineStr">
+        <is>
+          <t>Cash available at entry.</t>
+        </is>
+      </c>
+      <c r="H18" s="559" t="inlineStr">
+        <is>
+          <t>Cash &amp; equivalents + short-term investments.</t>
+        </is>
+      </c>
+      <c r="I18" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30.</t>
+        </is>
+      </c>
+      <c r="J18" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="244">
+      <c r="B19" s="559" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D19" s="559" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="E19" s="559" t="inlineStr">
+        <is>
+          <t>Minimum cash</t>
+        </is>
+      </c>
+      <c r="F19" s="559" t="inlineStr">
+        <is>
+          <t>$50.0m</t>
+        </is>
+      </c>
+      <c r="G19" s="559" t="inlineStr">
+        <is>
+          <t>Cash retained for ops; excess used as a Source.</t>
+        </is>
+      </c>
+      <c r="H19" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy input.</t>
+        </is>
+      </c>
+      <c r="I19" s="559" t="inlineStr">
+        <is>
+          <t>Leaves liquidity post-close; excess cash = 150.1 − 50 = 100.1.</t>
+        </is>
+      </c>
+      <c r="J19" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="244">
+      <c r="B20" s="559" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D20" s="559" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="E20" s="559" t="inlineStr">
+        <is>
+          <t>Entry EV / LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="F20" s="559" t="inlineStr">
+        <is>
+          <t>8.57x</t>
+        </is>
+      </c>
+      <c r="G20" s="559" t="inlineStr">
+        <is>
+          <t>Implied entry multiple.</t>
+        </is>
+      </c>
+      <c r="H20" s="559" t="inlineStr">
+        <is>
+          <t>(Equity buy + debt − cash) / EBITDA.</t>
+        </is>
+      </c>
+      <c r="I20" s="559" t="inlineStr">
+        <is>
+          <t>Output of offer + net debt vs LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="J20" s="559" t="inlineStr">
+        <is>
+          <t>Derived from SEC + market inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="244">
+      <c r="B21" s="559" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D21" s="559" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="E21" s="559" t="inlineStr">
+        <is>
+          <t>Exit EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="F21" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="G21" s="559" t="inlineStr">
+        <is>
+          <t>Exit multiple in hold-year 5.</t>
+        </is>
+      </c>
+      <c r="H21" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17 policy input.</t>
+        </is>
+      </c>
+      <c r="I21" s="559" t="inlineStr">
+        <is>
+          <t>Near entry; assumes modest multiple compression vs entry 8.57x.</t>
+        </is>
+      </c>
+      <c r="J21" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="244">
+      <c r="B22" s="559" t="n">
+        <v>16</v>
+      </c>
+      <c r="C22" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D22" s="559" t="inlineStr">
+        <is>
+          <t>C29/D29</t>
+        </is>
+      </c>
+      <c r="E22" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan A</t>
+        </is>
+      </c>
+      <c r="F22" s="559" t="inlineStr">
+        <is>
+          <t>2.5x / $786.2m</t>
+        </is>
+      </c>
+      <c r="G22" s="559" t="inlineStr">
+        <is>
+          <t>New TLA quantum.</t>
+        </is>
+      </c>
+      <c r="H22" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="I22" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="J22" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="244">
+      <c r="B23" s="559" t="n">
+        <v>17</v>
+      </c>
+      <c r="C23" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D23" s="559" t="inlineStr">
+        <is>
+          <t>C30/D30</t>
+        </is>
+      </c>
+      <c r="E23" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan B</t>
+        </is>
+      </c>
+      <c r="F23" s="559" t="inlineStr">
+        <is>
+          <t>1.5x / $471.8m</t>
+        </is>
+      </c>
+      <c r="G23" s="559" t="inlineStr">
+        <is>
+          <t>New TLB quantum.</t>
+        </is>
+      </c>
+      <c r="H23" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="I23" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="J23" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="244">
+      <c r="B24" s="559" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D24" s="559" t="inlineStr">
+        <is>
+          <t>C31/D31</t>
+        </is>
+      </c>
+      <c r="E24" s="559" t="inlineStr">
+        <is>
+          <t>Senior Notes</t>
+        </is>
+      </c>
+      <c r="F24" s="559" t="inlineStr">
+        <is>
+          <t>1.0x / $314.5m</t>
+        </is>
+      </c>
+      <c r="G24" s="559" t="inlineStr">
+        <is>
+          <t>New senior notes quantum.</t>
+        </is>
+      </c>
+      <c r="H24" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="I24" s="559" t="inlineStr">
+        <is>
+          <t>Completes 5.0x new debt with TLA+TLB.</t>
+        </is>
+      </c>
+      <c r="J24" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="244">
+      <c r="B25" s="559" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D25" s="559" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="E25" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor equity</t>
+        </is>
+      </c>
+      <c r="F25" s="559" t="inlineStr">
+        <is>
+          <t>$1,203.6m</t>
+        </is>
+      </c>
+      <c r="G25" s="559" t="inlineStr">
+        <is>
+          <t>Equity check (Sources plug).</t>
+        </is>
+      </c>
+      <c r="H25" s="559" t="inlineStr">
+        <is>
+          <t>Total Uses − excess cash − new debt.</t>
+        </is>
+      </c>
+      <c r="I25" s="559" t="inlineStr">
+        <is>
+          <t>Balancing figure so Sources = Uses ($2,876.2m).</t>
+        </is>
+      </c>
+      <c r="J25" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="244">
+      <c r="B26" s="559" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D26" s="559" t="inlineStr">
+        <is>
+          <t>G36</t>
+        </is>
+      </c>
+      <c r="E26" s="559" t="inlineStr">
+        <is>
+          <t>Transaction fee %</t>
+        </is>
+      </c>
+      <c r="F26" s="559" t="inlineStr">
+        <is>
+          <t>2% of equity value</t>
+        </is>
+      </c>
+      <c r="G26" s="559" t="inlineStr">
+        <is>
+          <t>M&amp;A / financing fee assumption.</t>
+        </is>
+      </c>
+      <c r="H26" s="559" t="inlineStr">
+        <is>
+          <t>Fees $ = 2% × equity purchase.</t>
+        </is>
+      </c>
+      <c r="I26" s="559" t="inlineStr">
+        <is>
+          <t>Simple fee load for Uses; financing fee dollars also shown in fee block.</t>
+        </is>
+      </c>
+      <c r="J26" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="244">
+      <c r="B27" s="559" t="n">
+        <v>21</v>
+      </c>
+      <c r="C27" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D27" s="559" t="inlineStr">
+        <is>
+          <t>F65:J65</t>
+        </is>
+      </c>
+      <c r="E27" s="559" t="inlineStr">
+        <is>
+          <t>Revenue growth (FY26–30)</t>
+        </is>
+      </c>
+      <c r="F27" s="559" t="inlineStr">
+        <is>
+          <t>4% / 5% / 5% / 4% / 3%</t>
+        </is>
+      </c>
+      <c r="G27" s="559" t="inlineStr">
+        <is>
+          <t>YoY revenue growth in forecast.</t>
+        </is>
+      </c>
+      <c r="H27" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded on growth row.</t>
+        </is>
+      </c>
+      <c r="I27" s="559" t="inlineStr">
+        <is>
+          <t>Modest recovery vs FY24 dip; not a hyper-growth case.</t>
+        </is>
+      </c>
+      <c r="J27" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="244">
+      <c r="B28" s="559" t="n">
+        <v>22</v>
+      </c>
+      <c r="C28" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D28" s="559" t="inlineStr">
+        <is>
+          <t>E66/F66</t>
+        </is>
+      </c>
+      <c r="E28" s="559" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="F28" s="559" t="inlineStr">
+        <is>
+          <t>FY25 82.35% → Fcst 82.85%</t>
+        </is>
+      </c>
+      <c r="G28" s="559" t="inlineStr">
+        <is>
+          <t>Gross profit % of sales.</t>
+        </is>
+      </c>
+      <c r="H28" s="559" t="inlineStr">
+        <is>
+          <t>From FY25 COGS implied by 10-K; slight +50 bps in forecast.</t>
+        </is>
+      </c>
+      <c r="I28" s="559" t="inlineStr">
+        <is>
+          <t>Software gross margin structure from SEC P&amp;L.</t>
+        </is>
+      </c>
+      <c r="J28" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="244">
+      <c r="B29" s="559" t="n">
+        <v>23</v>
+      </c>
+      <c r="C29" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D29" s="559" t="inlineStr">
+        <is>
+          <t>E67/F67</t>
+        </is>
+      </c>
+      <c r="E29" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D margin</t>
+        </is>
+      </c>
+      <c r="F29" s="559" t="inlineStr">
+        <is>
+          <t>14.57% flat in forecast</t>
+        </is>
+      </c>
+      <c r="G29" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D % of sales.</t>
+        </is>
+      </c>
+      <c r="H29" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 R&amp;D / Revenue held flat.</t>
+        </is>
+      </c>
+      <c r="I29" s="559" t="inlineStr">
+        <is>
+          <t>Keeps product investment while S&amp;M is the efficiency lever.</t>
+        </is>
+      </c>
+      <c r="J29" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1" s="244">
+      <c r="B30" s="559" t="n">
+        <v>24</v>
+      </c>
+      <c r="C30" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D30" s="559" t="inlineStr">
+        <is>
+          <t>F68:J68</t>
+        </is>
+      </c>
+      <c r="E30" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A margin path</t>
+        </is>
+      </c>
+      <c r="F30" s="559" t="inlineStr">
+        <is>
+          <t>47.72% → 46.22% → 44.72% → 44.22% → 44.22%</t>
+        </is>
+      </c>
+      <c r="G30" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A (S&amp;M+G&amp;A) % of sales in forecast.</t>
+        </is>
+      </c>
+      <c r="H30" s="559" t="inlineStr">
+        <is>
+          <t>Compresses ~500 bps of revenue by Y3 vs FY25 49.72%.</t>
+        </is>
+      </c>
+      <c r="I30" s="559" t="inlineStr">
+        <is>
+          <t>Operationalizes ZI AI-SDR thesis into the LBO P&amp;L.</t>
+        </is>
+      </c>
+      <c r="J30" s="559" t="inlineStr">
+        <is>
+          <t>LBOMODEL1 thesis + ZI_* tabs; FY25 base from https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1" s="244">
+      <c r="B31" s="559" t="n">
+        <v>25</v>
+      </c>
+      <c r="C31" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D31" s="559" t="inlineStr">
+        <is>
+          <t>C69:J69</t>
+        </is>
+      </c>
+      <c r="E31" s="559" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="F31" s="559" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="G31" s="559" t="inlineStr">
+        <is>
+          <t>Book tax rate on EBT.</t>
+        </is>
+      </c>
+      <c r="H31" s="559" t="inlineStr">
+        <is>
+          <t>Flat statutory-like rate in MODEL1.</t>
+        </is>
+      </c>
+      <c r="I31" s="559" t="inlineStr">
+        <is>
+          <t>Simplifies vs actual cash tax / NOL complexity.</t>
+        </is>
+      </c>
+      <c r="J31" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1" s="244">
+      <c r="B32" s="559" t="n">
+        <v>26</v>
+      </c>
+      <c r="C32" s="559" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="D32" s="559" t="inlineStr">
+        <is>
+          <t>I275/J275</t>
+        </is>
+      </c>
+      <c r="E32" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor MoIC / IRR</t>
+        </is>
+      </c>
+      <c r="F32" s="559" t="inlineStr">
+        <is>
+          <t>~2.97x / ~24.4%</t>
+        </is>
+      </c>
+      <c r="G32" s="559" t="inlineStr">
+        <is>
+          <t>Base returns at 8.0x exit.</t>
+        </is>
+      </c>
+      <c r="H32" s="559" t="inlineStr">
+        <is>
+          <t>Exit equity / sponsor equity; IRR = MoIC^(1/5)−1.</t>
+        </is>
+      </c>
+      <c r="I32" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative; sensitive to exit multiple, leverage, and SG&amp;A path.</t>
+        </is>
+      </c>
+      <c r="J32" s="559" t="inlineStr">
+        <is>
+          <t>Derived on LBO returns block</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1" s="244">
+      <c r="B33" s="559" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D33" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E33" s="559" t="inlineStr">
+        <is>
+          <t>DCF reference share price</t>
+        </is>
+      </c>
+      <c r="F33" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875 (LBO offer)</t>
+        </is>
+      </c>
+      <c r="G33" s="559" t="inlineStr">
+        <is>
+          <t>Price shown in DCF header for football-field compare.</t>
+        </is>
+      </c>
+      <c r="H33" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer/sh.</t>
+        </is>
+      </c>
+      <c r="I33" s="559" t="inlineStr">
+        <is>
+          <t>Makes DCF tab speak the same deal price as the LBO.</t>
+        </is>
+      </c>
+      <c r="J33" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1" s="244">
+      <c r="B34" s="559" t="n">
+        <v>28</v>
+      </c>
+      <c r="C34" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D34" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="E34" s="559" t="inlineStr">
+        <is>
+          <t>Basic / diluted share count</t>
+        </is>
+      </c>
+      <c r="F34" s="559" t="inlineStr">
+        <is>
+          <t>292.312m</t>
+        </is>
+      </c>
+      <c r="G34" s="559" t="inlineStr">
+        <is>
+          <t>Share count for per-share value.</t>
+        </is>
+      </c>
+      <c r="H34" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO shares.</t>
+        </is>
+      </c>
+      <c r="I34" s="559" t="inlineStr">
+        <is>
+          <t>Same 10-Q share count as LBO.</t>
+        </is>
+      </c>
+      <c r="J34" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1" s="244">
+      <c r="B35" s="559" t="n">
+        <v>29</v>
+      </c>
+      <c r="C35" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D35" s="559" t="inlineStr">
+        <is>
+          <t>C55/C56/C57</t>
+        </is>
+      </c>
+      <c r="E35" s="559" t="inlineStr">
+        <is>
+          <t>CAPM inputs</t>
+        </is>
+      </c>
+      <c r="F35" s="559" t="inlineStr">
+        <is>
+          <t>Rf 4.3% / β 1.20 / ERP 5.0%</t>
+        </is>
+      </c>
+      <c r="G35" s="559" t="inlineStr">
+        <is>
+          <t>Building blocks of cost of equity.</t>
+        </is>
+      </c>
+      <c r="H35" s="559" t="inlineStr">
+        <is>
+          <t>Ke = Rf + β×ERP.</t>
+        </is>
+      </c>
+      <c r="I35" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative SaaS CAPM stack for DCF tab (not Yacktman-adjusted).</t>
+        </is>
+      </c>
+      <c r="J35" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1" s="244">
+      <c r="B36" s="559" t="n">
+        <v>30</v>
+      </c>
+      <c r="C36" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D36" s="559" t="inlineStr">
+        <is>
+          <t>C50/C51</t>
+        </is>
+      </c>
+      <c r="E36" s="559" t="inlineStr">
+        <is>
+          <t>Cost of debt / tax</t>
+        </is>
+      </c>
+      <c r="F36" s="559" t="inlineStr">
+        <is>
+          <t>7.0% / 21%</t>
+        </is>
+      </c>
+      <c r="G36" s="559" t="inlineStr">
+        <is>
+          <t>After-tax debt cost inputs.</t>
+        </is>
+      </c>
+      <c r="H36" s="559" t="inlineStr">
+        <is>
+          <t>Rd×(1−t) in WACC.</t>
+        </is>
+      </c>
+      <c r="I36" s="559" t="inlineStr">
+        <is>
+          <t>Rounded financing cost vs new LBO stack.</t>
+        </is>
+      </c>
+      <c r="J36" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" s="244">
+      <c r="B37" s="559" t="n">
+        <v>31</v>
+      </c>
+      <c r="C37" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D37" s="559" t="inlineStr">
+        <is>
+          <t>C53/C58</t>
+        </is>
+      </c>
+      <c r="E37" s="559" t="inlineStr">
+        <is>
+          <t>Capital structure weights</t>
+        </is>
+      </c>
+      <c r="F37" s="559" t="inlineStr">
+        <is>
+          <t>Wd 45% / We 55%</t>
+        </is>
+      </c>
+      <c r="G37" s="559" t="inlineStr">
+        <is>
+          <t>Target weights in WACC.</t>
+        </is>
+      </c>
+      <c r="H37" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy on DCF tab.</t>
+        </is>
+      </c>
+      <c r="I37" s="559" t="inlineStr">
+        <is>
+          <t>Closer to PF leveraged structure than pre-deal equity-heavy weights.</t>
+        </is>
+      </c>
+      <c r="J37" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1" s="244">
+      <c r="B38" s="559" t="n">
+        <v>32</v>
+      </c>
+      <c r="C38" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D38" s="559" t="inlineStr">
+        <is>
+          <t>C9/C59</t>
+        </is>
+      </c>
+      <c r="E38" s="559" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="F38" s="559" t="inlineStr">
+        <is>
+          <t>~8.53%</t>
+        </is>
+      </c>
+      <c r="G38" s="559" t="inlineStr">
+        <is>
+          <t>Discount rate for unlevered FCF.</t>
+        </is>
+      </c>
+      <c r="H38" s="559" t="inlineStr">
+        <is>
+          <t>We×Ke + Wd×Rd×(1−t).</t>
+        </is>
+      </c>
+      <c r="I38" s="559" t="inlineStr">
+        <is>
+          <t>Used for DCF PV math on this tab.</t>
+        </is>
+      </c>
+      <c r="J38" s="559" t="inlineStr">
+        <is>
+          <t>Derived from CAPM + Rd assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="48" customHeight="1" s="244">
+      <c r="B39" s="559" t="n">
+        <v>33</v>
+      </c>
+      <c r="C39" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D39" s="559" t="inlineStr">
+        <is>
+          <t>J37</t>
+        </is>
+      </c>
+      <c r="E39" s="559" t="inlineStr">
+        <is>
+          <t>Exit EBITDA multiple (DCF)</t>
+        </is>
+      </c>
+      <c r="F39" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="G39" s="559" t="inlineStr">
+        <is>
+          <t>Terminal multiple in exit-EBITDA approach.</t>
+        </is>
+      </c>
+      <c r="H39" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO!D17.</t>
+        </is>
+      </c>
+      <c r="I39" s="559" t="inlineStr">
+        <is>
+          <t>Keeps LBO and DCF exit frameworks comparable.</t>
+        </is>
+      </c>
+      <c r="J39" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="48" customHeight="1" s="244">
+      <c r="B40" s="559" t="n">
+        <v>34</v>
+      </c>
+      <c r="C40" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D40" s="559" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="E40" s="559" t="inlineStr">
+        <is>
+          <t>Perpetuity g</t>
+        </is>
+      </c>
+      <c r="F40" s="559" t="inlineStr">
+        <is>
+          <t>0% in template cell (sensitivity uses 2–4%)</t>
+        </is>
+      </c>
+      <c r="G40" s="559" t="inlineStr">
+        <is>
+          <t>Long-term growth in Gordon approach.</t>
+        </is>
+      </c>
+      <c r="H40" s="559" t="inlineStr">
+        <is>
+          <t>Template default; grid varies g.</t>
+        </is>
+      </c>
+      <c r="I40" s="559" t="inlineStr">
+        <is>
+          <t>Football-field sensitivity still shows 2–4% g range.</t>
+        </is>
+      </c>
+      <c r="J40" s="559" t="inlineStr">
+        <is>
+          <t>WSP template convention + MODEL1 note</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1" s="244">
+      <c r="B41" s="559" t="n">
+        <v>35</v>
+      </c>
+      <c r="C41" s="559" t="inlineStr">
+        <is>
+          <t>DCF</t>
+        </is>
+      </c>
+      <c r="D41" s="559" t="inlineStr">
+        <is>
+          <t>C31</t>
+        </is>
+      </c>
+      <c r="E41" s="559" t="inlineStr">
+        <is>
+          <t>Cash-flow timing</t>
+        </is>
+      </c>
+      <c r="F41" s="559" t="inlineStr">
+        <is>
+          <t>Middle of period</t>
+        </is>
+      </c>
+      <c r="G41" s="559" t="inlineStr">
+        <is>
+          <t>Mid-year discounting convention.</t>
+        </is>
+      </c>
+      <c r="H41" s="559" t="inlineStr">
+        <is>
+          <t>Midperiod adjustment factor on DCF tab.</t>
+        </is>
+      </c>
+      <c r="I41" s="559" t="inlineStr">
+        <is>
+          <t>Standard IB mid-year convention for annual FCFs.</t>
+        </is>
+      </c>
+      <c r="J41" s="559" t="inlineStr">
+        <is>
+          <t>WSP template</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1" s="244">
+      <c r="B42" s="559" t="n">
+        <v>36</v>
+      </c>
+      <c r="C42" s="559" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D42" s="559" t="inlineStr">
+        <is>
+          <t>E5/E6</t>
+        </is>
+      </c>
+      <c r="E42" s="559" t="inlineStr">
+        <is>
+          <t>Offer price for dilution</t>
+        </is>
+      </c>
+      <c r="F42" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="G42" s="559" t="inlineStr">
+        <is>
+          <t>Price used in treasury-stock method.</t>
+        </is>
+      </c>
+      <c r="H42" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer.</t>
+        </is>
+      </c>
+      <c r="I42" s="559" t="inlineStr">
+        <is>
+          <t>Aligns diluted-share math with deal price.</t>
+        </is>
+      </c>
+      <c r="J42" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1" s="244">
+      <c r="B43" s="559" t="n">
+        <v>37</v>
+      </c>
+      <c r="C43" s="559" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D43" s="559" t="inlineStr">
+        <is>
+          <t>E7/E14</t>
+        </is>
+      </c>
+      <c r="E43" s="559" t="inlineStr">
+        <is>
+          <t>Basic &amp; net diluted shares</t>
+        </is>
+      </c>
+      <c r="F43" s="559" t="inlineStr">
+        <is>
+          <t>292.312m / 292.312m</t>
+        </is>
+      </c>
+      <c r="G43" s="559" t="inlineStr">
+        <is>
+          <t>Share count used for equity value.</t>
+        </is>
+      </c>
+      <c r="H43" s="559" t="inlineStr">
+        <is>
+          <t>Outstanding shares; options set to 0 in MODEL1.</t>
+        </is>
+      </c>
+      <c r="I43" s="559" t="inlineStr">
+        <is>
+          <t>10-Q share count; detailed options ladder not loaded (net dilutive options = 0).</t>
+        </is>
+      </c>
+      <c r="J43" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1" s="244">
+      <c r="B44" s="559" t="n">
+        <v>38</v>
+      </c>
+      <c r="C44" s="559" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D44" s="559" t="inlineStr">
+        <is>
+          <t>E8:E11</t>
+        </is>
+      </c>
+      <c r="E44" s="559" t="inlineStr">
+        <is>
+          <t>Options / other dilutives</t>
+        </is>
+      </c>
+      <c r="F44" s="559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" s="559" t="inlineStr">
+        <is>
+          <t>Incremental dilutive securities.</t>
+        </is>
+      </c>
+      <c r="H44" s="559" t="inlineStr">
+        <is>
+          <t>Cleared BMC ladder; set to zero pending full award rollforward.</t>
+        </is>
+      </c>
+      <c r="I44" s="559" t="inlineStr">
+        <is>
+          <t>Conservative vs overstating dilution without a current award table.</t>
+        </is>
+      </c>
+      <c r="J44" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1) — update from proxy/10-K award note when refined</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1" s="244">
+      <c r="B45" s="559" t="n">
+        <v>39</v>
+      </c>
+      <c r="C45" s="559" t="inlineStr">
+        <is>
+          <t>52wkHL</t>
+        </is>
+      </c>
+      <c r="D45" s="559" t="inlineStr">
+        <is>
+          <t>E4/E5</t>
+        </is>
+      </c>
+      <c r="E45" s="559" t="inlineStr">
+        <is>
+          <t>52-week high / low</t>
+        </is>
+      </c>
+      <c r="F45" s="559" t="inlineStr">
+        <is>
+          <t>Legacy sample tape (not GTM)</t>
+        </is>
+      </c>
+      <c r="G45" s="559" t="inlineStr">
+        <is>
+          <t>Market range for football-field.</t>
+        </is>
+      </c>
+      <c r="H45" s="559" t="inlineStr">
+        <is>
+          <t>Still WSP BMC sample series in MODEL1.</t>
+        </is>
+      </c>
+      <c r="I45" s="559" t="inlineStr">
+        <is>
+          <t>Not yet replaced with GTM price history; LBO uses spot $4.31 instead.</t>
+        </is>
+      </c>
+      <c r="J45" s="559" t="inlineStr">
+        <is>
+          <t>WSP sample residual — replace with GTM tape in MODEL2+</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1" s="244">
+      <c r="B46" s="559" t="n">
+        <v>40</v>
+      </c>
+      <c r="C46" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D46" s="559" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="E46" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Revenue</t>
+        </is>
+      </c>
+      <c r="F46" s="559" t="inlineStr">
+        <is>
+          <t>$1,249.5m</t>
+        </is>
+      </c>
+      <c r="G46" s="559" t="inlineStr">
+        <is>
+          <t>Annual revenue anchor.</t>
+        </is>
+      </c>
+      <c r="H46" s="559" t="inlineStr">
+        <is>
+          <t>XBRL RevenueFromContractWithCustomerExcludingAssessedTax.</t>
+        </is>
+      </c>
+      <c r="I46" s="559" t="inlineStr">
+        <is>
+          <t>Latest annual 10-K fact.</t>
+        </is>
+      </c>
+      <c r="J46" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1" s="244">
+      <c r="B47" s="559" t="n">
+        <v>41</v>
+      </c>
+      <c r="C47" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D47" s="559" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="E47" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Selling &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="F47" s="559" t="inlineStr">
+        <is>
+          <t>$414.6m</t>
+        </is>
+      </c>
+      <c r="G47" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M expense (the bloat line).</t>
+        </is>
+      </c>
+      <c r="H47" s="559" t="inlineStr">
+        <is>
+          <t>XBRL SellingAndMarketingExpense.</t>
+        </is>
+      </c>
+      <c r="I47" s="559" t="inlineStr">
+        <is>
+          <t>33.2% of FY25 revenue — thesis starting point.</t>
+        </is>
+      </c>
+      <c r="J47" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1" s="244">
+      <c r="B48" s="559" t="n">
+        <v>42</v>
+      </c>
+      <c r="C48" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D48" s="559" t="inlineStr">
+        <is>
+          <t>E10/E13/E20</t>
+        </is>
+      </c>
+      <c r="E48" s="559" t="inlineStr">
+        <is>
+          <t>OpInc / D&amp;A / EBITDA proxy</t>
+        </is>
+      </c>
+      <c r="F48" s="559" t="inlineStr">
+        <is>
+          <t>$225.7 / $88.8 / $314.5m</t>
+        </is>
+      </c>
+      <c r="G48" s="559" t="inlineStr">
+        <is>
+          <t>Operating income, D&amp;A, EBITDA proxy.</t>
+        </is>
+      </c>
+      <c r="H48" s="559" t="inlineStr">
+        <is>
+          <t>OpInc + OtherDepreciationAndAmortization.</t>
+        </is>
+      </c>
+      <c r="I48" s="559" t="inlineStr">
+        <is>
+          <t>Bridges to LBO!D13 LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="J48" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1" s="244">
+      <c r="B49" s="559" t="n">
+        <v>43</v>
+      </c>
+      <c r="C49" s="559" t="inlineStr">
+        <is>
+          <t>ZI_01_10K_Source</t>
+        </is>
+      </c>
+      <c r="D49" s="559" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="E49" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M employees</t>
+        </is>
+      </c>
+      <c r="F49" s="559" t="inlineStr">
+        <is>
+          <t>1,370</t>
+        </is>
+      </c>
+      <c r="G49" s="559" t="inlineStr">
+        <is>
+          <t>Headcount in sales &amp; marketing.</t>
+        </is>
+      </c>
+      <c r="H49" s="559" t="inlineStr">
+        <is>
+          <t>10-K Human Capital disclosure (3,180 total).</t>
+        </is>
+      </c>
+      <c r="I49" s="559" t="inlineStr">
+        <is>
+          <t>Denominator for SDR % assumption.</t>
+        </is>
+      </c>
+      <c r="J49" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1" s="244">
+      <c r="B50" s="559" t="n">
+        <v>44</v>
+      </c>
+      <c r="C50" s="559" t="inlineStr">
+        <is>
+          <t>ZI_02_SM_Isolation</t>
+        </is>
+      </c>
+      <c r="D50" s="559" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="E50" s="559" t="inlineStr">
+        <is>
+          <t>Target mature SaaS S&amp;M % rev</t>
+        </is>
+      </c>
+      <c r="F50" s="559" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G50" s="559" t="inlineStr">
+        <is>
+          <t>Benchmark efficient S&amp;M intensity.</t>
+        </is>
+      </c>
+      <c r="H50" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input vs FY25 33.2%.</t>
+        </is>
+      </c>
+      <c r="I50" s="559" t="inlineStr">
+        <is>
+          <t>Defines “bloat” dollars vs a mature SaaS target.</t>
+        </is>
+      </c>
+      <c r="J50" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1" s="244">
+      <c r="B51" s="559" t="n">
+        <v>45</v>
+      </c>
+      <c r="C51" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D51" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="E51" s="559" t="inlineStr">
+        <is>
+          <t>% of S&amp;M that are outbound SDR/BDR</t>
+        </is>
+      </c>
+      <c r="F51" s="559" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="G51" s="559" t="inlineStr">
+        <is>
+          <t>Share of S&amp;M headcount treated as AI-replaceable SDRs.</t>
+        </is>
+      </c>
+      <c r="H51" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input × 1,370.</t>
+        </is>
+      </c>
+      <c r="I51" s="559" t="inlineStr">
+        <is>
+          <t>10-K does not disclose SDR count — explicit model assumption.</t>
+        </is>
+      </c>
+      <c r="J51" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1" s="244">
+      <c r="B52" s="559" t="n">
+        <v>46</v>
+      </c>
+      <c r="C52" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D52" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="E52" s="559" t="inlineStr">
+        <is>
+          <t>Fully loaded cost / SDR / yr</t>
+        </is>
+      </c>
+      <c r="F52" s="559" t="inlineStr">
+        <is>
+          <t>$155k</t>
+        </is>
+      </c>
+      <c r="G52" s="559" t="inlineStr">
+        <is>
+          <t>Cash cost per outbound SDR.</t>
+        </is>
+      </c>
+      <c r="H52" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input.</t>
+        </is>
+      </c>
+      <c r="I52" s="559" t="inlineStr">
+        <is>
+          <t>Below blended residual S&amp;M $/employee (commissions/ads stay).</t>
+        </is>
+      </c>
+      <c r="J52" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1" s="244">
+      <c r="B53" s="559" t="n">
+        <v>47</v>
+      </c>
+      <c r="C53" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D53" s="559" t="inlineStr">
+        <is>
+          <t>C13/C15</t>
+        </is>
+      </c>
+      <c r="E53" s="559" t="inlineStr">
+        <is>
+          <t>AI seat / oversight cost</t>
+        </is>
+      </c>
+      <c r="F53" s="559" t="inlineStr">
+        <is>
+          <t>$15k per seat; $150k per oversight FTE</t>
+        </is>
+      </c>
+      <c r="G53" s="559" t="inlineStr">
+        <is>
+          <t>Replacement opex for AI agents + humans.</t>
+        </is>
+      </c>
+      <c r="H53" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs; 1 oversight FTE / 20 seats.</t>
+        </is>
+      </c>
+      <c r="I53" s="559" t="inlineStr">
+        <is>
+          <t>Net savings must clear AI + oversight to hit margin target.</t>
+        </is>
+      </c>
+      <c r="J53" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1" s="244">
+      <c r="B54" s="559" t="n">
+        <v>48</v>
+      </c>
+      <c r="C54" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D54" s="559" t="inlineStr">
+        <is>
+          <t>C21:E21</t>
+        </is>
+      </c>
+      <c r="E54" s="559" t="inlineStr">
+        <is>
+          <t>Cumulative % SDRs replaced</t>
+        </is>
+      </c>
+      <c r="F54" s="559" t="inlineStr">
+        <is>
+          <t>45% / 80% / 95% (2026–28)</t>
+        </is>
+      </c>
+      <c r="G54" s="559" t="inlineStr">
+        <is>
+          <t>Headcount reduction schedule.</t>
+        </is>
+      </c>
+      <c r="H54" s="559" t="inlineStr">
+        <is>
+          <t>Yellow cumulative exit fractions.</t>
+        </is>
+      </c>
+      <c r="I54" s="559" t="inlineStr">
+        <is>
+          <t>Phased cut to avoid one-year cliff risk.</t>
+        </is>
+      </c>
+      <c r="J54" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1" s="244">
+      <c r="B55" s="559" t="n">
+        <v>49</v>
+      </c>
+      <c r="C55" s="559" t="inlineStr">
+        <is>
+          <t>ZI_03_Headcount_AI</t>
+        </is>
+      </c>
+      <c r="D55" s="559" t="inlineStr">
+        <is>
+          <t>C16/C17</t>
+        </is>
+      </c>
+      <c r="E55" s="559" t="inlineStr">
+        <is>
+          <t>Severance / AI build</t>
+        </is>
+      </c>
+      <c r="F55" s="559" t="inlineStr">
+        <is>
+          <t>$25k per SDR; $8m Y1 build</t>
+        </is>
+      </c>
+      <c r="G55" s="559" t="inlineStr">
+        <is>
+          <t>One-time costs.</t>
+        </is>
+      </c>
+      <c r="H55" s="559" t="inlineStr">
+        <is>
+          <t>Yellow inputs in P&amp;L impact.</t>
+        </is>
+      </c>
+      <c r="I55" s="559" t="inlineStr">
+        <is>
+          <t>Hits in-year EBITDA but excluded from run-rate bps.</t>
+        </is>
+      </c>
+      <c r="J55" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1" s="244">
+      <c r="B56" s="559" t="n">
+        <v>50</v>
+      </c>
+      <c r="C56" s="559" t="inlineStr">
+        <is>
+          <t>ZI_04_EBITDA_Bridge</t>
+        </is>
+      </c>
+      <c r="D56" s="559" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="E56" s="559" t="inlineStr">
+        <is>
+          <t>Target margin expansion</t>
+        </is>
+      </c>
+      <c r="F56" s="559" t="inlineStr">
+        <is>
+          <t>500 bps</t>
+        </is>
+      </c>
+      <c r="G56" s="559" t="inlineStr">
+        <is>
+          <t>Minimum success hurdle for the AI program.</t>
+        </is>
+      </c>
+      <c r="H56" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input; YES/NO vs run-rate bps.</t>
+        </is>
+      </c>
+      <c r="I56" s="559" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> equates to ~$62.5m EBITDA on $1,249.5m revenue.</t>
+        </is>
+      </c>
+      <c r="J56" s="559" t="inlineStr">
+        <is>
+          <t>User thesis requirement</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1" s="244">
+      <c r="B57" s="559" t="n">
+        <v>51</v>
+      </c>
+      <c r="C57" s="559" t="inlineStr">
+        <is>
+          <t>ZI_05_Sensitivity</t>
+        </is>
+      </c>
+      <c r="D57" s="559" t="inlineStr">
+        <is>
+          <t>B12:H17</t>
+        </is>
+      </c>
+      <c r="E57" s="559" t="inlineStr">
+        <is>
+          <t>Sensitivity grid</t>
+        </is>
+      </c>
+      <c r="F57" s="559" t="inlineStr">
+        <is>
+          <t>Replace-% × AI $/seat → bps</t>
+        </is>
+      </c>
+      <c r="G57" s="559" t="inlineStr">
+        <is>
+          <t>Y3 run-rate bps under alternate AI costs / cut depths.</t>
+        </is>
+      </c>
+      <c r="H57" s="559" t="inlineStr">
+        <is>
+          <t>Algebra on SDR0 &amp; unit costs.</t>
+        </is>
+      </c>
+      <c r="I57" s="559" t="inlineStr">
+        <is>
+          <t>Shows what it takes to stay above 500 bps if AI is more expensive.</t>
+        </is>
+      </c>
+      <c r="J57" s="559" t="inlineStr">
+        <is>
+          <t>Derived from ZI_03 inputs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B6:J57"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId17"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="48" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12" customWidth="1" style="244" min="3" max="3"/>
+    <col width="12" customWidth="1" style="244" min="4" max="4"/>
+    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Headcount reduction: outbound SDRs → AI agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="547" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M employees (10-K)</t>
+        </is>
+      </c>
+      <c r="C5" s="549">
+        <f>'ZI_01_10K_Source'!E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>% of S&amp;M that are outbound SDR/BDR</t>
+        </is>
+      </c>
+      <c r="C6" s="551" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="542" t="inlineStr">
+        <is>
+          <t>Outbound SDR headcount (Y0)</t>
+        </is>
+      </c>
+      <c r="C7" s="549">
+        <f>ROUND(C5*C6,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="542" t="inlineStr">
+        <is>
+          <t>Fully loaded cost / SDR / yr ($000s)</t>
+        </is>
+      </c>
+      <c r="C8" s="556" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="542" t="inlineStr">
+        <is>
+          <t>Addressable SDR cost pool ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="557">
+        <f>C7*C8/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="547" t="inlineStr">
+        <is>
+          <t>AI AGENT UNIT ECONOMICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="542" t="inlineStr">
+        <is>
+          <t>AI agent seats per SDR replaced</t>
+        </is>
+      </c>
+      <c r="C12" s="552" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="542" t="inlineStr">
+        <is>
+          <t>AI platform + compute / seat / yr ($000s)</t>
+        </is>
+      </c>
+      <c r="C13" s="556" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="542" t="inlineStr">
+        <is>
+          <t>Human oversight FTE per 20 AI seats</t>
+        </is>
+      </c>
+      <c r="C14" s="552" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="542" t="inlineStr">
+        <is>
+          <t>Oversight fully loaded / FTE / yr ($000s)</t>
+        </is>
+      </c>
+      <c r="C15" s="556" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="542" t="inlineStr">
+        <is>
+          <t>One-time severance / SDR ($000s)</t>
+        </is>
+      </c>
+      <c r="C16" s="556" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="542" t="inlineStr">
+        <is>
+          <t>One-time AI build / integration ($m) in Y1</t>
+        </is>
+      </c>
+      <c r="C17" s="556" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="547" t="inlineStr">
+        <is>
+          <t>REDUCTION SCHEDULE (% of Y0 SDRs exited by year-end)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="542" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C20" s="541" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="541" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E20" s="541" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="542" t="inlineStr">
+        <is>
+          <t>Cumulative % SDRs replaced</t>
+        </is>
+      </c>
+      <c r="C21" s="553" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D21" s="553" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E21" s="553" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="542" t="inlineStr">
+        <is>
+          <t>SDRs remaining</t>
+        </is>
+      </c>
+      <c r="C22" s="549">
+        <f>ROUND($C$7*(1-C21),0)</f>
+        <v/>
+      </c>
+      <c r="D22" s="549">
+        <f>ROUND($C$7*(1-D21),0)</f>
+        <v/>
+      </c>
+      <c r="E22" s="549">
+        <f>ROUND($C$7*(1-E21),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="542" t="inlineStr">
+        <is>
+          <t>SDRs exited (cumulative)</t>
+        </is>
+      </c>
+      <c r="C23" s="549">
+        <f>$C$7-C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="549">
+        <f>$C$7-D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="549">
+        <f>$C$7-E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="542" t="inlineStr">
+        <is>
+          <t>SDRs exited this year</t>
+        </is>
+      </c>
+      <c r="C24" s="549">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="549">
+        <f>D23-C23</f>
+        <v/>
+      </c>
+      <c r="E24" s="549">
+        <f>E23-D23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="542" t="inlineStr">
+        <is>
+          <t>Avg SDRs during year</t>
+        </is>
+      </c>
+      <c r="C25" s="557">
+        <f>($C$7+C22)/2</f>
+        <v/>
+      </c>
+      <c r="D25" s="557">
+        <f>(C22+D22)/2</f>
+        <v/>
+      </c>
+      <c r="E25" s="557">
+        <f>(D22+E22)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="547" t="inlineStr">
+        <is>
+          <t>AI SEATS &amp; OVERSIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="542" t="inlineStr">
+        <is>
+          <t>AI seats (cum.)</t>
+        </is>
+      </c>
+      <c r="C28" s="557">
+        <f>C23*$C$12</f>
+        <v/>
+      </c>
+      <c r="D28" s="557">
+        <f>D23*$C$12</f>
+        <v/>
+      </c>
+      <c r="E28" s="557">
+        <f>E23*$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="542" t="inlineStr">
+        <is>
+          <t>Oversight FTEs</t>
+        </is>
+      </c>
+      <c r="C29" s="549">
+        <f>ROUNDUP(C28/(20/$C$14),0)</f>
+        <v/>
+      </c>
+      <c r="D29" s="549">
+        <f>ROUNDUP(D28/(20/$C$14),0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="549">
+        <f>ROUNDUP(E28/(20/$C$14),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="547" t="inlineStr">
+        <is>
+          <t>P&amp;L IMPACT ($m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="542" t="inlineStr">
+        <is>
+          <t>SDR cash cost (avg HC × cost)</t>
+        </is>
+      </c>
+      <c r="C32" s="557">
+        <f>C25*$C$8/1000</f>
+        <v/>
+      </c>
+      <c r="D32" s="557">
+        <f>D25*$C$8/1000</f>
+        <v/>
+      </c>
+      <c r="E32" s="557">
+        <f>E25*$C$8/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="542" t="inlineStr">
+        <is>
+          <t>Baseline SDR cost if no program</t>
+        </is>
+      </c>
+      <c r="C33" s="557">
+        <f>$C$9</f>
+        <v/>
+      </c>
+      <c r="D33" s="557">
+        <f>$C$9</f>
+        <v/>
+      </c>
+      <c r="E33" s="557">
+        <f>$C$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="542" t="inlineStr">
+        <is>
+          <t>Gross SDR savings vs baseline</t>
+        </is>
+      </c>
+      <c r="C34" s="557">
+        <f>C33-C32</f>
+        <v/>
+      </c>
+      <c r="D34" s="557">
+        <f>D33-D32</f>
+        <v/>
+      </c>
+      <c r="E34" s="557">
+        <f>E33-E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="542" t="inlineStr">
+        <is>
+          <t>AI seat opex</t>
+        </is>
+      </c>
+      <c r="C35" s="557">
+        <f>C28*$C$13/1000</f>
+        <v/>
+      </c>
+      <c r="D35" s="557">
+        <f>D28*$C$13/1000</f>
+        <v/>
+      </c>
+      <c r="E35" s="557">
+        <f>E28*$C$13/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="542" t="inlineStr">
+        <is>
+          <t>Oversight opex</t>
+        </is>
+      </c>
+      <c r="C36" s="557">
+        <f>C29*$C$15/1000</f>
+        <v/>
+      </c>
+      <c r="D36" s="557">
+        <f>D29*$C$15/1000</f>
+        <v/>
+      </c>
+      <c r="E36" s="557">
+        <f>E29*$C$15/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="542" t="inlineStr">
+        <is>
+          <t>Severance (this year's exits)</t>
+        </is>
+      </c>
+      <c r="C37" s="557">
+        <f>C24*$C$16/1000</f>
+        <v/>
+      </c>
+      <c r="D37" s="557">
+        <f>D24*$C$16/1000</f>
+        <v/>
+      </c>
+      <c r="E37" s="557">
+        <f>E24*$C$16/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="542" t="inlineStr">
+        <is>
+          <t>AI build (Y1 only)</t>
+        </is>
+      </c>
+      <c r="C38" s="557">
+        <f>$C$17</f>
+        <v/>
+      </c>
+      <c r="D38" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="556" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="544" t="inlineStr">
+        <is>
+          <t>Net EBITDA benefit (in-year, after one-time)</t>
+        </is>
+      </c>
+      <c r="C39" s="557">
+        <f>C34-C35-C36-C37-C38</f>
+        <v/>
+      </c>
+      <c r="D39" s="557">
+        <f>D34-D35-D36-D37-D38</f>
+        <v/>
+      </c>
+      <c r="E39" s="557">
+        <f>E34-E35-E36-E37-E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="544" t="inlineStr">
+        <is>
+          <t>Year-end run-rate benefit (ex one-time)</t>
+        </is>
+      </c>
+      <c r="C40" s="557">
+        <f>(C23*$C$8/1000)-(C28*$C$13/1000)-(C29*$C$15/1000)</f>
+        <v/>
+      </c>
+      <c r="D40" s="557">
+        <f>(D23*$C$8/1000)-(D28*$C$13/1000)-(D29*$C$15/1000)</f>
+        <v/>
+      </c>
+      <c r="E40" s="557">
+        <f>(E23*$C$8/1000)-(E28*$C$13/1000)-(E29*$C$15/1000)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="55" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12" customWidth="1" style="244" min="3" max="3"/>
+    <col width="12" customWidth="1" style="244" min="4" max="4"/>
+    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>EBITDA margin expansion bridge (target ≥500 bps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="542" t="inlineStr">
+        <is>
+          <t>FY2025 baseline Revenue ($m)</t>
+        </is>
+      </c>
+      <c r="C4" s="557">
+        <f>'ZI_01_10K_Source'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>FY2025 GAAP EBITDA proxy ($m)</t>
+        </is>
+      </c>
+      <c r="C5" s="557">
+        <f>'ZI_01_10K_Source'!E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>Baseline EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C6" s="546">
+        <f>C5/C4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="542" t="inlineStr">
+        <is>
+          <t>Target margin expansion (bps)</t>
+        </is>
+      </c>
+      <c r="C7" s="548" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="542" t="inlineStr">
+        <is>
+          <t>Required incremental EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="C8" s="557">
+        <f>C4*C7/10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="542" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C10" s="541" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="541" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E10" s="541" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="542" t="inlineStr">
+        <is>
+          <t>Revenue (flat case for margin math)</t>
+        </is>
+      </c>
+      <c r="C11" s="557">
+        <f>$C$4</f>
+        <v/>
+      </c>
+      <c r="D11" s="557">
+        <f>$C$4</f>
+        <v/>
+      </c>
+      <c r="E11" s="557">
+        <f>$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="542" t="inlineStr">
+        <is>
+          <t>Net EBITDA benefit from program</t>
+        </is>
+      </c>
+      <c r="C12" s="557">
+        <f>'ZI_03_Headcount_AI'!C39</f>
+        <v/>
+      </c>
+      <c r="D12" s="557">
+        <f>'ZI_03_Headcount_AI'!D39</f>
+        <v/>
+      </c>
+      <c r="E12" s="557">
+        <f>'ZI_03_Headcount_AI'!E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="542" t="inlineStr">
+        <is>
+          <t>Run-rate benefit (ex one-time)</t>
+        </is>
+      </c>
+      <c r="C13" s="557">
+        <f>'ZI_03_Headcount_AI'!C40</f>
+        <v/>
+      </c>
+      <c r="D13" s="557">
+        <f>'ZI_03_Headcount_AI'!D40</f>
+        <v/>
+      </c>
+      <c r="E13" s="557">
+        <f>'ZI_03_Headcount_AI'!E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="542" t="inlineStr">
+        <is>
+          <t>Pro forma EBITDA</t>
+        </is>
+      </c>
+      <c r="C14" s="557">
+        <f>$C$5+C12</f>
+        <v/>
+      </c>
+      <c r="D14" s="557">
+        <f>$C$5+D12</f>
+        <v/>
+      </c>
+      <c r="E14" s="557">
+        <f>$C$5+E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="542" t="inlineStr">
+        <is>
+          <t>Pro forma EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C15" s="546">
+        <f>C14/C11</f>
+        <v/>
+      </c>
+      <c r="D15" s="546">
+        <f>D14/D11</f>
+        <v/>
+      </c>
+      <c r="E15" s="546">
+        <f>E14/E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="544" t="inlineStr">
+        <is>
+          <t>Margin expansion (bps)</t>
+        </is>
+      </c>
+      <c r="C16" s="557">
+        <f>(C15-$C$6)*10000</f>
+        <v/>
+      </c>
+      <c r="D16" s="557">
+        <f>(D15-$C$6)*10000</f>
+        <v/>
+      </c>
+      <c r="E16" s="557">
+        <f>(E15-$C$6)*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="544" t="inlineStr">
+        <is>
+          <t>Run-rate expansion (bps)</t>
+        </is>
+      </c>
+      <c r="C17" s="557">
+        <f>(C13/$C$4)*10000</f>
+        <v/>
+      </c>
+      <c r="D17" s="557">
+        <f>(D13/$C$4)*10000</f>
+        <v/>
+      </c>
+      <c r="E17" s="557">
+        <f>(E13/$C$4)*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="542" t="inlineStr">
+        <is>
+          <t>Hits ≥500 bps run-rate?</t>
+        </is>
+      </c>
+      <c r="C18" s="554">
+        <f>IF(C17&gt;=$C$7,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="D18" s="554">
+        <f>IF(D17&gt;=$C$7,"YES","NO")</f>
+        <v/>
+      </c>
+      <c r="E18" s="554">
+        <f>IF(E17&gt;=$C$7,"YES","NO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="542" t="inlineStr">
+        <is>
+          <t>S&amp;M % revenue bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="542" t="inlineStr">
+        <is>
+          <t>Baseline S&amp;M %</t>
+        </is>
+      </c>
+      <c r="C21" s="546">
+        <f>'ZI_02_SM_Isolation'!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="542" t="inlineStr">
+        <is>
+          <t>PF S&amp;M $ (baseline − SDR save + AI/oversight)</t>
+        </is>
+      </c>
+      <c r="C22" s="557">
+        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!C34+'ZI_03_Headcount_AI'!C35+'ZI_03_Headcount_AI'!C36</f>
+        <v/>
+      </c>
+      <c r="D22" s="557">
+        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!D34+'ZI_03_Headcount_AI'!D35+'ZI_03_Headcount_AI'!D36</f>
+        <v/>
+      </c>
+      <c r="E22" s="557">
+        <f>'ZI_01_10K_Source'!E6-'ZI_03_Headcount_AI'!E34+'ZI_03_Headcount_AI'!E35+'ZI_03_Headcount_AI'!E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="542" t="inlineStr">
+        <is>
+          <t>PF S&amp;M % revenue</t>
+        </is>
+      </c>
+      <c r="C23" s="546">
+        <f>C22/$C$4</f>
+        <v/>
+      </c>
+      <c r="D23" s="546">
+        <f>D22/$C$4</f>
+        <v/>
+      </c>
+      <c r="E23" s="546">
+        <f>E22/$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yellow cells on 03_Headcount_AI drive the bridge. Base case sized to clear 500 bps by Y3 run-rate: 40% of S&amp;M = outbound SDRs; 95% replaced; $155k/SDR vs $15k AI seat + oversight. 500 bps on $1,249.5m revenue needs ~$62.5m run-rate EBITDA.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="18" customWidth="1" style="244" min="2" max="2"/>
+    <col width="10" customWidth="1" style="244" min="3" max="3"/>
+    <col width="10" customWidth="1" style="244" min="4" max="4"/>
+    <col width="10" customWidth="1" style="244" min="5" max="5"/>
+    <col width="10" customWidth="1" style="244" min="6" max="6"/>
+    <col width="10" customWidth="1" style="244" min="7" max="7"/>
+    <col width="10" customWidth="1" style="244" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Sensitivity — Y3 run-rate margin expansion (bps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rows = cumulative % SDRs replaced; Cols = AI $/seat-yr ($000s). Other inputs from 03_Headcount_AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="542" t="inlineStr">
+        <is>
+          <t>SDR0</t>
+        </is>
+      </c>
+      <c r="C5" s="549">
+        <f>'ZI_03_Headcount_AI'!C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="542" t="inlineStr">
+        <is>
+          <t>SDR cost $k</t>
+        </is>
+      </c>
+      <c r="C6" s="557">
+        <f>'ZI_03_Headcount_AI'!C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="542" t="inlineStr">
+        <is>
+          <t>Seats/SDR</t>
+        </is>
+      </c>
+      <c r="C7" s="555">
+        <f>'ZI_03_Headcount_AI'!C12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="542" t="inlineStr">
+        <is>
+          <t>Oversight $k</t>
+        </is>
+      </c>
+      <c r="C8" s="557">
+        <f>'ZI_03_Headcount_AI'!C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="542" t="inlineStr">
+        <is>
+          <t>Revenue $m</t>
+        </is>
+      </c>
+      <c r="C9" s="557">
+        <f>'ZI_01_10K_Source'!E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>bps \ AI $k</t>
+        </is>
+      </c>
+      <c r="C11" s="548" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="548" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" s="548" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="548" t="n">
+        <v>24</v>
+      </c>
+      <c r="G11" s="548" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="548" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="553" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*8/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*12/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*18/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*24/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*30/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H12" s="549">
+        <f>(($C$5*0.5)*$C$6/1000-($C$5*0.5)*$C$7*40/1000-ROUNDUP(($C$5*0.5)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="553" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*8/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*12/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*18/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*24/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*30/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H13" s="549">
+        <f>(($C$5*0.6)*$C$6/1000-($C$5*0.6)*$C$7*40/1000-ROUNDUP(($C$5*0.6)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="553" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*8/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*12/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*18/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*24/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*30/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H14" s="549">
+        <f>(($C$5*0.7)*$C$6/1000-($C$5*0.7)*$C$7*40/1000-ROUNDUP(($C$5*0.7)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="553" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*8/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*12/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*18/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*24/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*30/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H15" s="549">
+        <f>(($C$5*0.8)*$C$6/1000-($C$5*0.8)*$C$7*40/1000-ROUNDUP(($C$5*0.8)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="553" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*8/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*12/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*18/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*24/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*30/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H16" s="549">
+        <f>(($C$5*0.9)*$C$6/1000-($C$5*0.9)*$C$7*40/1000-ROUNDUP(($C$5*0.9)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="553" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*8/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="D17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*12/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="E17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*18/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="F17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*24/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="G17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*30/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+      <c r="H17" s="549">
+        <f>(($C$5*1.0)*$C$6/1000-($C$5*1.0)*$C$7*40/1000-ROUNDUP(($C$5*1.0)*$C$7/20,0)*$C$8/1000)/$C$9*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="542" t="inlineStr">
+        <is>
+          <t>Base case Y3 run-rate bps (from bridge)</t>
+        </is>
+      </c>
+      <c r="C20" s="557">
+        <f>'ZI_04_EBITDA_Bridge'!E17</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — Coversheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `Coversheet` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Model identity</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — ZoomInfo (GTM)</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Name of this LBO case.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Set on Coversheet and LBO!B2.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Separates ZoomInfo LBOMODEL1 from the blank WSP BMC sample.</t>
+        </is>
+      </c>
+      <c r="I6" s="560" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/vengeanceaiUSC_LBOMODEL1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$ millions except per share / rates / multiples</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Unit convention for the workbook.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Stated on LBO!B3 / DCF!B3.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Matches WSP template convention and SEC $ presentation scaled to millions.</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — LBO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `LBO` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>D6/D7</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Company / ticker</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>ZoomInfo Technologies Inc. / GTM</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Target company identity.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded inputs on LBO general inputs.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Public GTM (legacy ZI) is the LBOMODEL1 case company.</t>
+        </is>
+      </c>
+      <c r="I6" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$4.31</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Spot equity price used for premium math.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D8 market input.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Latest available GTM print used when MODEL1 was built (~2026-08-12).</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>Price date</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>As-of date for the spot price.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D9.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Timestamps the market input for auditability.</t>
+        </is>
+      </c>
+      <c r="I8" s="560" t="inlineStr">
+        <is>
+          <t>https://finance.yahoo.com/quote/GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>H21</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>Acquisition premium</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>Premium of offer price over spot.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh = D8×(1+premium).</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Standard illustrative take-private premium; editable deal assumption.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>H20</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>Offer price / share</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>Implied takeout price per share.</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>D8 × 1.25.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>Drives equity purchase price in Uses.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption + market price</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="559" t="inlineStr">
+        <is>
+          <t>H18</t>
+        </is>
+      </c>
+      <c r="D11" s="559" t="inlineStr">
+        <is>
+          <t>Diluted shares (millions)</t>
+        </is>
+      </c>
+      <c r="E11" s="559" t="inlineStr">
+        <is>
+          <t>292.312</t>
+        </is>
+      </c>
+      <c r="F11" s="559" t="inlineStr">
+        <is>
+          <t>Share count for equity value.</t>
+        </is>
+      </c>
+      <c r="G11" s="559" t="inlineStr">
+        <is>
+          <t>From latest shares outstanding.</t>
+        </is>
+      </c>
+      <c r="H11" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30 common shares outstanding used as diluted proxy (options ladder not fully modeled).</t>
+        </is>
+      </c>
+      <c r="I11" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="559" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="D12" s="559" t="inlineStr">
+        <is>
+          <t>Equity purchase price</t>
+        </is>
+      </c>
+      <c r="E12" s="559" t="inlineStr">
+        <is>
+          <t>$1,574.8m</t>
+        </is>
+      </c>
+      <c r="F12" s="559" t="inlineStr">
+        <is>
+          <t>Cash to buy equity.</t>
+        </is>
+      </c>
+      <c r="G12" s="559" t="inlineStr">
+        <is>
+          <t>Offer/sh × shares.</t>
+        </is>
+      </c>
+      <c r="H12" s="559" t="inlineStr">
+        <is>
+          <t>Primary Use of funds line.</t>
+        </is>
+      </c>
+      <c r="I12" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="559" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="559" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="D13" s="559" t="inlineStr">
+        <is>
+          <t>LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="E13" s="559" t="inlineStr">
+        <is>
+          <t>$314.5m</t>
+        </is>
+      </c>
+      <c r="F13" s="559" t="inlineStr">
+        <is>
+          <t>Entry EBITDA for leverage / multiple math.</t>
+        </is>
+      </c>
+      <c r="G13" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 OpInc $225.7m + D&amp;A $88.8m.</t>
+        </is>
+      </c>
+      <c r="H13" s="559" t="inlineStr">
+        <is>
+          <t>GAAP EBITDA proxy from latest annual 10-K (not adjusted EBITDA).</t>
+        </is>
+      </c>
+      <c r="I13" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="559" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="559" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="D14" s="559" t="inlineStr">
+        <is>
+          <t>Gross debt</t>
+        </is>
+      </c>
+      <c r="E14" s="559" t="inlineStr">
+        <is>
+          <t>−$1,269.9m</t>
+        </is>
+      </c>
+      <c r="F14" s="559" t="inlineStr">
+        <is>
+          <t>Debt refinanced at close (entered as negative in template).</t>
+        </is>
+      </c>
+      <c r="G14" s="559" t="inlineStr">
+        <is>
+          <t>LT debt + current maturities.</t>
+        </is>
+      </c>
+      <c r="H14" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30: LongTermDebt + LongTermDebtCurrent.</t>
+        </is>
+      </c>
+      <c r="I14" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="48" customHeight="1" s="244">
+      <c r="B15" s="559" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="559" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="D15" s="559" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E15" s="559" t="inlineStr">
+        <is>
+          <t>$150.1m</t>
+        </is>
+      </c>
+      <c r="F15" s="559" t="inlineStr">
+        <is>
+          <t>Cash available at entry.</t>
+        </is>
+      </c>
+      <c r="G15" s="559" t="inlineStr">
+        <is>
+          <t>Cash &amp; equivalents + short-term investments.</t>
+        </is>
+      </c>
+      <c r="H15" s="559" t="inlineStr">
+        <is>
+          <t>10-Q 2026-06-30.</t>
+        </is>
+      </c>
+      <c r="I15" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1" s="244">
+      <c r="B16" s="559" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" s="559" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="D16" s="559" t="inlineStr">
+        <is>
+          <t>Minimum cash</t>
+        </is>
+      </c>
+      <c r="E16" s="559" t="inlineStr">
+        <is>
+          <t>$50.0m</t>
+        </is>
+      </c>
+      <c r="F16" s="559" t="inlineStr">
+        <is>
+          <t>Cash retained for ops; excess used as a Source.</t>
+        </is>
+      </c>
+      <c r="G16" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy input.</t>
+        </is>
+      </c>
+      <c r="H16" s="559" t="inlineStr">
+        <is>
+          <t>Leaves liquidity post-close; excess cash = 150.1 − 50 = 100.1.</t>
+        </is>
+      </c>
+      <c r="I16" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1" s="244">
+      <c r="B17" s="559" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="559" t="inlineStr">
+        <is>
+          <t>I11</t>
+        </is>
+      </c>
+      <c r="D17" s="559" t="inlineStr">
+        <is>
+          <t>Entry EV / LTM EBITDA</t>
+        </is>
+      </c>
+      <c r="E17" s="559" t="inlineStr">
+        <is>
+          <t>8.57x</t>
+        </is>
+      </c>
+      <c r="F17" s="559" t="inlineStr">
+        <is>
+          <t>Implied entry multiple.</t>
+        </is>
+      </c>
+      <c r="G17" s="559" t="inlineStr">
+        <is>
+          <t>(Equity buy + debt − cash) / EBITDA.</t>
+        </is>
+      </c>
+      <c r="H17" s="559" t="inlineStr">
+        <is>
+          <t>Output of offer + net debt vs LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="I17" s="559" t="inlineStr">
+        <is>
+          <t>Derived from SEC + market inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1" s="244">
+      <c r="B18" s="559" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="559" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="D18" s="559" t="inlineStr">
+        <is>
+          <t>Exit EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="E18" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="F18" s="559" t="inlineStr">
+        <is>
+          <t>Exit multiple in hold-year 5.</t>
+        </is>
+      </c>
+      <c r="G18" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17 policy input.</t>
+        </is>
+      </c>
+      <c r="H18" s="559" t="inlineStr">
+        <is>
+          <t>Near entry; assumes modest multiple compression vs entry 8.57x.</t>
+        </is>
+      </c>
+      <c r="I18" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1" s="244">
+      <c r="B19" s="559" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="559" t="inlineStr">
+        <is>
+          <t>C29/D29</t>
+        </is>
+      </c>
+      <c r="D19" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan A</t>
+        </is>
+      </c>
+      <c r="E19" s="559" t="inlineStr">
+        <is>
+          <t>2.5x / $786.2m</t>
+        </is>
+      </c>
+      <c r="F19" s="559" t="inlineStr">
+        <is>
+          <t>New TLA quantum.</t>
+        </is>
+      </c>
+      <c r="G19" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="H19" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="I19" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1" s="244">
+      <c r="B20" s="559" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="559" t="inlineStr">
+        <is>
+          <t>C30/D30</t>
+        </is>
+      </c>
+      <c r="D20" s="559" t="inlineStr">
+        <is>
+          <t>Term Loan B</t>
+        </is>
+      </c>
+      <c r="E20" s="559" t="inlineStr">
+        <is>
+          <t>1.5x / $471.8m</t>
+        </is>
+      </c>
+      <c r="F20" s="559" t="inlineStr">
+        <is>
+          <t>New TLB quantum.</t>
+        </is>
+      </c>
+      <c r="G20" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="H20" s="559" t="inlineStr">
+        <is>
+          <t>Part of 5.0x new-money debt stack.</t>
+        </is>
+      </c>
+      <c r="I20" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1" s="244">
+      <c r="B21" s="559" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="559" t="inlineStr">
+        <is>
+          <t>C31/D31</t>
+        </is>
+      </c>
+      <c r="D21" s="559" t="inlineStr">
+        <is>
+          <t>Senior Notes</t>
+        </is>
+      </c>
+      <c r="E21" s="559" t="inlineStr">
+        <is>
+          <t>1.0x / $314.5m</t>
+        </is>
+      </c>
+      <c r="F21" s="559" t="inlineStr">
+        <is>
+          <t>New senior notes quantum.</t>
+        </is>
+      </c>
+      <c r="G21" s="559" t="inlineStr">
+        <is>
+          <t>EBITDA × turns.</t>
+        </is>
+      </c>
+      <c r="H21" s="559" t="inlineStr">
+        <is>
+          <t>Completes 5.0x new debt with TLA+TLB.</t>
+        </is>
+      </c>
+      <c r="I21" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1" s="244">
+      <c r="B22" s="559" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="559" t="inlineStr">
+        <is>
+          <t>D35</t>
+        </is>
+      </c>
+      <c r="D22" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor equity</t>
+        </is>
+      </c>
+      <c r="E22" s="559" t="inlineStr">
+        <is>
+          <t>$1,203.6m</t>
+        </is>
+      </c>
+      <c r="F22" s="559" t="inlineStr">
+        <is>
+          <t>Equity check (Sources plug).</t>
+        </is>
+      </c>
+      <c r="G22" s="559" t="inlineStr">
+        <is>
+          <t>Total Uses − excess cash − new debt.</t>
+        </is>
+      </c>
+      <c r="H22" s="559" t="inlineStr">
+        <is>
+          <t>Balancing figure so Sources = Uses ($2,876.2m).</t>
+        </is>
+      </c>
+      <c r="I22" s="559" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="48" customHeight="1" s="244">
+      <c r="B23" s="559" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="559" t="inlineStr">
+        <is>
+          <t>G36</t>
+        </is>
+      </c>
+      <c r="D23" s="559" t="inlineStr">
+        <is>
+          <t>Transaction fee %</t>
+        </is>
+      </c>
+      <c r="E23" s="559" t="inlineStr">
+        <is>
+          <t>2% of equity value</t>
+        </is>
+      </c>
+      <c r="F23" s="559" t="inlineStr">
+        <is>
+          <t>M&amp;A / financing fee assumption.</t>
+        </is>
+      </c>
+      <c r="G23" s="559" t="inlineStr">
+        <is>
+          <t>Fees $ = 2% × equity purchase.</t>
+        </is>
+      </c>
+      <c r="H23" s="559" t="inlineStr">
+        <is>
+          <t>Simple fee load for Uses; financing fee dollars also shown in fee block.</t>
+        </is>
+      </c>
+      <c r="I23" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1" s="244">
+      <c r="B24" s="559" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="559" t="inlineStr">
+        <is>
+          <t>F65:J65</t>
+        </is>
+      </c>
+      <c r="D24" s="559" t="inlineStr">
+        <is>
+          <t>Revenue growth (FY26–30)</t>
+        </is>
+      </c>
+      <c r="E24" s="559" t="inlineStr">
+        <is>
+          <t>4% / 5% / 5% / 4% / 3%</t>
+        </is>
+      </c>
+      <c r="F24" s="559" t="inlineStr">
+        <is>
+          <t>YoY revenue growth in forecast.</t>
+        </is>
+      </c>
+      <c r="G24" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded on growth row.</t>
+        </is>
+      </c>
+      <c r="H24" s="559" t="inlineStr">
+        <is>
+          <t>Modest recovery vs FY24 dip; not a hyper-growth case.</t>
+        </is>
+      </c>
+      <c r="I24" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1" s="244">
+      <c r="B25" s="559" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="559" t="inlineStr">
+        <is>
+          <t>E66/F66</t>
+        </is>
+      </c>
+      <c r="D25" s="559" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="E25" s="559" t="inlineStr">
+        <is>
+          <t>FY25 82.35% → Fcst 82.85%</t>
+        </is>
+      </c>
+      <c r="F25" s="559" t="inlineStr">
+        <is>
+          <t>Gross profit % of sales.</t>
+        </is>
+      </c>
+      <c r="G25" s="559" t="inlineStr">
+        <is>
+          <t>From FY25 COGS implied by 10-K; slight +50 bps in forecast.</t>
+        </is>
+      </c>
+      <c r="H25" s="559" t="inlineStr">
+        <is>
+          <t>Software gross margin structure from SEC P&amp;L.</t>
+        </is>
+      </c>
+      <c r="I25" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1" s="244">
+      <c r="B26" s="559" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="559" t="inlineStr">
+        <is>
+          <t>E67/F67</t>
+        </is>
+      </c>
+      <c r="D26" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D margin</t>
+        </is>
+      </c>
+      <c r="E26" s="559" t="inlineStr">
+        <is>
+          <t>14.57% flat in forecast</t>
+        </is>
+      </c>
+      <c r="F26" s="559" t="inlineStr">
+        <is>
+          <t>R&amp;D % of sales.</t>
+        </is>
+      </c>
+      <c r="G26" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 R&amp;D / Revenue held flat.</t>
+        </is>
+      </c>
+      <c r="H26" s="559" t="inlineStr">
+        <is>
+          <t>Keeps product investment while S&amp;M is the efficiency lever.</t>
+        </is>
+      </c>
+      <c r="I26" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1" s="244">
+      <c r="B27" s="559" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="559" t="inlineStr">
+        <is>
+          <t>F68:J68</t>
+        </is>
+      </c>
+      <c r="D27" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A margin path</t>
+        </is>
+      </c>
+      <c r="E27" s="559" t="inlineStr">
+        <is>
+          <t>47.72% → 46.22% → 44.72% → 44.22% → 44.22%</t>
+        </is>
+      </c>
+      <c r="F27" s="559" t="inlineStr">
+        <is>
+          <t>SG&amp;A (S&amp;M+G&amp;A) % of sales in forecast.</t>
+        </is>
+      </c>
+      <c r="G27" s="559" t="inlineStr">
+        <is>
+          <t>Compresses ~500 bps of revenue by Y3 vs FY25 49.72%.</t>
+        </is>
+      </c>
+      <c r="H27" s="559" t="inlineStr">
+        <is>
+          <t>Operationalizes ZI AI-SDR thesis into the LBO P&amp;L.</t>
+        </is>
+      </c>
+      <c r="I27" s="559" t="inlineStr">
+        <is>
+          <t>LBOMODEL1 thesis + ZI_* tabs; FY25 base from https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1" s="244">
+      <c r="B28" s="559" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="559" t="inlineStr">
+        <is>
+          <t>C69:J69</t>
+        </is>
+      </c>
+      <c r="D28" s="559" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="E28" s="559" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="F28" s="559" t="inlineStr">
+        <is>
+          <t>Book tax rate on EBT.</t>
+        </is>
+      </c>
+      <c r="G28" s="559" t="inlineStr">
+        <is>
+          <t>Flat statutory-like rate in MODEL1.</t>
+        </is>
+      </c>
+      <c r="H28" s="559" t="inlineStr">
+        <is>
+          <t>Simplifies vs actual cash tax / NOL complexity.</t>
+        </is>
+      </c>
+      <c r="I28" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1" s="244">
+      <c r="B29" s="559" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="559" t="inlineStr">
+        <is>
+          <t>I275/J275</t>
+        </is>
+      </c>
+      <c r="D29" s="559" t="inlineStr">
+        <is>
+          <t>Sponsor MoIC / IRR</t>
+        </is>
+      </c>
+      <c r="E29" s="559" t="inlineStr">
+        <is>
+          <t>~2.97x / ~24.4%</t>
+        </is>
+      </c>
+      <c r="F29" s="559" t="inlineStr">
+        <is>
+          <t>Base returns at 8.0x exit.</t>
+        </is>
+      </c>
+      <c r="G29" s="559" t="inlineStr">
+        <is>
+          <t>Exit equity / sponsor equity; IRR = MoIC^(1/5)−1.</t>
+        </is>
+      </c>
+      <c r="H29" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative; sensitive to exit multiple, leverage, and SG&amp;A path.</t>
+        </is>
+      </c>
+      <c r="I29" s="559" t="inlineStr">
+        <is>
+          <t>Derived on LBO returns block</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — DCF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `DCF` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>DCF reference share price</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875 (LBO offer)</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Price shown in DCF header for football-field compare.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer/sh.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Makes DCF tab speak the same deal price as the LBO.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Basic / diluted share count</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>292.312m</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Share count for per-share value.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO shares.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>Same 10-Q share count as LBO.</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>C55/C56/C57</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>CAPM inputs</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>Rf 4.3% / β 1.20 / ERP 5.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Building blocks of cost of equity.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Ke = Rf + β×ERP.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Illustrative SaaS CAPM stack for DCF tab (not Yacktman-adjusted).</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>C50/C51</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>Cost of debt / tax</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>7.0% / 21%</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>After-tax debt cost inputs.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>Rd×(1−t) in WACC.</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Rounded financing cost vs new LBO stack.</t>
+        </is>
+      </c>
+      <c r="I9" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" s="244">
+      <c r="B10" s="559" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="559" t="inlineStr">
+        <is>
+          <t>C53/C58</t>
+        </is>
+      </c>
+      <c r="D10" s="559" t="inlineStr">
+        <is>
+          <t>Capital structure weights</t>
+        </is>
+      </c>
+      <c r="E10" s="559" t="inlineStr">
+        <is>
+          <t>Wd 45% / We 55%</t>
+        </is>
+      </c>
+      <c r="F10" s="559" t="inlineStr">
+        <is>
+          <t>Target weights in WACC.</t>
+        </is>
+      </c>
+      <c r="G10" s="559" t="inlineStr">
+        <is>
+          <t>Hardcoded policy on DCF tab.</t>
+        </is>
+      </c>
+      <c r="H10" s="559" t="inlineStr">
+        <is>
+          <t>Closer to PF leveraged structure than pre-deal equity-heavy weights.</t>
+        </is>
+      </c>
+      <c r="I10" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="244">
+      <c r="B11" s="559" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="559" t="inlineStr">
+        <is>
+          <t>C9/C59</t>
+        </is>
+      </c>
+      <c r="D11" s="559" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="E11" s="559" t="inlineStr">
+        <is>
+          <t>~8.53%</t>
+        </is>
+      </c>
+      <c r="F11" s="559" t="inlineStr">
+        <is>
+          <t>Discount rate for unlevered FCF.</t>
+        </is>
+      </c>
+      <c r="G11" s="559" t="inlineStr">
+        <is>
+          <t>We×Ke + Wd×Rd×(1−t).</t>
+        </is>
+      </c>
+      <c r="H11" s="559" t="inlineStr">
+        <is>
+          <t>Used for DCF PV math on this tab.</t>
+        </is>
+      </c>
+      <c r="I11" s="559" t="inlineStr">
+        <is>
+          <t>Derived from CAPM + Rd assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" s="244">
+      <c r="B12" s="559" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" s="559" t="inlineStr">
+        <is>
+          <t>J37</t>
+        </is>
+      </c>
+      <c r="D12" s="559" t="inlineStr">
+        <is>
+          <t>Exit EBITDA multiple (DCF)</t>
+        </is>
+      </c>
+      <c r="E12" s="559" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="F12" s="559" t="inlineStr">
+        <is>
+          <t>Terminal multiple in exit-EBITDA approach.</t>
+        </is>
+      </c>
+      <c r="G12" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO!D17.</t>
+        </is>
+      </c>
+      <c r="H12" s="559" t="inlineStr">
+        <is>
+          <t>Keeps LBO and DCF exit frameworks comparable.</t>
+        </is>
+      </c>
+      <c r="I12" s="559" t="inlineStr">
+        <is>
+          <t>LBO!D17</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" s="244">
+      <c r="B13" s="559" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="559" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="D13" s="559" t="inlineStr">
+        <is>
+          <t>Perpetuity g</t>
+        </is>
+      </c>
+      <c r="E13" s="559" t="inlineStr">
+        <is>
+          <t>0% in template cell (sensitivity uses 2–4%)</t>
+        </is>
+      </c>
+      <c r="F13" s="559" t="inlineStr">
+        <is>
+          <t>Long-term growth in Gordon approach.</t>
+        </is>
+      </c>
+      <c r="G13" s="559" t="inlineStr">
+        <is>
+          <t>Template default; grid varies g.</t>
+        </is>
+      </c>
+      <c r="H13" s="559" t="inlineStr">
+        <is>
+          <t>Football-field sensitivity still shows 2–4% g range.</t>
+        </is>
+      </c>
+      <c r="I13" s="559" t="inlineStr">
+        <is>
+          <t>WSP template convention + MODEL1 note</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="48" customHeight="1" s="244">
+      <c r="B14" s="559" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" s="559" t="inlineStr">
+        <is>
+          <t>C31</t>
+        </is>
+      </c>
+      <c r="D14" s="559" t="inlineStr">
+        <is>
+          <t>Cash-flow timing</t>
+        </is>
+      </c>
+      <c r="E14" s="559" t="inlineStr">
+        <is>
+          <t>Middle of period</t>
+        </is>
+      </c>
+      <c r="F14" s="559" t="inlineStr">
+        <is>
+          <t>Mid-year discounting convention.</t>
+        </is>
+      </c>
+      <c r="G14" s="559" t="inlineStr">
+        <is>
+          <t>Midperiod adjustment factor on DCF tab.</t>
+        </is>
+      </c>
+      <c r="H14" s="559" t="inlineStr">
+        <is>
+          <t>Standard IB mid-year convention for annual FCFs.</t>
+        </is>
+      </c>
+      <c r="I14" s="559" t="inlineStr">
+        <is>
+          <t>WSP template</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="539" t="inlineStr">
+        <is>
+          <t>Assumptions — Shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `Shares` only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>E5/E6</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Offer price for dilution</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>$5.3875</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Price used in treasury-stock method.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Synced to LBO offer.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Aligns diluted-share math with deal price.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>LBO!H20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>E7/E14</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>Basic &amp; net diluted shares</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>292.312m / 292.312m</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>Share count used for equity value.</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>Outstanding shares; options set to 0 in MODEL1.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>10-Q share count; detailed options ladder not loaded (net dilutive options = 0).</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001794515&amp;type=10-Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>E8:E11</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>Options / other dilutives</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Incremental dilutive securities.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>Cleared BMC ladder; set to zero pending full award rollforward.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Conservative vs overstating dilution without a current award table.</t>
+        </is>
+      </c>
+      <c r="I8" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1) — update from proxy/10-K award note when refined</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21475,476 +27462,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="42" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="12" customWidth="1" style="244" min="4" max="4"/>
-    <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="70" customWidth="1" style="244" min="6" max="6"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>FY2025 10-K source financials ($ millions unless noted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="541" t="inlineStr">
-        <is>
-          <t>Line item</t>
-        </is>
-      </c>
-      <c r="C4" s="541" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="D4" s="541" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="E4" s="541" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="F4" s="541" t="inlineStr">
-        <is>
-          <t>XBRL / note</t>
+          <t>Assumptions — 52wkHL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `52wkHL` only.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C5" s="556" t="n">
-        <v>1239.5</v>
-      </c>
-      <c r="D5" s="556" t="n">
-        <v>1214.3</v>
-      </c>
-      <c r="E5" s="556" t="n">
-        <v>1249.5</v>
-      </c>
-      <c r="F5" s="542" t="inlineStr">
-        <is>
-          <t>RevenueFromContractWithCustomerExcludingAssessedTax</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>Selling &amp; Marketing</t>
-        </is>
-      </c>
-      <c r="C6" s="556" t="n">
-        <v>408.5</v>
-      </c>
-      <c r="D6" s="556" t="n">
-        <v>414.1</v>
-      </c>
-      <c r="E6" s="556" t="n">
-        <v>414.6</v>
-      </c>
-      <c r="F6" s="542" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="542" t="inlineStr">
-        <is>
-          <t>Research &amp; Development</t>
-        </is>
-      </c>
-      <c r="C7" s="556" t="n">
-        <v>191.5</v>
-      </c>
-      <c r="D7" s="556" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="E7" s="556" t="n">
-        <v>182</v>
-      </c>
-      <c r="F7" s="542" t="inlineStr">
-        <is>
-          <t>ResearchAndDevelopmentExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="542" t="inlineStr">
-        <is>
-          <t>General &amp; Administrative</t>
-        </is>
-      </c>
-      <c r="C8" s="556" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="D8" s="556" t="n">
-        <v>295.3</v>
-      </c>
-      <c r="E8" s="556" t="n">
-        <v>206.7</v>
-      </c>
-      <c r="F8" s="542" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="542" t="inlineStr">
-        <is>
-          <t>Operating expenses (ex-COGS)</t>
-        </is>
-      </c>
-      <c r="E9" s="556" t="n">
-        <v>824.2</v>
-      </c>
-      <c r="F9" s="542" t="inlineStr">
-        <is>
-          <t>OperatingExpenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="542" t="inlineStr">
-        <is>
-          <t>Operating income</t>
-        </is>
-      </c>
-      <c r="C10" s="556" t="n">
-        <v>259.5</v>
-      </c>
-      <c r="D10" s="556" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="E10" s="556" t="n">
-        <v>225.7</v>
-      </c>
-      <c r="F10" s="542" t="inlineStr">
-        <is>
-          <t>OperatingIncomeLoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="542" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="C11" s="556" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="D11" s="556" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E11" s="556" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="F11" s="542" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="542" t="inlineStr">
-        <is>
-          <t>Amort. of intangibles</t>
-        </is>
-      </c>
-      <c r="C12" s="556" t="n">
-        <v>61</v>
-      </c>
-      <c r="D12" s="556" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="E12" s="556" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="F12" s="542" t="inlineStr">
-        <is>
-          <t>AmortizationOfIntangibleAssets</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="542" t="inlineStr">
-        <is>
-          <t>Total D&amp;A (dep+intang)</t>
-        </is>
-      </c>
-      <c r="C13" s="556" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="D13" s="556" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="E13" s="556" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="F13" s="542" t="inlineStr">
-        <is>
-          <t>OtherDepreciationAndAmortization</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="542" t="inlineStr">
-        <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="C14" s="556" t="n">
-        <v>167.6</v>
-      </c>
-      <c r="D14" s="556" t="n">
-        <v>138</v>
-      </c>
-      <c r="E14" s="556" t="n">
-        <v>116.2</v>
-      </c>
-      <c r="F14" s="542" t="inlineStr">
-        <is>
-          <t>ShareBasedCompensation</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="542" t="inlineStr">
-        <is>
-          <t>Advertising expense</t>
-        </is>
-      </c>
-      <c r="E15" s="556" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="F15" s="542" t="inlineStr">
-        <is>
-          <t>AdvertisingExpense</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="542" t="inlineStr">
-        <is>
-          <t>Amort. deferred commissions</t>
-        </is>
-      </c>
-      <c r="C16" s="556" t="n">
-        <v>75.3</v>
-      </c>
-      <c r="D16" s="556" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="E16" s="556" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="F16" s="542" t="inlineStr">
-        <is>
-          <t>AmortizationOfDeferredSalesCommissions</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="542" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="C17" s="556" t="n">
-        <v>107.3</v>
-      </c>
-      <c r="D17" s="556" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E17" s="556" t="n">
-        <v>124.2</v>
-      </c>
-      <c r="F17" s="542" t="inlineStr">
-        <is>
-          <t>NetIncomeLoss</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="544" t="inlineStr">
-        <is>
-          <t>Implied COGS (Rev − OpEx − OpInc)</t>
-        </is>
-      </c>
-      <c r="E19" s="557">
-        <f>E5-E9-E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="544" t="inlineStr">
-        <is>
-          <t>GAAP EBITDA proxy (OpInc + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="E20" s="557">
-        <f>E10+E13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="542" t="inlineStr">
-        <is>
-          <t>GAAP EBITDA margin</t>
-        </is>
-      </c>
-      <c r="E21" s="546">
-        <f>E20/E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="544" t="inlineStr">
-        <is>
-          <t>Adj. EBITDA proxy (+SBC)</t>
-        </is>
-      </c>
-      <c r="E22" s="557">
-        <f>E20+E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="542" t="inlineStr">
-        <is>
-          <t>Adj. EBITDA margin</t>
-        </is>
-      </c>
-      <c r="E23" s="546">
-        <f>E22/E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="547" t="inlineStr">
-        <is>
-          <t>HUMAN CAPITAL (10-K Item 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="542" t="inlineStr">
-        <is>
-          <t>Total employees (12/31/2025)</t>
-        </is>
-      </c>
-      <c r="E26" s="548" t="n">
-        <v>3180</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="542" t="inlineStr">
-        <is>
-          <t>Cost of service employees</t>
-        </is>
-      </c>
-      <c r="E27" s="548" t="n">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="542" t="inlineStr">
-        <is>
-          <t>Sales &amp; Marketing employees</t>
-        </is>
-      </c>
-      <c r="E28" s="548" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="542" t="inlineStr">
-        <is>
-          <t>R&amp;D employees</t>
-        </is>
-      </c>
-      <c r="E29" s="548" t="n">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="542" t="inlineStr">
-        <is>
-          <t>G&amp;A employees</t>
-        </is>
-      </c>
-      <c r="E30" s="548" t="n">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="542" t="inlineStr">
-        <is>
-          <t>Headcount check (sum)</t>
-        </is>
-      </c>
-      <c r="E31" s="549">
-        <f>E27+E28+E29+E30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M $ / S&amp;M employee ($000s)</t>
-        </is>
-      </c>
-      <c r="E32" s="557">
-        <f>E6*1000/E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M % of revenue</t>
-        </is>
-      </c>
-      <c r="E33" s="546">
-        <f>E6/E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="542" t="inlineStr">
-        <is>
-          <t>Quote — Human Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="550" t="inlineStr">
-        <is>
-          <t>As of December 31, 2025, we had 3,180 employees, consisting of 662 in cost of service, 1,370 in sales and marketing, 763 in research and development, and 385 in general and administrative.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38"/>
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>E4/E5</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>52-week high / low</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>Legacy sample tape (not GTM)</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Market range for football-field.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Still WSP BMC sample series in MODEL1.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Not yet replaced with GTM price history; LBO uses spot $4.31 instead.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>WSP sample residual — replace with GTM tape in MODEL2+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B36:F38"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21955,173 +27582,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="48" customWidth="1" style="244" min="2" max="2"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
     <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>Isolate bloated Sales &amp; Marketing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="542" t="inlineStr">
-        <is>
-          <t>FY2025 Revenue ($m)</t>
-        </is>
-      </c>
-      <c r="C4" s="557">
-        <f>'ZI_01_10K_Source'!E5</f>
-        <v/>
+          <t>Assumptions — ZI_01_10K_Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_01_10K_Source` only.</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>FY2025 S&amp;M ($m)</t>
-        </is>
-      </c>
-      <c r="C5" s="557">
-        <f>'ZI_01_10K_Source'!E6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M % revenue</t>
-        </is>
-      </c>
-      <c r="C6" s="546">
-        <f>C5/C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="547" t="inlineStr">
-        <is>
-          <t>S&amp;M STACK (FY2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="542" t="inlineStr">
-        <is>
-          <t>Advertising</t>
-        </is>
-      </c>
-      <c r="C9" s="557">
-        <f>'ZI_01_10K_Source'!E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="542" t="inlineStr">
-        <is>
-          <t>Deferred commission amortization</t>
-        </is>
-      </c>
-      <c r="C10" s="557">
-        <f>'ZI_01_10K_Source'!E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="542" t="inlineStr">
-        <is>
-          <t>Residual S&amp;M (people + other)</t>
-        </is>
-      </c>
-      <c r="C11" s="557">
-        <f>C5-C9-C10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="542" t="inlineStr">
-        <is>
-          <t>Residual as % of S&amp;M</t>
-        </is>
-      </c>
-      <c r="C12" s="546">
-        <f>C11/C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="542" t="inlineStr">
-        <is>
-          <t>Residual $ / S&amp;M employee ($000s)</t>
-        </is>
-      </c>
-      <c r="C13" s="557">
-        <f>C11*1000/'ZI_01_10K_Source'!E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="547" t="inlineStr">
-        <is>
-          <t>BENCHMARK / THESIS INPUTS (edit yellow)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="542" t="inlineStr">
-        <is>
-          <t>Target mature SaaS S&amp;M % rev</t>
-        </is>
-      </c>
-      <c r="C16" s="551" t="n">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M bloat vs target ($m)</t>
-        </is>
-      </c>
-      <c r="C17" s="557">
-        <f>MAX(0,C5-C4*C16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="542" t="inlineStr">
-        <is>
-          <t>Bloat as % of revenue</t>
-        </is>
-      </c>
-      <c r="C18" s="546">
-        <f>C17/C4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="542" t="inlineStr">
-        <is>
-          <t>Bloat in basis points</t>
-        </is>
-      </c>
-      <c r="C19" s="549">
-        <f>C18*10000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>10-K: 1,370 S&amp;M employees; S&amp;M is ~33% of revenue. Model treats outbound SDR/BDR capacity as the AI-replaceable slice (yellow % on next sheet).</t>
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>E5</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Revenue</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>$1,249.5m</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Annual revenue anchor.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>XBRL RevenueFromContractWithCustomerExcludingAssessedTax.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Latest annual 10-K fact.</t>
+        </is>
+      </c>
+      <c r="I6" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm ; https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" s="244">
+      <c r="B7" s="559" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="559" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="D7" s="559" t="inlineStr">
+        <is>
+          <t>FY2025 Selling &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="E7" s="559" t="inlineStr">
+        <is>
+          <t>$414.6m</t>
+        </is>
+      </c>
+      <c r="F7" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M expense (the bloat line).</t>
+        </is>
+      </c>
+      <c r="G7" s="559" t="inlineStr">
+        <is>
+          <t>XBRL SellingAndMarketingExpense.</t>
+        </is>
+      </c>
+      <c r="H7" s="559" t="inlineStr">
+        <is>
+          <t>33.2% of FY25 revenue — thesis starting point.</t>
+        </is>
+      </c>
+      <c r="I7" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="244">
+      <c r="B8" s="559" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="559" t="inlineStr">
+        <is>
+          <t>E10/E13/E20</t>
+        </is>
+      </c>
+      <c r="D8" s="559" t="inlineStr">
+        <is>
+          <t>OpInc / D&amp;A / EBITDA proxy</t>
+        </is>
+      </c>
+      <c r="E8" s="559" t="inlineStr">
+        <is>
+          <t>$225.7 / $88.8 / $314.5m</t>
+        </is>
+      </c>
+      <c r="F8" s="559" t="inlineStr">
+        <is>
+          <t>Operating income, D&amp;A, EBITDA proxy.</t>
+        </is>
+      </c>
+      <c r="G8" s="559" t="inlineStr">
+        <is>
+          <t>OpInc + OtherDepreciationAndAmortization.</t>
+        </is>
+      </c>
+      <c r="H8" s="559" t="inlineStr">
+        <is>
+          <t>Bridges to LBO!D13 LTM EBITDA.</t>
+        </is>
+      </c>
+      <c r="I8" s="560" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/api/xbrl/companyfacts/CIK0001794515.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" s="244">
+      <c r="B9" s="559" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="559" t="inlineStr">
+        <is>
+          <t>E28</t>
+        </is>
+      </c>
+      <c r="D9" s="559" t="inlineStr">
+        <is>
+          <t>S&amp;M employees</t>
+        </is>
+      </c>
+      <c r="E9" s="559" t="inlineStr">
+        <is>
+          <t>1,370</t>
+        </is>
+      </c>
+      <c r="F9" s="559" t="inlineStr">
+        <is>
+          <t>Headcount in sales &amp; marketing.</t>
+        </is>
+      </c>
+      <c r="G9" s="559" t="inlineStr">
+        <is>
+          <t>10-K Human Capital disclosure (3,180 total).</t>
+        </is>
+      </c>
+      <c r="H9" s="559" t="inlineStr">
+        <is>
+          <t>Denominator for SDR % assumption.</t>
+        </is>
+      </c>
+      <c r="I9" s="560" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1794515/000179451526000012/zi-20251231.htm</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22132,483 +27828,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="B2:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="48" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="12" customWidth="1" style="244" min="4" max="4"/>
-    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+    <col width="4" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="28" customWidth="1" style="244" min="4" max="4"/>
+    <col width="26" customWidth="1" style="244" min="5" max="5"/>
+    <col width="36" customWidth="1" style="244" min="6" max="6"/>
+    <col width="36" customWidth="1" style="244" min="7" max="7"/>
+    <col width="40" customWidth="1" style="244" min="8" max="8"/>
+    <col width="55" customWidth="1" style="244" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="539" t="inlineStr">
         <is>
-          <t>Headcount reduction: outbound SDRs → AI agents</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="547" t="inlineStr">
-        <is>
-          <t>BASELINE</t>
+          <t>Assumptions — ZI_02_SM_Isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Subset of 00_Assumptions_List for tab `ZI_02_SM_Isolation` only.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="542" t="inlineStr">
-        <is>
-          <t>S&amp;M employees (10-K)</t>
-        </is>
-      </c>
-      <c r="C5" s="549">
-        <f>'ZI_01_10K_Source'!E28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="542" t="inlineStr">
-        <is>
-          <t>% of S&amp;M that are outbound SDR/BDR</t>
-        </is>
-      </c>
-      <c r="C6" s="551" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="542" t="inlineStr">
-        <is>
-          <t>Outbound SDR headcount (Y0)</t>
-        </is>
-      </c>
-      <c r="C7" s="549">
-        <f>ROUND(C5*C6,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="542" t="inlineStr">
-        <is>
-          <t>Fully loaded cost / SDR / yr ($000s)</t>
-        </is>
-      </c>
-      <c r="C8" s="556" t="n">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="542" t="inlineStr">
-        <is>
-          <t>Addressable SDR cost pool ($m)</t>
-        </is>
-      </c>
-      <c r="C9" s="557">
-        <f>C7*C8/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="547" t="inlineStr">
-        <is>
-          <t>AI AGENT UNIT ECONOMICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="542" t="inlineStr">
-        <is>
-          <t>AI agent seats per SDR replaced</t>
-        </is>
-      </c>
-      <c r="C12" s="552" t="n">
+      <c r="B5" s="558" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C5" s="558" t="inlineStr">
+        <is>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="D5" s="558" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="E5" s="558" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F5" s="558" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="G5" s="558" t="inlineStr">
+        <is>
+          <t>How</t>
+        </is>
+      </c>
+      <c r="H5" s="558" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="I5" s="558" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" s="244">
+      <c r="B6" s="559" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="542" t="inlineStr">
-        <is>
-          <t>AI platform + compute / seat / yr ($000s)</t>
-        </is>
-      </c>
-      <c r="C13" s="556" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="542" t="inlineStr">
-        <is>
-          <t>Human oversight FTE per 20 AI seats</t>
-        </is>
-      </c>
-      <c r="C14" s="552" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="542" t="inlineStr">
-        <is>
-          <t>Oversight fully loaded / FTE / yr ($000s)</t>
-        </is>
-      </c>
-      <c r="C15" s="556" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="542" t="inlineStr">
-        <is>
-          <t>One-time severance / SDR ($000s)</t>
-        </is>
-      </c>
-      <c r="C16" s="556" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="542" t="inlineStr">
-        <is>
-          <t>One-time AI build / integration ($m) in Y1</t>
-        </is>
-      </c>
-      <c r="C17" s="556" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="547" t="inlineStr">
-        <is>
-          <t>REDUCTION SCHEDULE (% of Y0 SDRs exited by year-end)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="542" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C20" s="541" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="541" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E20" s="541" t="n">
-        <v>2028</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="542" t="inlineStr">
-        <is>
-          <t>Cumulative % SDRs replaced</t>
-        </is>
-      </c>
-      <c r="C21" s="553" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D21" s="553" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E21" s="553" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="542" t="inlineStr">
-        <is>
-          <t>SDRs remaining</t>
-        </is>
-      </c>
-      <c r="C22" s="549">
-        <f>ROUND($C$7*(1-C21),0)</f>
-        <v/>
-      </c>
-      <c r="D22" s="549">
-        <f>ROUND($C$7*(1-D21),0)</f>
-        <v/>
-      </c>
-      <c r="E22" s="549">
-        <f>ROUND($C$7*(1-E21),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="542" t="inlineStr">
-        <is>
-          <t>SDRs exited (cumulative)</t>
-        </is>
-      </c>
-      <c r="C23" s="549">
-        <f>$C$7-C22</f>
-        <v/>
-      </c>
-      <c r="D23" s="549">
-        <f>$C$7-D22</f>
-        <v/>
-      </c>
-      <c r="E23" s="549">
-        <f>$C$7-E22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="542" t="inlineStr">
-        <is>
-          <t>SDRs exited this year</t>
-        </is>
-      </c>
-      <c r="C24" s="549">
-        <f>C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="549">
-        <f>D23-C23</f>
-        <v/>
-      </c>
-      <c r="E24" s="549">
-        <f>E23-D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="542" t="inlineStr">
-        <is>
-          <t>Avg SDRs during year</t>
-        </is>
-      </c>
-      <c r="C25" s="557">
-        <f>($C$7+C22)/2</f>
-        <v/>
-      </c>
-      <c r="D25" s="557">
-        <f>(C22+D22)/2</f>
-        <v/>
-      </c>
-      <c r="E25" s="557">
-        <f>(D22+E22)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="547" t="inlineStr">
-        <is>
-          <t>AI SEATS &amp; OVERSIGHT</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="542" t="inlineStr">
-        <is>
-          <t>AI seats (cum.)</t>
-        </is>
-      </c>
-      <c r="C28" s="557">
-        <f>C23*$C$12</f>
-        <v/>
-      </c>
-      <c r="D28" s="557">
-        <f>D23*$C$12</f>
-        <v/>
-      </c>
-      <c r="E28" s="557">
-        <f>E23*$C$12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="542" t="inlineStr">
-        <is>
-          <t>Oversight FTEs</t>
-        </is>
-      </c>
-      <c r="C29" s="549">
-        <f>ROUNDUP(C28/(20/$C$14),0)</f>
-        <v/>
-      </c>
-      <c r="D29" s="549">
-        <f>ROUNDUP(D28/(20/$C$14),0)</f>
-        <v/>
-      </c>
-      <c r="E29" s="549">
-        <f>ROUNDUP(E28/(20/$C$14),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="547" t="inlineStr">
-        <is>
-          <t>P&amp;L IMPACT ($m)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="542" t="inlineStr">
-        <is>
-          <t>SDR cash cost (avg HC × cost)</t>
-        </is>
-      </c>
-      <c r="C32" s="557">
-        <f>C25*$C$8/1000</f>
-        <v/>
-      </c>
-      <c r="D32" s="557">
-        <f>D25*$C$8/1000</f>
-        <v/>
-      </c>
-      <c r="E32" s="557">
-        <f>E25*$C$8/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="542" t="inlineStr">
-        <is>
-          <t>Baseline SDR cost if no program</t>
-        </is>
-      </c>
-      <c r="C33" s="557">
-        <f>$C$9</f>
-        <v/>
-      </c>
-      <c r="D33" s="557">
-        <f>$C$9</f>
-        <v/>
-      </c>
-      <c r="E33" s="557">
-        <f>$C$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="542" t="inlineStr">
-        <is>
-          <t>Gross SDR savings vs baseline</t>
-        </is>
-      </c>
-      <c r="C34" s="557">
-        <f>C33-C32</f>
-        <v/>
-      </c>
-      <c r="D34" s="557">
-        <f>D33-D32</f>
-        <v/>
-      </c>
-      <c r="E34" s="557">
-        <f>E33-E32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="542" t="inlineStr">
-        <is>
-          <t>AI seat opex</t>
-        </is>
-      </c>
-      <c r="C35" s="557">
-        <f>C28*$C$13/1000</f>
-        <v/>
-      </c>
-      <c r="D35" s="557">
-        <f>D28*$C$13/1000</f>
-        <v/>
-      </c>
-      <c r="E35" s="557">
-        <f>E28*$C$13/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="542" t="inlineStr">
-        <is>
-          <t>Oversight opex</t>
-        </is>
-      </c>
-      <c r="C36" s="557">
-        <f>C29*$C$15/1000</f>
-        <v/>
-      </c>
-      <c r="D36" s="557">
-        <f>D29*$C$15/1000</f>
-        <v/>
-      </c>
-      <c r="E36" s="557">
-        <f>E29*$C$15/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="542" t="inlineStr">
-        <is>
-          <t>Severance (this year's exits)</t>
-        </is>
-      </c>
-      <c r="C37" s="557">
-        <f>C24*$C$16/1000</f>
-        <v/>
-      </c>
-      <c r="D37" s="557">
-        <f>D24*$C$16/1000</f>
-        <v/>
-      </c>
-      <c r="E37" s="557">
-        <f>E24*$C$16/1000</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="542" t="inlineStr">
-        <is>
-          <t>AI build (Y1 only)</t>
-        </is>
-      </c>
-      <c r="C38" s="557">
-        <f>$C$17</f>
-        <v/>
-      </c>
-      <c r="D38" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="556" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="544" t="inlineStr">
-        <is>
-          <t>Net EBITDA benefit (in-year, after one-time)</t>
-        </is>
-      </c>
-      <c r="C39" s="557">
-        <f>C34-C35-C36-C37-C38</f>
-        <v/>
-      </c>
-      <c r="D39" s="557">
-        <f>D34-D35-D36-D37-D38</f>
-        <v/>
-      </c>
-      <c r="E39" s="557">
-        <f>E34-E35-E36-E37-E38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="544" t="inlineStr">
-        <is>
-          <t>Year-end run-rate benefit (ex one-time)</t>
-        </is>
-      </c>
-      <c r="C40" s="557">
-        <f>(C23*$C$8/1000)-(C28*$C$13/1000)-(C29*$C$15/1000)</f>
-        <v/>
-      </c>
-      <c r="D40" s="557">
-        <f>(D23*$C$8/1000)-(D28*$C$13/1000)-(D29*$C$15/1000)</f>
-        <v/>
-      </c>
-      <c r="E40" s="557">
-        <f>(E23*$C$8/1000)-(E28*$C$13/1000)-(E29*$C$15/1000)</f>
-        <v/>
+      <c r="C6" s="559" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="D6" s="559" t="inlineStr">
+        <is>
+          <t>Target mature SaaS S&amp;M % rev</t>
+        </is>
+      </c>
+      <c r="E6" s="559" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="F6" s="559" t="inlineStr">
+        <is>
+          <t>Benchmark efficient S&amp;M intensity.</t>
+        </is>
+      </c>
+      <c r="G6" s="559" t="inlineStr">
+        <is>
+          <t>Yellow input vs FY25 33.2%.</t>
+        </is>
+      </c>
+      <c r="H6" s="559" t="inlineStr">
+        <is>
+          <t>Defines “bloat” dollars vs a mature SaaS target.</t>
+        </is>
+      </c>
+      <c r="I6" s="559" t="inlineStr">
+        <is>
+          <t>Model assumption (LBOMODEL1)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
@@ -93,64 +93,64 @@
     <numFmt numFmtId="187" formatCode="0\A"/>
     <numFmt numFmtId="188" formatCode="General\ &quot;yrs&quot;"/>
     <numFmt numFmtId="189" formatCode="0.000%"/>
-    <numFmt numFmtId="190" formatCode="#,##0.00_);\(#,##0\)"/>
-    <numFmt numFmtId="191" formatCode="#,##0.0%_);\(#,##0.0%\)"/>
-    <numFmt numFmtId="192" formatCode="0.0\ \x"/>
-    <numFmt numFmtId="193" formatCode="#,##0.00\ ;\(#,##0.00\)"/>
-    <numFmt numFmtId="194" formatCode="&quot;$&quot;#,##0.00\ ;\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="195" formatCode="0.0%_);\(0.0%\)"/>
-    <numFmt numFmtId="196" formatCode="0.000\ \x&quot;rate&quot;"/>
-    <numFmt numFmtId="197" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
-    <numFmt numFmtId="198" formatCode="0.00_);\(0.00\);0.00"/>
-    <numFmt numFmtId="199" formatCode="\C&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="200" formatCode="#,##0%_);\(#,##0.0%\)"/>
-    <numFmt numFmtId="201" formatCode="_(* #,##0.00000000_);_(* \(#,##0.00000000\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="202" formatCode="mmm\-d\-yyyy"/>
-    <numFmt numFmtId="203" formatCode="mmm\-yyyy"/>
-    <numFmt numFmtId="204" formatCode="yyyy"/>
-    <numFmt numFmtId="205" formatCode="0.00\x&quot;rate&quot;"/>
-    <numFmt numFmtId="206" formatCode="0.0&quot;  &quot;"/>
-    <numFmt numFmtId="207" formatCode="&quot;$&quot;#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="208" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="209" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="210" formatCode="&quot;$&quot;#,##0.00&quot;A&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;A&quot;"/>
-    <numFmt numFmtId="211" formatCode="#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="212" formatCode="&quot;$&quot;#,##0.00&quot;E&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;E&quot;"/>
-    <numFmt numFmtId="213" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="214" formatCode="#,##0.00;\(#,##0.00\)"/>
-    <numFmt numFmtId="215" formatCode=".%\,\(0.0%%;\t"/>
-    <numFmt numFmtId="216" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="217" formatCode="0.0%_);[Red]\(0.0%\)"/>
-    <numFmt numFmtId="218" formatCode="0.00_);\(0.00\);0.00_)"/>
-    <numFmt numFmtId="219" formatCode="#,##0\x"/>
-    <numFmt numFmtId="220" formatCode="&quot;TKR&quot;\ 0"/>
-    <numFmt numFmtId="221" formatCode=".%\,\(0.%%;\t"/>
-    <numFmt numFmtId="222" formatCode="&quot;$&quot;#,###.0\ \ "/>
-    <numFmt numFmtId="223" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\)"/>
-    <numFmt numFmtId="224" formatCode="#,##0.000_);\(#,##0.000\)"/>
-    <numFmt numFmtId="225" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\);&quot;--  &quot;"/>
-    <numFmt numFmtId="226" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="227" formatCode="0.0\x_);[Red]\(0.0\x\)"/>
-    <numFmt numFmtId="228" formatCode="0.0\ "/>
-    <numFmt numFmtId="229" formatCode="&quot;$&quot;#,##0.0;\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="230" formatCode="#,##0.00%_);\(#,##0.00%\)"/>
-    <numFmt numFmtId="231" formatCode="0.00\%;\-0.00\%;0.00\%"/>
-    <numFmt numFmtId="232" formatCode="0.0%\ ;\(0.0%\)"/>
-    <numFmt numFmtId="233" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="234" formatCode="&quot;$&quot;0.00\ "/>
-    <numFmt numFmtId="235" formatCode="0.0\ \ \ \ \ "/>
-    <numFmt numFmtId="236" formatCode="0.00\x;\-0.00\x;0.00\x"/>
-    <numFmt numFmtId="237" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="238" formatCode="#,##0.0_);\(#,##0.0\);_(* &quot;-&quot;_)"/>
-    <numFmt numFmtId="239" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="240" formatCode="0.00%_);[Red]\(0.00%\)"/>
-    <numFmt numFmtId="241" formatCode="#,##0.0\x_);\(#,##0.0\x\)"/>
-    <numFmt numFmtId="242" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
-    <numFmt numFmtId="243" formatCode="###0&quot;E&quot;_)"/>
-    <numFmt numFmtId="244" formatCode="#,##0.0"/>
-    <numFmt numFmtId="245" formatCode="0.00x"/>
+    <numFmt numFmtId="190" formatCode="#,##0.0"/>
+    <numFmt numFmtId="191" formatCode="0.00x"/>
+    <numFmt numFmtId="192" formatCode="#,##0.00_);\(#,##0\)"/>
+    <numFmt numFmtId="193" formatCode="#,##0.0%_);\(#,##0.0%\)"/>
+    <numFmt numFmtId="194" formatCode="0.0\ \x"/>
+    <numFmt numFmtId="195" formatCode="#,##0.00\ ;\(#,##0.00\)"/>
+    <numFmt numFmtId="196" formatCode="&quot;$&quot;#,##0.00\ ;\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="197" formatCode="0.0%_);\(0.0%\)"/>
+    <numFmt numFmtId="198" formatCode="0.000\ \x&quot;rate&quot;"/>
+    <numFmt numFmtId="199" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
+    <numFmt numFmtId="200" formatCode="0.00_);\(0.00\);0.00"/>
+    <numFmt numFmtId="201" formatCode="\C&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="202" formatCode="#,##0%_);\(#,##0.0%\)"/>
+    <numFmt numFmtId="203" formatCode="_(* #,##0.00000000_);_(* \(#,##0.00000000\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="204" formatCode="mmm\-d\-yyyy"/>
+    <numFmt numFmtId="205" formatCode="mmm\-yyyy"/>
+    <numFmt numFmtId="206" formatCode="yyyy"/>
+    <numFmt numFmtId="207" formatCode="0.00\x&quot;rate&quot;"/>
+    <numFmt numFmtId="208" formatCode="0.0&quot;  &quot;"/>
+    <numFmt numFmtId="209" formatCode="&quot;$&quot;#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="210" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="211" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="212" formatCode="&quot;$&quot;#,##0.00&quot;A&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;A&quot;"/>
+    <numFmt numFmtId="213" formatCode="#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="214" formatCode="&quot;$&quot;#,##0.00&quot;E&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;E&quot;"/>
+    <numFmt numFmtId="215" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="216" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="217" formatCode=".%\,\(0.0%%;\t"/>
+    <numFmt numFmtId="218" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="219" formatCode="0.0%_);[Red]\(0.0%\)"/>
+    <numFmt numFmtId="220" formatCode="0.00_);\(0.00\);0.00_)"/>
+    <numFmt numFmtId="221" formatCode="#,##0\x"/>
+    <numFmt numFmtId="222" formatCode="&quot;TKR&quot;\ 0"/>
+    <numFmt numFmtId="223" formatCode=".%\,\(0.%%;\t"/>
+    <numFmt numFmtId="224" formatCode="&quot;$&quot;#,###.0\ \ "/>
+    <numFmt numFmtId="225" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\)"/>
+    <numFmt numFmtId="226" formatCode="#,##0.000_);\(#,##0.000\)"/>
+    <numFmt numFmtId="227" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\);&quot;--  &quot;"/>
+    <numFmt numFmtId="228" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="229" formatCode="0.0\x_);[Red]\(0.0\x\)"/>
+    <numFmt numFmtId="230" formatCode="0.0\ "/>
+    <numFmt numFmtId="231" formatCode="&quot;$&quot;#,##0.0;\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="232" formatCode="#,##0.00%_);\(#,##0.00%\)"/>
+    <numFmt numFmtId="233" formatCode="0.00\%;\-0.00\%;0.00\%"/>
+    <numFmt numFmtId="234" formatCode="0.0%\ ;\(0.0%\)"/>
+    <numFmt numFmtId="235" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="236" formatCode="&quot;$&quot;0.00\ "/>
+    <numFmt numFmtId="237" formatCode="0.0\ \ \ \ \ "/>
+    <numFmt numFmtId="238" formatCode="0.00\x;\-0.00\x;0.00\x"/>
+    <numFmt numFmtId="239" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="240" formatCode="#,##0.0_);\(#,##0.0\);_(* &quot;-&quot;_)"/>
+    <numFmt numFmtId="241" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="242" formatCode="0.00%_);[Red]\(0.00%\)"/>
+    <numFmt numFmtId="243" formatCode="#,##0.0\x_);\(#,##0.0\x\)"/>
+    <numFmt numFmtId="244" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
+    <numFmt numFmtId="245" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="105">
+  <fonts count="107">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -836,6 +836,15 @@
       <name val="Calibri"/>
       <color rgb="000000FF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="38">
     <fill>
@@ -1443,19 +1452,19 @@
   <cellStyleXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="190" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="192" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="191" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="192" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="191" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="193" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="194" fontId="10" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="194" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="193" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="196" fontId="10" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="195" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="197" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="196" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="198" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0"/>
@@ -1482,7 +1491,7 @@
     <xf numFmtId="0" fontId="15" fillId="20" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="199" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1491,10 +1500,10 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="5"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="199" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="6"/>
+    <xf numFmtId="199" fontId="17" fillId="0" borderId="6"/>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="7"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1512,35 +1521,35 @@
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="198" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="200" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="7" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="5" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="199" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="201" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="200" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="202" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="201" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="203" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="200" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="202" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="15" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="202" fontId="25" fillId="24" borderId="0"/>
-    <xf numFmtId="203" fontId="27" fillId="0" borderId="8"/>
+    <xf numFmtId="204" fontId="25" fillId="24" borderId="0"/>
+    <xf numFmtId="205" fontId="27" fillId="0" borderId="8"/>
     <xf numFmtId="14" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="204" fontId="28" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="206" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="205" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="207" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1548,48 +1557,48 @@
     <xf numFmtId="6" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="7" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="206" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="207" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="208" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="209" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="210" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="211" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="209" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="210" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="211" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="212" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="213" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="195" fontId="10" fillId="0" borderId="10"/>
-    <xf numFmtId="214" fontId="10" fillId="2" borderId="9" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="215" fontId="10" fillId="2" borderId="9" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="214" fontId="10" fillId="2" borderId="9" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="216" fontId="17" fillId="0" borderId="0" applyProtection="1">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="0"/>
-    <xf numFmtId="217" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="195" fontId="32" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="213" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="214" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="13" fillId="26" borderId="11"/>
+    <xf numFmtId="215" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
+    <xf numFmtId="197" fontId="10" fillId="0" borderId="10"/>
+    <xf numFmtId="216" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="217" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="216" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="218" fontId="17" fillId="0" borderId="0" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="0"/>
+    <xf numFmtId="219" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="197" fontId="32" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="218" fontId="13" fillId="26" borderId="11"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="12"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="14"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="216" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="218" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="199" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
@@ -1603,7 +1612,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="17" fontId="39" fillId="27" borderId="0"/>
-    <xf numFmtId="218" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="220" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1614,26 +1623,26 @@
     <xf numFmtId="173" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="219" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="220" fontId="10" fillId="25" borderId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="221" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="219" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="222" fontId="10" fillId="25" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="195" fontId="42" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="223" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="195" fontId="42" fillId="0" borderId="0"/>
-    <xf numFmtId="222" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="221" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="223" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="197" fontId="42" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="197" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="224" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="225" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="1" hidden="1"/>
@@ -1642,62 +1651,62 @@
     <xf numFmtId="37" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="175" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="224" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="226" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="225" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="227" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="29" borderId="17"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="226" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="228" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="44" fillId="21" borderId="18"/>
-    <xf numFmtId="227" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="229" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="228" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="230" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="229" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="231" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="191" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="230" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="231" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="193" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="232" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="233" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="217" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="219" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="199" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="218" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="193" fontId="10" fillId="2" borderId="19" applyAlignment="1">
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="19" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="232" fontId="46" fillId="2" borderId="0"/>
-    <xf numFmtId="233" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="234" fontId="46" fillId="2" borderId="0"/>
+    <xf numFmtId="235" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="234" fontId="10" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="236" fontId="10" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="235" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="237" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="236" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="238" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="218" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1705,10 +1714,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="197" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="199" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="237" fontId="28" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="239" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="38" fontId="12" fillId="0" borderId="0"/>
@@ -1726,40 +1735,40 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="238" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="240" fontId="55" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="239" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="241" fontId="55" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="209" fontId="56" fillId="0" borderId="0"/>
-    <xf numFmtId="240" fontId="57" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="211" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="242" fontId="57" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="240" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="240" fontId="58" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="242" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="242" fontId="58" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="240" fontId="58" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="242" fontId="58" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="218" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="216" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="218" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="49" fontId="59" fillId="0" borderId="0"/>
-    <xf numFmtId="241" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="242" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="243" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="244" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="61" fillId="1" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="216" fontId="62" fillId="0" borderId="0"/>
+    <xf numFmtId="218" fontId="62" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="63" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1768,10 +1777,10 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="21"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="243" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="237" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="245" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="239" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="556">
+  <cellXfs count="563">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2503,14 +2512,14 @@
     <xf numFmtId="0" fontId="99" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="100" fillId="33" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="244" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="102" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="244" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="245" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="245" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="191" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="191" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="100" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="103" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2749,6 +2758,17 @@
     <xf numFmtId="183" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="190" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="102" fillId="35" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="37" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="191" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="191" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3097,6 +3117,127 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ZoomInfo LBOMODEL1 — Base vs AI-SDR Strategy</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Strategy_Summary'!C49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Strategy_Summary'!$B$50:$B$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Strategy_Summary'!$C$50:$C$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Strategy_Summary'!D49</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Strategy_Summary'!$B$50:$B$55</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Strategy_Summary'!$D$50:$D$55</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Value</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4165,6 +4306,33 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3600000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>1</col>
@@ -4797,14 +4965,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E45"/>
+  <dimension ref="B2:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="48" customWidth="1" style="244" min="2" max="2"/>
     <col width="16" customWidth="1" style="244" min="3" max="3"/>
     <col width="16" customWidth="1" style="244" min="4" max="4"/>
     <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="40" customWidth="1" style="244" min="6" max="6"/>
+    <col width="78" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -4855,7 +5023,7 @@
           <t>Revenue (FY2024)</t>
         </is>
       </c>
-      <c r="C10" s="409" t="n">
+      <c r="C10" s="556" t="n">
         <v>1214.3</v>
       </c>
       <c r="D10" s="408" t="inlineStr">
@@ -4887,7 +5055,7 @@
           <t>GAAP Operating Income</t>
         </is>
       </c>
-      <c r="C12" s="409" t="n">
+      <c r="C12" s="556" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="D12" s="408" t="inlineStr">
@@ -4902,7 +5070,7 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C13" s="409" t="n">
+      <c r="C13" s="556" t="n">
         <v>85.7</v>
       </c>
       <c r="D13" s="408" t="inlineStr">
@@ -4917,7 +5085,7 @@
           <t>Baseline EBITDA (OpInc+D&amp;A)</t>
         </is>
       </c>
-      <c r="C14" s="409" t="n">
+      <c r="C14" s="556" t="n">
         <v>183.1</v>
       </c>
       <c r="D14" s="408" t="inlineStr">
@@ -4947,7 +5115,7 @@
           <t>S&amp;M baseline (35% of rev)</t>
         </is>
       </c>
-      <c r="C16" s="409" t="n">
+      <c r="C16" s="556" t="n">
         <v>425</v>
       </c>
       <c r="D16" s="408" t="inlineStr">
@@ -5013,7 +5181,7 @@
           <t>Sponsor equity check</t>
         </is>
       </c>
-      <c r="C20" s="409" t="n">
+      <c r="C20" s="556" t="n">
         <v>1871.3</v>
       </c>
       <c r="D20" s="408" t="inlineStr">
@@ -5028,7 +5196,7 @@
           <t>New debt (5.0x EBITDA)</t>
         </is>
       </c>
-      <c r="C21" s="409" t="n">
+      <c r="C21" s="556" t="n">
         <v>915.5</v>
       </c>
       <c r="D21" s="408" t="inlineStr">
@@ -5110,8 +5278,13 @@
           <t>Delta</t>
         </is>
       </c>
-    </row>
-    <row r="31">
+      <c r="F30" s="557" t="inlineStr">
+        <is>
+          <t>COMMENTARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1" s="244">
       <c r="B31" s="408" t="inlineStr">
         <is>
           <t>Y2 EBITDA margin</t>
@@ -5126,104 +5299,139 @@
       <c r="E31" s="411" t="n">
         <v>0.05519116328280424</v>
       </c>
-    </row>
-    <row r="32">
+      <c r="F31" s="558" t="inlineStr">
+        <is>
+          <t>Year 2 operating profitability; the AI strategy drove this from 15.2% to 20.7%, expanding the margin by 5.5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1" s="244">
       <c r="B32" s="408" t="inlineStr">
         <is>
           <t>Y2 margin vs baseline (bps)</t>
         </is>
       </c>
-      <c r="C32" s="409" t="n">
+      <c r="C32" s="556" t="n">
         <v>14.17277443794801</v>
       </c>
-      <c r="D32" s="414" t="n">
+      <c r="D32" s="559" t="n">
         <v>566.0844072659904</v>
       </c>
-      <c r="E32" s="409" t="n">
+      <c r="E32" s="556" t="n">
         <v>551.9116328280425</v>
       </c>
-    </row>
-    <row r="33">
+      <c r="F32" s="558" t="inlineStr">
+        <is>
+          <t>The difference from baseline margin; AI implementation increased this metric by 551.9 basis points to reach 566.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1" s="244">
       <c r="B33" s="408" t="inlineStr">
         <is>
           <t>Y5 EBITDA ($m)</t>
         </is>
       </c>
-      <c r="C33" s="409" t="n">
+      <c r="C33" s="556" t="n">
         <v>218.4</v>
       </c>
-      <c r="D33" s="414" t="n">
+      <c r="D33" s="559" t="n">
         <v>314.7</v>
       </c>
-      <c r="E33" s="409" t="n">
+      <c r="E33" s="556" t="n">
         <v>96.3</v>
       </c>
-    </row>
-    <row r="34">
+      <c r="F33" s="558" t="inlineStr">
+        <is>
+          <t>Year 5 operating cash flow; AI-driven cost savings boosted this figure by $96.3 million to $314.7 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1" s="244">
       <c r="B34" s="408" t="inlineStr">
         <is>
           <t>Exit EV @ 13x ($m)</t>
         </is>
       </c>
-      <c r="C34" s="409" t="n">
+      <c r="C34" s="556" t="n">
         <v>2839.7</v>
       </c>
-      <c r="D34" s="414" t="n">
+      <c r="D34" s="559" t="n">
         <v>4091.4</v>
       </c>
-      <c r="E34" s="409" t="n">
+      <c r="E34" s="556" t="n">
         <v>1251.7</v>
       </c>
-    </row>
-    <row r="35">
+      <c r="F34" s="558" t="inlineStr">
+        <is>
+          <t>Projected exit Enterprise Value; higher EBITDA from AI increased this valuation by $1,251.7 million to $4,091.4 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="48" customHeight="1" s="244">
       <c r="B35" s="408" t="inlineStr">
         <is>
           <t>Exit net debt ($m)</t>
         </is>
       </c>
-      <c r="C35" s="409" t="n">
+      <c r="C35" s="556" t="n">
         <v>357.1</v>
       </c>
-      <c r="D35" s="414" t="n">
+      <c r="D35" s="559" t="n">
         <v>4.5</v>
       </c>
-      <c r="E35" s="409" t="n">
+      <c r="E35" s="556" t="n">
         <v>-352.6</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="F35" s="558" t="inlineStr">
+        <is>
+          <t>Remaining debt balance at exit; higher cash flow from the AI strategy paid down an extra $352.6 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="48" customHeight="1" s="244">
       <c r="B36" s="408" t="inlineStr">
         <is>
           <t>Exit equity value ($m)</t>
         </is>
       </c>
-      <c r="C36" s="409" t="n">
+      <c r="C36" s="556" t="n">
         <v>2482.6</v>
       </c>
-      <c r="D36" s="414" t="n">
+      <c r="D36" s="559" t="n">
         <v>4086.9</v>
       </c>
-      <c r="E36" s="409" t="n">
+      <c r="E36" s="556" t="n">
         <v>1604.3</v>
       </c>
-    </row>
-    <row r="37">
+      <c r="F36" s="558" t="inlineStr">
+        <is>
+          <t>Total payout to equity holders; the AI strategy increased this final payout by $1,604.3 million to $4,086.9 million.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="48" customHeight="1" s="244">
       <c r="B37" s="408" t="inlineStr">
         <is>
           <t>MOIC</t>
         </is>
       </c>
-      <c r="C37" s="415" t="n">
+      <c r="C37" s="560" t="n">
         <v>1.326661957981033</v>
       </c>
-      <c r="D37" s="416" t="n">
+      <c r="D37" s="561" t="n">
         <v>2.183979483523617</v>
       </c>
-      <c r="E37" s="415" t="n">
+      <c r="E37" s="560" t="n">
         <v>0.8573175255425849</v>
       </c>
-    </row>
-    <row r="38">
+      <c r="F37" s="558" t="inlineStr">
+        <is>
+          <t>Multiple on Invested Capital; the AI strategy significantly improved the total gross cash return from 1.33x to 2.18x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="48" customHeight="1" s="244">
       <c r="B38" s="408" t="inlineStr">
         <is>
           <t>IRR</t>
@@ -5238,6 +5446,18 @@
       <c r="E38" s="411" t="n">
         <v>0.1109330103741204</v>
       </c>
+      <c r="F38" s="558" t="inlineStr">
+        <is>
+          <t>Annualized compound return rate over a 5-year period; replacing human SDRs with AI boosted this return by 11.1 percentage points to 16.9%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="562" t="inlineStr">
+        <is>
+          <t>The IRR is calculated over a 5-year period.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="417" t="inlineStr">
@@ -5263,7 +5483,7 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>See AI_Operating, Base_Operating, Debt_Sweep_AI, LBO (WSP shell inputs), 00_Assumptions_List</t>
+          <t>See AI_Operating, Base_Operating, Debt_Sweep_AI, LBO, 00_Assumptions_List</t>
         </is>
       </c>
     </row>
@@ -5272,13 +5492,131 @@
         <is>
           <t>10-K: https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm</t>
         </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PDF version of this Strategy Summary + Commentary:</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="419" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_STRATEGY_SUMMARY.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="407" t="inlineStr">
+        <is>
+          <t>CHART DATA (Base vs AI-SDR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C49" s="412" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D49" s="412" t="inlineStr">
+        <is>
+          <t>AI-SDR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="D50" t="n">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Y5 EBITDA $m</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>314.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Exit EV $m</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2839.7</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4091.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Exit equity $m</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2482.6</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4086.9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MOIC (x)</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>IRR %</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.9</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -11319,19 +11657,19 @@
       <c r="B5" s="421" t="n">
         <v>2025</v>
       </c>
-      <c r="C5" s="409" t="n">
+      <c r="C5" s="556" t="n">
         <v>137.5282912000001</v>
       </c>
-      <c r="D5" s="409" t="n">
+      <c r="D5" s="556" t="n">
         <v>137.5282912000001</v>
       </c>
-      <c r="E5" s="414" t="n">
+      <c r="E5" s="559" t="n">
         <v>777.9717088</v>
       </c>
-      <c r="F5" s="409" t="n">
+      <c r="F5" s="556" t="n">
         <v>826.5607773</v>
       </c>
-      <c r="G5" s="414" t="n">
+      <c r="G5" s="559" t="n">
         <v>48.58906850000005</v>
       </c>
     </row>
@@ -11339,19 +11677,19 @@
       <c r="B6" s="421" t="n">
         <v>2026</v>
       </c>
-      <c r="C6" s="409" t="n">
+      <c r="C6" s="556" t="n">
         <v>159.2865991016001</v>
       </c>
-      <c r="D6" s="409" t="n">
+      <c r="D6" s="556" t="n">
         <v>159.2865991016001</v>
       </c>
-      <c r="E6" s="414" t="n">
+      <c r="E6" s="559" t="n">
         <v>618.6851096983999</v>
       </c>
-      <c r="F6" s="409" t="n">
+      <c r="F6" s="556" t="n">
         <v>726.867461747025</v>
       </c>
-      <c r="G6" s="414" t="n">
+      <c r="G6" s="559" t="n">
         <v>108.1823520486251</v>
       </c>
     </row>
@@ -11359,19 +11697,19 @@
       <c r="B7" s="421" t="n">
         <v>2027</v>
       </c>
-      <c r="C7" s="409" t="n">
+      <c r="C7" s="556" t="n">
         <v>183.23549201229</v>
       </c>
-      <c r="D7" s="409" t="n">
+      <c r="D7" s="556" t="n">
         <v>183.23549201229</v>
       </c>
-      <c r="E7" s="414" t="n">
+      <c r="E7" s="559" t="n">
         <v>435.4496176861098</v>
       </c>
-      <c r="F7" s="409" t="n">
+      <c r="F7" s="556" t="n">
         <v>615.320635583216</v>
       </c>
-      <c r="G7" s="414" t="n">
+      <c r="G7" s="559" t="n">
         <v>179.8710178971062</v>
       </c>
     </row>
@@ -11379,19 +11717,19 @@
       <c r="B8" s="421" t="n">
         <v>2028</v>
       </c>
-      <c r="C8" s="409" t="n">
+      <c r="C8" s="556" t="n">
         <v>204.2737956388759</v>
       </c>
-      <c r="D8" s="409" t="n">
+      <c r="D8" s="556" t="n">
         <v>204.2737956388759</v>
       </c>
-      <c r="E8" s="414" t="n">
+      <c r="E8" s="559" t="n">
         <v>231.1758220472339</v>
       </c>
-      <c r="F8" s="409" t="n">
+      <c r="F8" s="556" t="n">
         <v>492.2660966390317</v>
       </c>
-      <c r="G8" s="414" t="n">
+      <c r="G8" s="559" t="n">
         <v>261.0902745917978</v>
       </c>
     </row>
@@ -11399,19 +11737,19 @@
       <c r="B9" s="421" t="n">
         <v>2029</v>
       </c>
-      <c r="C9" s="409" t="n">
+      <c r="C9" s="556" t="n">
         <v>226.6632985760825</v>
       </c>
-      <c r="D9" s="409" t="n">
+      <c r="D9" s="556" t="n">
         <v>226.6632985760825</v>
       </c>
-      <c r="E9" s="414" t="n">
+      <c r="E9" s="559" t="n">
         <v>4.512523471151439</v>
       </c>
-      <c r="F9" s="409" t="n">
+      <c r="F9" s="556" t="n">
         <v>357.1352076643299</v>
       </c>
-      <c r="G9" s="414" t="n">
+      <c r="G9" s="559" t="n">
         <v>352.6226841931785</v>
       </c>
     </row>
@@ -11421,7 +11759,7 @@
           <t>New debt at close</t>
         </is>
       </c>
-      <c r="C11" s="409" t="n">
+      <c r="C11" s="556" t="n">
         <v>915.5000000000001</v>
       </c>
     </row>
@@ -11505,22 +11843,22 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="409" t="n">
+      <c r="C5" s="556" t="n">
         <v>1214.3</v>
       </c>
-      <c r="D5" s="409" t="n">
+      <c r="D5" s="556" t="n">
         <v>1250.729</v>
       </c>
-      <c r="E5" s="409" t="n">
+      <c r="E5" s="556" t="n">
         <v>1300.75816</v>
       </c>
-      <c r="F5" s="409" t="n">
+      <c r="F5" s="556" t="n">
         <v>1352.7884864</v>
       </c>
-      <c r="G5" s="409" t="n">
+      <c r="G5" s="556" t="n">
         <v>1393.372140992</v>
       </c>
-      <c r="H5" s="409" t="n">
+      <c r="H5" s="556" t="n">
         <v>1435.173305221761</v>
       </c>
     </row>
@@ -11530,22 +11868,22 @@
           <t>COGS</t>
         </is>
       </c>
-      <c r="C6" s="409" t="n">
+      <c r="C6" s="556" t="n">
         <v>189.8</v>
       </c>
-      <c r="D6" s="409" t="n">
+      <c r="D6" s="556" t="n">
         <v>195.4939999999999</v>
       </c>
-      <c r="E6" s="409" t="n">
+      <c r="E6" s="556" t="n">
         <v>203.31376</v>
       </c>
-      <c r="F6" s="409" t="n">
+      <c r="F6" s="556" t="n">
         <v>211.4463104</v>
       </c>
-      <c r="G6" s="409" t="n">
+      <c r="G6" s="556" t="n">
         <v>217.789699712</v>
       </c>
-      <c r="H6" s="409" t="n">
+      <c r="H6" s="556" t="n">
         <v>224.32339070336</v>
       </c>
     </row>
@@ -11555,22 +11893,22 @@
           <t>S&amp;M (human)</t>
         </is>
       </c>
-      <c r="C7" s="409" t="n">
+      <c r="C7" s="556" t="n">
         <v>425</v>
       </c>
-      <c r="D7" s="409" t="n">
+      <c r="D7" s="556" t="n">
         <v>437.75515</v>
       </c>
-      <c r="E7" s="409" t="n">
+      <c r="E7" s="556" t="n">
         <v>455.265356</v>
       </c>
-      <c r="F7" s="409" t="n">
+      <c r="F7" s="556" t="n">
         <v>473.47597024</v>
       </c>
-      <c r="G7" s="409" t="n">
+      <c r="G7" s="556" t="n">
         <v>487.6802493472001</v>
       </c>
-      <c r="H7" s="409" t="n">
+      <c r="H7" s="556" t="n">
         <v>502.3106568276161</v>
       </c>
     </row>
@@ -11580,22 +11918,22 @@
           <t>AI agent cost</t>
         </is>
       </c>
-      <c r="C8" s="409" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="409" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="409" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="409" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="409" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="409" t="n">
+      <c r="C8" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="556" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11605,22 +11943,22 @@
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="C9" s="409" t="n">
+      <c r="C9" s="556" t="n">
         <v>196.1</v>
       </c>
-      <c r="D9" s="409" t="n">
+      <c r="D9" s="556" t="n">
         <v>201.983</v>
       </c>
-      <c r="E9" s="409" t="n">
+      <c r="E9" s="556" t="n">
         <v>210.06232</v>
       </c>
-      <c r="F9" s="409" t="n">
+      <c r="F9" s="556" t="n">
         <v>218.4648128</v>
       </c>
-      <c r="G9" s="409" t="n">
+      <c r="G9" s="556" t="n">
         <v>225.018757184</v>
       </c>
-      <c r="H9" s="409" t="n">
+      <c r="H9" s="556" t="n">
         <v>231.7693198995201</v>
       </c>
     </row>
@@ -11630,22 +11968,22 @@
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="C10" s="409" t="n">
+      <c r="C10" s="556" t="n">
         <v>295.3</v>
       </c>
-      <c r="D10" s="409" t="n">
+      <c r="D10" s="556" t="n">
         <v>225.13122</v>
       </c>
-      <c r="E10" s="409" t="n">
+      <c r="E10" s="556" t="n">
         <v>234.1364688</v>
       </c>
-      <c r="F10" s="409" t="n">
+      <c r="F10" s="556" t="n">
         <v>243.501927552</v>
       </c>
-      <c r="G10" s="409" t="n">
+      <c r="G10" s="556" t="n">
         <v>250.8069853785601</v>
       </c>
-      <c r="H10" s="409" t="n">
+      <c r="H10" s="556" t="n">
         <v>258.3311949399169</v>
       </c>
     </row>
@@ -11655,22 +11993,22 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="409" t="n">
+      <c r="C11" s="556" t="n">
         <v>183.1</v>
       </c>
-      <c r="D11" s="414" t="n">
+      <c r="D11" s="559" t="n">
         <v>190.3656300000002</v>
       </c>
-      <c r="E11" s="414" t="n">
+      <c r="E11" s="559" t="n">
         <v>197.9802552000001</v>
       </c>
-      <c r="F11" s="414" t="n">
+      <c r="F11" s="559" t="n">
         <v>205.8994654080003</v>
       </c>
-      <c r="G11" s="414" t="n">
+      <c r="G11" s="559" t="n">
         <v>212.0764493702403</v>
       </c>
-      <c r="H11" s="414" t="n">
+      <c r="H11" s="559" t="n">
         <v>218.4387428513474</v>
       </c>
     </row>
@@ -11705,22 +12043,22 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C13" s="409" t="n">
+      <c r="C13" s="556" t="n">
         <v>85.7</v>
       </c>
-      <c r="D13" s="409" t="n">
+      <c r="D13" s="556" t="n">
         <v>88.271</v>
       </c>
-      <c r="E13" s="409" t="n">
+      <c r="E13" s="556" t="n">
         <v>91.80184</v>
       </c>
-      <c r="F13" s="409" t="n">
+      <c r="F13" s="556" t="n">
         <v>95.47391360000002</v>
       </c>
-      <c r="G13" s="409" t="n">
+      <c r="G13" s="556" t="n">
         <v>98.33813100800002</v>
       </c>
-      <c r="H13" s="409" t="n">
+      <c r="H13" s="556" t="n">
         <v>101.28827493824</v>
       </c>
     </row>
@@ -11730,22 +12068,22 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="409" t="n">
+      <c r="C14" s="556" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="D14" s="409" t="n">
+      <c r="D14" s="556" t="n">
         <v>102.0946300000002</v>
       </c>
-      <c r="E14" s="409" t="n">
+      <c r="E14" s="556" t="n">
         <v>106.1784152000001</v>
       </c>
-      <c r="F14" s="409" t="n">
+      <c r="F14" s="556" t="n">
         <v>110.4255518080002</v>
       </c>
-      <c r="G14" s="409" t="n">
+      <c r="G14" s="556" t="n">
         <v>113.7383183622403</v>
       </c>
-      <c r="H14" s="409" t="n">
+      <c r="H14" s="556" t="n">
         <v>117.1504679131074</v>
       </c>
     </row>
@@ -11755,19 +12093,19 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="D15" s="409" t="n">
+      <c r="D15" s="556" t="n">
         <v>68.66250000000001</v>
       </c>
-      <c r="E15" s="409" t="n">
+      <c r="E15" s="556" t="n">
         <v>61.9920582975</v>
       </c>
-      <c r="F15" s="409" t="n">
+      <c r="F15" s="556" t="n">
         <v>54.51505963102687</v>
       </c>
-      <c r="G15" s="409" t="n">
+      <c r="G15" s="556" t="n">
         <v>46.1490476687412</v>
       </c>
-      <c r="H15" s="409" t="n">
+      <c r="H15" s="556" t="n">
         <v>36.91995724792738</v>
       </c>
     </row>
@@ -11777,19 +12115,19 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="D16" s="409" t="n">
+      <c r="D16" s="556" t="n">
         <v>26.41138270000011</v>
       </c>
-      <c r="E16" s="409" t="n">
+      <c r="E16" s="556" t="n">
         <v>34.90722195297506</v>
       </c>
-      <c r="F16" s="409" t="n">
+      <c r="F16" s="556" t="n">
         <v>44.16928881980895</v>
       </c>
-      <c r="G16" s="409" t="n">
+      <c r="G16" s="556" t="n">
         <v>53.39552384786428</v>
       </c>
-      <c r="H16" s="409" t="n">
+      <c r="H16" s="556" t="n">
         <v>63.38210342549219</v>
       </c>
     </row>
@@ -11799,19 +12137,19 @@
           <t>FCF (after interest)</t>
         </is>
       </c>
-      <c r="D17" s="414" t="n">
+      <c r="D17" s="559" t="n">
         <v>88.93922270000012</v>
       </c>
-      <c r="E17" s="414" t="n">
+      <c r="E17" s="559" t="n">
         <v>99.69331555297505</v>
       </c>
-      <c r="F17" s="414" t="n">
+      <c r="F17" s="559" t="n">
         <v>111.546826163809</v>
       </c>
-      <c r="G17" s="414" t="n">
+      <c r="G17" s="559" t="n">
         <v>123.0545389441843</v>
       </c>
-      <c r="H17" s="414" t="n">
+      <c r="H17" s="559" t="n">
         <v>135.1308889747018</v>
       </c>
     </row>
@@ -11821,19 +12159,19 @@
           <t>Debt paydown</t>
         </is>
       </c>
-      <c r="D18" s="409" t="n">
+      <c r="D18" s="556" t="n">
         <v>88.93922270000012</v>
       </c>
-      <c r="E18" s="409" t="n">
+      <c r="E18" s="556" t="n">
         <v>99.69331555297505</v>
       </c>
-      <c r="F18" s="409" t="n">
+      <c r="F18" s="556" t="n">
         <v>111.546826163809</v>
       </c>
-      <c r="G18" s="409" t="n">
+      <c r="G18" s="556" t="n">
         <v>123.0545389441843</v>
       </c>
-      <c r="H18" s="409" t="n">
+      <c r="H18" s="556" t="n">
         <v>135.1308889747018</v>
       </c>
     </row>
@@ -11843,22 +12181,22 @@
           <t>Debt end</t>
         </is>
       </c>
-      <c r="C19" s="409" t="n">
+      <c r="C19" s="556" t="n">
         <v>1329.9</v>
       </c>
-      <c r="D19" s="409" t="n">
+      <c r="D19" s="556" t="n">
         <v>826.5607773</v>
       </c>
-      <c r="E19" s="409" t="n">
+      <c r="E19" s="556" t="n">
         <v>726.867461747025</v>
       </c>
-      <c r="F19" s="409" t="n">
+      <c r="F19" s="556" t="n">
         <v>615.320635583216</v>
       </c>
-      <c r="G19" s="409" t="n">
+      <c r="G19" s="556" t="n">
         <v>492.2660966390317</v>
       </c>
-      <c r="H19" s="409" t="n">
+      <c r="H19" s="556" t="n">
         <v>357.1352076643299</v>
       </c>
     </row>
@@ -11932,22 +12270,22 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="409" t="n">
+      <c r="C5" s="556" t="n">
         <v>1214.3</v>
       </c>
-      <c r="D5" s="409" t="n">
+      <c r="D5" s="556" t="n">
         <v>1250.729</v>
       </c>
-      <c r="E5" s="409" t="n">
+      <c r="E5" s="556" t="n">
         <v>1300.75816</v>
       </c>
-      <c r="F5" s="409" t="n">
+      <c r="F5" s="556" t="n">
         <v>1352.7884864</v>
       </c>
-      <c r="G5" s="409" t="n">
+      <c r="G5" s="556" t="n">
         <v>1393.372140992</v>
       </c>
-      <c r="H5" s="409" t="n">
+      <c r="H5" s="556" t="n">
         <v>1435.173305221761</v>
       </c>
     </row>
@@ -11957,22 +12295,22 @@
           <t>COGS</t>
         </is>
       </c>
-      <c r="C6" s="409" t="n">
+      <c r="C6" s="556" t="n">
         <v>189.8</v>
       </c>
-      <c r="D6" s="409" t="n">
+      <c r="D6" s="556" t="n">
         <v>195.4939999999999</v>
       </c>
-      <c r="E6" s="409" t="n">
+      <c r="E6" s="556" t="n">
         <v>203.31376</v>
       </c>
-      <c r="F6" s="409" t="n">
+      <c r="F6" s="556" t="n">
         <v>211.4463104</v>
       </c>
-      <c r="G6" s="409" t="n">
+      <c r="G6" s="556" t="n">
         <v>217.789699712</v>
       </c>
-      <c r="H6" s="409" t="n">
+      <c r="H6" s="556" t="n">
         <v>224.32339070336</v>
       </c>
     </row>
@@ -11982,22 +12320,22 @@
           <t>S&amp;M (human)</t>
         </is>
       </c>
-      <c r="C7" s="409" t="n">
+      <c r="C7" s="556" t="n">
         <v>425</v>
       </c>
-      <c r="D7" s="409" t="n">
+      <c r="D7" s="556" t="n">
         <v>361.25</v>
       </c>
-      <c r="E7" s="409" t="n">
+      <c r="E7" s="556" t="n">
         <v>368.475</v>
       </c>
-      <c r="F7" s="409" t="n">
+      <c r="F7" s="556" t="n">
         <v>375.8445</v>
       </c>
-      <c r="G7" s="409" t="n">
+      <c r="G7" s="556" t="n">
         <v>383.36139</v>
       </c>
-      <c r="H7" s="409" t="n">
+      <c r="H7" s="556" t="n">
         <v>391.0286178000001</v>
       </c>
     </row>
@@ -12007,22 +12345,22 @@
           <t>AI agent cost</t>
         </is>
       </c>
-      <c r="C8" s="409" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="409" t="n">
+      <c r="C8" s="556" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="556" t="n">
         <v>15</v>
       </c>
-      <c r="E8" s="409" t="n">
+      <c r="E8" s="556" t="n">
         <v>15</v>
       </c>
-      <c r="F8" s="409" t="n">
+      <c r="F8" s="556" t="n">
         <v>15</v>
       </c>
-      <c r="G8" s="409" t="n">
+      <c r="G8" s="556" t="n">
         <v>15</v>
       </c>
-      <c r="H8" s="409" t="n">
+      <c r="H8" s="556" t="n">
         <v>15</v>
       </c>
     </row>
@@ -12032,22 +12370,22 @@
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="C9" s="409" t="n">
+      <c r="C9" s="556" t="n">
         <v>196.1</v>
       </c>
-      <c r="D9" s="409" t="n">
+      <c r="D9" s="556" t="n">
         <v>201.983</v>
       </c>
-      <c r="E9" s="409" t="n">
+      <c r="E9" s="556" t="n">
         <v>210.06232</v>
       </c>
-      <c r="F9" s="409" t="n">
+      <c r="F9" s="556" t="n">
         <v>218.4648128</v>
       </c>
-      <c r="G9" s="409" t="n">
+      <c r="G9" s="556" t="n">
         <v>225.018757184</v>
       </c>
-      <c r="H9" s="409" t="n">
+      <c r="H9" s="556" t="n">
         <v>231.7693198995201</v>
       </c>
     </row>
@@ -12057,22 +12395,22 @@
           <t>G&amp;A</t>
         </is>
       </c>
-      <c r="C10" s="409" t="n">
+      <c r="C10" s="556" t="n">
         <v>295.3</v>
       </c>
-      <c r="D10" s="409" t="n">
+      <c r="D10" s="556" t="n">
         <v>225.13122</v>
       </c>
-      <c r="E10" s="409" t="n">
+      <c r="E10" s="556" t="n">
         <v>234.1364688</v>
       </c>
-      <c r="F10" s="409" t="n">
+      <c r="F10" s="556" t="n">
         <v>243.501927552</v>
       </c>
-      <c r="G10" s="409" t="n">
+      <c r="G10" s="556" t="n">
         <v>250.8069853785601</v>
       </c>
-      <c r="H10" s="409" t="n">
+      <c r="H10" s="556" t="n">
         <v>258.3311949399169</v>
       </c>
     </row>
@@ -12082,22 +12420,22 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="409" t="n">
+      <c r="C11" s="556" t="n">
         <v>183.1</v>
       </c>
-      <c r="D11" s="414" t="n">
+      <c r="D11" s="559" t="n">
         <v>251.8707800000001</v>
       </c>
-      <c r="E11" s="414" t="n">
+      <c r="E11" s="559" t="n">
         <v>269.7706112000001</v>
       </c>
-      <c r="F11" s="414" t="n">
+      <c r="F11" s="559" t="n">
         <v>288.5309356480003</v>
       </c>
-      <c r="G11" s="414" t="n">
+      <c r="G11" s="559" t="n">
         <v>301.3953087174403</v>
       </c>
-      <c r="H11" s="414" t="n">
+      <c r="H11" s="559" t="n">
         <v>314.7207818789635</v>
       </c>
     </row>
@@ -12132,22 +12470,22 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C13" s="409" t="n">
+      <c r="C13" s="556" t="n">
         <v>85.7</v>
       </c>
-      <c r="D13" s="409" t="n">
+      <c r="D13" s="556" t="n">
         <v>88.271</v>
       </c>
-      <c r="E13" s="409" t="n">
+      <c r="E13" s="556" t="n">
         <v>91.80184</v>
       </c>
-      <c r="F13" s="409" t="n">
+      <c r="F13" s="556" t="n">
         <v>95.47391360000002</v>
       </c>
-      <c r="G13" s="409" t="n">
+      <c r="G13" s="556" t="n">
         <v>98.33813100800002</v>
       </c>
-      <c r="H13" s="409" t="n">
+      <c r="H13" s="556" t="n">
         <v>101.28827493824</v>
       </c>
     </row>
@@ -12157,22 +12495,22 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="409" t="n">
+      <c r="C14" s="556" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="D14" s="409" t="n">
+      <c r="D14" s="556" t="n">
         <v>163.5997800000001</v>
       </c>
-      <c r="E14" s="409" t="n">
+      <c r="E14" s="556" t="n">
         <v>177.9687712000001</v>
       </c>
-      <c r="F14" s="409" t="n">
+      <c r="F14" s="556" t="n">
         <v>193.0570220480002</v>
       </c>
-      <c r="G14" s="409" t="n">
+      <c r="G14" s="556" t="n">
         <v>203.0571777094403</v>
       </c>
-      <c r="H14" s="409" t="n">
+      <c r="H14" s="556" t="n">
         <v>213.4325069407234</v>
       </c>
     </row>
@@ -12182,19 +12520,19 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="D15" s="409" t="n">
+      <c r="D15" s="556" t="n">
         <v>68.66250000000001</v>
       </c>
-      <c r="E15" s="409" t="n">
+      <c r="E15" s="556" t="n">
         <v>58.34787815999999</v>
       </c>
-      <c r="F15" s="409" t="n">
+      <c r="F15" s="556" t="n">
         <v>46.40138322737999</v>
       </c>
-      <c r="G15" s="409" t="n">
+      <c r="G15" s="556" t="n">
         <v>32.65872132645823</v>
       </c>
-      <c r="H15" s="409" t="n">
+      <c r="H15" s="556" t="n">
         <v>17.33818665354254</v>
       </c>
     </row>
@@ -12204,19 +12542,19 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="D16" s="409" t="n">
+      <c r="D16" s="556" t="n">
         <v>75.0004512000001</v>
       </c>
-      <c r="E16" s="409" t="n">
+      <c r="E16" s="556" t="n">
         <v>94.50050550160006</v>
       </c>
-      <c r="F16" s="409" t="n">
+      <c r="F16" s="556" t="n">
         <v>115.85795466829</v>
       </c>
-      <c r="G16" s="409" t="n">
+      <c r="G16" s="556" t="n">
         <v>134.6147805425558</v>
       </c>
-      <c r="H16" s="409" t="n">
+      <c r="H16" s="556" t="n">
         <v>154.9145130268729</v>
       </c>
     </row>
@@ -12226,19 +12564,19 @@
           <t>FCF (after interest)</t>
         </is>
       </c>
-      <c r="D17" s="414" t="n">
+      <c r="D17" s="559" t="n">
         <v>137.5282912000001</v>
       </c>
-      <c r="E17" s="414" t="n">
+      <c r="E17" s="559" t="n">
         <v>159.2865991016001</v>
       </c>
-      <c r="F17" s="414" t="n">
+      <c r="F17" s="559" t="n">
         <v>183.23549201229</v>
       </c>
-      <c r="G17" s="414" t="n">
+      <c r="G17" s="559" t="n">
         <v>204.2737956388759</v>
       </c>
-      <c r="H17" s="414" t="n">
+      <c r="H17" s="559" t="n">
         <v>226.6632985760825</v>
       </c>
     </row>
@@ -12248,19 +12586,19 @@
           <t>Debt paydown</t>
         </is>
       </c>
-      <c r="D18" s="409" t="n">
+      <c r="D18" s="556" t="n">
         <v>137.5282912000001</v>
       </c>
-      <c r="E18" s="409" t="n">
+      <c r="E18" s="556" t="n">
         <v>159.2865991016001</v>
       </c>
-      <c r="F18" s="409" t="n">
+      <c r="F18" s="556" t="n">
         <v>183.23549201229</v>
       </c>
-      <c r="G18" s="409" t="n">
+      <c r="G18" s="556" t="n">
         <v>204.2737956388759</v>
       </c>
-      <c r="H18" s="409" t="n">
+      <c r="H18" s="556" t="n">
         <v>226.6632985760825</v>
       </c>
     </row>
@@ -12270,22 +12608,22 @@
           <t>Debt end</t>
         </is>
       </c>
-      <c r="C19" s="409" t="n">
+      <c r="C19" s="556" t="n">
         <v>1329.9</v>
       </c>
-      <c r="D19" s="409" t="n">
+      <c r="D19" s="556" t="n">
         <v>777.9717088</v>
       </c>
-      <c r="E19" s="409" t="n">
+      <c r="E19" s="556" t="n">
         <v>618.6851096983999</v>
       </c>
-      <c r="F19" s="409" t="n">
+      <c r="F19" s="556" t="n">
         <v>435.4496176861098</v>
       </c>
-      <c r="G19" s="409" t="n">
+      <c r="G19" s="556" t="n">
         <v>231.1758220472339</v>
       </c>
-      <c r="H19" s="409" t="n">
+      <c r="H19" s="556" t="n">
         <v>4.512523471151439</v>
       </c>
     </row>
@@ -13098,7 +13436,6 @@
         <v>134.838525</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -15269,7 +15606,6 @@
         <v>987.5822307314286</v>
       </c>
     </row>
-    <row r="124"/>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
@@ -15336,7 +15672,6 @@
         <v>-223</v>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
@@ -15878,7 +16213,6 @@
         <v>586.7181807314284</v>
       </c>
     </row>
-    <row r="154"/>
     <row r="155">
       <c r="B155" s="34" t="inlineStr">
         <is>
@@ -16017,7 +16351,6 @@
         </is>
       </c>
     </row>
-    <row r="160"/>
     <row r="161">
       <c r="B161" s="321" t="inlineStr">
         <is>
@@ -19391,7 +19724,6 @@
         <v>0.2849090713511313</v>
       </c>
     </row>
-    <row r="318"/>
     <row r="319">
       <c r="B319" s="317" t="inlineStr">
         <is>
@@ -21880,7 +22212,6 @@
         <v>0.7748616857223557</v>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
@@ -22293,7 +22624,6 @@
         <v>36.4886239211832</v>
       </c>
     </row>
-    <row r="82"/>
     <row r="83" ht="17.25" customHeight="1" s="244">
       <c r="C83" s="112" t="inlineStr">
         <is>
@@ -22469,7 +22799,6 @@
       <c r="D93" s="93" t="n"/>
       <c r="E93" s="93" t="n"/>
     </row>
-    <row r="94"/>
     <row r="114">
       <c r="B114" s="108" t="n"/>
       <c r="C114" s="109" t="inlineStr">

--- a/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
+++ b/LBO/output/vengeanceaiUSC_LBOMODEL1.xlsx
@@ -8,18 +8,19 @@
   <sheets>
     <sheet name="Strategy_Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="00_Assumptions_List" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Debt_Sweep_AI" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Base_Operating" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="AI_Operating" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Coversheet" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="LBO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Shares" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="52wkHL" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Assumptions_Drivers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Debt_Sweep_AI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Base_Operating" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="AI_Operating" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Coversheet" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="LBO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DCF" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Shares" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="52wkHL" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <definedNames>
     <definedName name="CIQWBGuid" hidden="1">"a611639b-bab1-425e-aaa5-008c326fdfdb"</definedName>
@@ -58,7 +59,8 @@
     <definedName name="One">'[1]Forecast Drivers'!$D$330</definedName>
     <definedName name="Products">[2]Array0!$B$5:$C$7</definedName>
     <definedName name="Rev">'[1]Forecast Drivers'!$E$25:$S$25</definedName>
-    <definedName name="CIQWBGuid" localSheetId="5" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'00_Assumptions_List'!$B$6:$M$21</definedName>
+    <definedName name="CIQWBGuid" localSheetId="6" hidden="1">"ab508404-a108-4d4f-b84c-e5fce791e559"</definedName>
   </definedNames>
   <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1" iterate="1"/>
 </workbook>
@@ -66,7 +68,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="82">
+  <numFmts count="83">
     <numFmt numFmtId="164" formatCode="#,##0.0_);\(#,##0.0\);@_)"/>
     <numFmt numFmtId="165" formatCode="0.0%_);\(0.0%\);@_)"/>
     <numFmt numFmtId="166" formatCode="0\A;[Red]0\A"/>
@@ -95,62 +97,63 @@
     <numFmt numFmtId="189" formatCode="0.000%"/>
     <numFmt numFmtId="190" formatCode="#,##0.0"/>
     <numFmt numFmtId="191" formatCode="0.00x"/>
-    <numFmt numFmtId="192" formatCode="#,##0.00_);\(#,##0\)"/>
-    <numFmt numFmtId="193" formatCode="#,##0.0%_);\(#,##0.0%\)"/>
-    <numFmt numFmtId="194" formatCode="0.0\ \x"/>
-    <numFmt numFmtId="195" formatCode="#,##0.00\ ;\(#,##0.00\)"/>
-    <numFmt numFmtId="196" formatCode="&quot;$&quot;#,##0.00\ ;\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="197" formatCode="0.0%_);\(0.0%\)"/>
-    <numFmt numFmtId="198" formatCode="0.000\ \x&quot;rate&quot;"/>
-    <numFmt numFmtId="199" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
-    <numFmt numFmtId="200" formatCode="0.00_);\(0.00\);0.00"/>
-    <numFmt numFmtId="201" formatCode="\C&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="202" formatCode="#,##0%_);\(#,##0.0%\)"/>
-    <numFmt numFmtId="203" formatCode="_(* #,##0.00000000_);_(* \(#,##0.00000000\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="204" formatCode="mmm\-d\-yyyy"/>
-    <numFmt numFmtId="205" formatCode="mmm\-yyyy"/>
-    <numFmt numFmtId="206" formatCode="yyyy"/>
-    <numFmt numFmtId="207" formatCode="0.00\x&quot;rate&quot;"/>
-    <numFmt numFmtId="208" formatCode="0.0&quot;  &quot;"/>
-    <numFmt numFmtId="209" formatCode="&quot;$&quot;#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="210" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="211" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="212" formatCode="&quot;$&quot;#,##0.00&quot;A&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;A&quot;"/>
-    <numFmt numFmtId="213" formatCode="#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="214" formatCode="&quot;$&quot;#,##0.00&quot;E&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;E&quot;"/>
-    <numFmt numFmtId="215" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="216" formatCode="#,##0.00;\(#,##0.00\)"/>
-    <numFmt numFmtId="217" formatCode=".%\,\(0.0%%;\t"/>
-    <numFmt numFmtId="218" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
-    <numFmt numFmtId="219" formatCode="0.0%_);[Red]\(0.0%\)"/>
-    <numFmt numFmtId="220" formatCode="0.00_);\(0.00\);0.00_)"/>
-    <numFmt numFmtId="221" formatCode="#,##0\x"/>
-    <numFmt numFmtId="222" formatCode="&quot;TKR&quot;\ 0"/>
-    <numFmt numFmtId="223" formatCode=".%\,\(0.%%;\t"/>
-    <numFmt numFmtId="224" formatCode="&quot;$&quot;#,###.0\ \ "/>
-    <numFmt numFmtId="225" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\)"/>
-    <numFmt numFmtId="226" formatCode="#,##0.000_);\(#,##0.000\)"/>
-    <numFmt numFmtId="227" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\);&quot;--  &quot;"/>
-    <numFmt numFmtId="228" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="229" formatCode="0.0\x_);[Red]\(0.0\x\)"/>
-    <numFmt numFmtId="230" formatCode="0.0\ "/>
-    <numFmt numFmtId="231" formatCode="&quot;$&quot;#,##0.0;\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="232" formatCode="#,##0.00%_);\(#,##0.00%\)"/>
-    <numFmt numFmtId="233" formatCode="0.00\%;\-0.00\%;0.00\%"/>
-    <numFmt numFmtId="234" formatCode="0.0%\ ;\(0.0%\)"/>
-    <numFmt numFmtId="235" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="236" formatCode="&quot;$&quot;0.00\ "/>
-    <numFmt numFmtId="237" formatCode="0.0\ \ \ \ \ "/>
-    <numFmt numFmtId="238" formatCode="0.00\x;\-0.00\x;0.00\x"/>
-    <numFmt numFmtId="239" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
-    <numFmt numFmtId="240" formatCode="#,##0.0_);\(#,##0.0\);_(* &quot;-&quot;_)"/>
-    <numFmt numFmtId="241" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="242" formatCode="0.00%_);[Red]\(0.00%\)"/>
-    <numFmt numFmtId="243" formatCode="#,##0.0\x_);\(#,##0.0\x\)"/>
-    <numFmt numFmtId="244" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
-    <numFmt numFmtId="245" formatCode="###0&quot;E&quot;_)"/>
+    <numFmt numFmtId="192" formatCode="0.0x"/>
+    <numFmt numFmtId="193" formatCode="#,##0.00_);\(#,##0\)"/>
+    <numFmt numFmtId="194" formatCode="#,##0.0%_);\(#,##0.0%\)"/>
+    <numFmt numFmtId="195" formatCode="0.0\ \x"/>
+    <numFmt numFmtId="196" formatCode="#,##0.00\ ;\(#,##0.00\)"/>
+    <numFmt numFmtId="197" formatCode="&quot;$&quot;#,##0.00\ ;\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="198" formatCode="0.0%_);\(0.0%\)"/>
+    <numFmt numFmtId="199" formatCode="0.000\ \x&quot;rate&quot;"/>
+    <numFmt numFmtId="200" formatCode="#,##0.000_);[Red]\(#,##0.000\)"/>
+    <numFmt numFmtId="201" formatCode="0.00_);\(0.00\);0.00"/>
+    <numFmt numFmtId="202" formatCode="\C&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="203" formatCode="#,##0%_);\(#,##0.0%\)"/>
+    <numFmt numFmtId="204" formatCode="_(* #,##0.00000000_);_(* \(#,##0.00000000\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="205" formatCode="mmm\-d\-yyyy"/>
+    <numFmt numFmtId="206" formatCode="mmm\-yyyy"/>
+    <numFmt numFmtId="207" formatCode="yyyy"/>
+    <numFmt numFmtId="208" formatCode="0.00\x&quot;rate&quot;"/>
+    <numFmt numFmtId="209" formatCode="0.0&quot;  &quot;"/>
+    <numFmt numFmtId="210" formatCode="&quot;$&quot;#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="211" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="212" formatCode="&quot;$&quot;#,##0.000_);[Red]\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="213" formatCode="&quot;$&quot;#,##0.00&quot;A&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;A&quot;"/>
+    <numFmt numFmtId="214" formatCode="#,##0.0\ ;[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="215" formatCode="&quot;$&quot;#,##0.00&quot;E&quot;;[Red]\(&quot;$&quot;#,##0.00\)&quot;E&quot;"/>
+    <numFmt numFmtId="216" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="217" formatCode="#,##0.00;\(#,##0.00\)"/>
+    <numFmt numFmtId="218" formatCode=".%\,\(0.0%%;\t"/>
+    <numFmt numFmtId="219" formatCode="#,##0.0_);[Red]\(#,##0.0\)"/>
+    <numFmt numFmtId="220" formatCode="0.0%_);[Red]\(0.0%\)"/>
+    <numFmt numFmtId="221" formatCode="0.00_);\(0.00\);0.00_)"/>
+    <numFmt numFmtId="222" formatCode="#,##0\x"/>
+    <numFmt numFmtId="223" formatCode="&quot;TKR&quot;\ 0"/>
+    <numFmt numFmtId="224" formatCode=".%\,\(0.%%;\t"/>
+    <numFmt numFmtId="225" formatCode="&quot;$&quot;#,###.0\ \ "/>
+    <numFmt numFmtId="226" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\)"/>
+    <numFmt numFmtId="227" formatCode="#,##0.000_);\(#,##0.000\)"/>
+    <numFmt numFmtId="228" formatCode="#,##0.00\x_);[Red]\(#,##0.00\x\);&quot;--  &quot;"/>
+    <numFmt numFmtId="229" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="230" formatCode="0.0\x_);[Red]\(0.0\x\)"/>
+    <numFmt numFmtId="231" formatCode="0.0\ "/>
+    <numFmt numFmtId="232" formatCode="&quot;$&quot;#,##0.0;\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="233" formatCode="#,##0.00%_);\(#,##0.00%\)"/>
+    <numFmt numFmtId="234" formatCode="0.00\%;\-0.00\%;0.00\%"/>
+    <numFmt numFmtId="235" formatCode="0.0%\ ;\(0.0%\)"/>
+    <numFmt numFmtId="236" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="237" formatCode="&quot;$&quot;0.00\ "/>
+    <numFmt numFmtId="238" formatCode="0.0\ \ \ \ \ "/>
+    <numFmt numFmtId="239" formatCode="0.00\x;\-0.00\x;0.00\x"/>
+    <numFmt numFmtId="240" formatCode="&quot;$&quot;#,##0.000_);\(&quot;$&quot;#,##0.000\)"/>
+    <numFmt numFmtId="241" formatCode="#,##0.0_);\(#,##0.0\);_(* &quot;-&quot;_)"/>
+    <numFmt numFmtId="242" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="243" formatCode="0.00%_);[Red]\(0.00%\)"/>
+    <numFmt numFmtId="244" formatCode="#,##0.0\x_);\(#,##0.0\x\)"/>
+    <numFmt numFmtId="245" formatCode="#,##0.00\x_);\(#,##0.00\x\)"/>
+    <numFmt numFmtId="246" formatCode="###0&quot;E&quot;_)"/>
   </numFmts>
-  <fonts count="107">
+  <fonts count="109">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -845,8 +848,20 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -1039,6 +1054,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7F3FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1452,19 +1472,19 @@
   <cellStyleXfs count="187">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="192" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="193" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="193" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="194" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="193" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="195" fontId="10" fillId="2" borderId="0"/>
-    <xf numFmtId="196" fontId="10" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="194" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="196" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="197" fontId="10" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="197" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="198" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="198" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="199" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0"/>
@@ -1491,7 +1511,7 @@
     <xf numFmtId="0" fontId="15" fillId="20" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0"/>
-    <xf numFmtId="199" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="200" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1500,10 +1520,10 @@
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="5"/>
-    <xf numFmtId="199" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="200" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="199" fontId="17" fillId="0" borderId="6"/>
+    <xf numFmtId="200" fontId="17" fillId="0" borderId="6"/>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="7"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1521,35 +1541,35 @@
     <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="200" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="201" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="7" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="5" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="201" fontId="13" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="202" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="202" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="203" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="202" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="204" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="203" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="15" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="204" fontId="25" fillId="24" borderId="0"/>
-    <xf numFmtId="205" fontId="27" fillId="0" borderId="8"/>
+    <xf numFmtId="205" fontId="25" fillId="24" borderId="0"/>
+    <xf numFmtId="206" fontId="27" fillId="0" borderId="8"/>
     <xf numFmtId="14" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="206" fontId="28" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="207" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="207" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="208" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1557,48 +1577,48 @@
     <xf numFmtId="6" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="7" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="208" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="209" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="210" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="209" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="210" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="211" fontId="10" fillId="25" borderId="0"/>
-    <xf numFmtId="212" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="212" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="213" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="213" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="214" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="214" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="215" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="215" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="216" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="197" fontId="10" fillId="0" borderId="10"/>
-    <xf numFmtId="216" fontId="10" fillId="2" borderId="9" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="198" fontId="10" fillId="0" borderId="10"/>
     <xf numFmtId="217" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="216" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="218" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="218" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="217" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="219" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="5" borderId="0"/>
-    <xf numFmtId="219" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="197" fontId="32" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="220" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="198" fontId="32" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="218" fontId="13" fillId="26" borderId="11"/>
+    <xf numFmtId="219" fontId="13" fillId="26" borderId="11"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="12"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="13"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="14"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
-    <xf numFmtId="218" fontId="36" fillId="0" borderId="0"/>
+    <xf numFmtId="219" fontId="36" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
-    <xf numFmtId="199" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="200" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
@@ -1612,7 +1632,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="17" fontId="39" fillId="27" borderId="0"/>
-    <xf numFmtId="220" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="221" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -1623,26 +1643,26 @@
     <xf numFmtId="173" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="221" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="222" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="222" fontId="10" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="223" fontId="10" fillId="25" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="223" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="224" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="221" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="222" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="197" fontId="42" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="198" fontId="42" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="197" fontId="42" fillId="0" borderId="0"/>
-    <xf numFmtId="224" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="198" fontId="42" fillId="0" borderId="0"/>
+    <xf numFmtId="225" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="225" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="226" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="1" hidden="1"/>
@@ -1651,62 +1671,62 @@
     <xf numFmtId="37" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="175" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="39" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="226" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="227" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="227" fontId="25" fillId="0" borderId="0"/>
+    <xf numFmtId="228" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="29" borderId="17"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
-    <xf numFmtId="228" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="229" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="44" fillId="21" borderId="18"/>
-    <xf numFmtId="229" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="230" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
-    <xf numFmtId="230" fontId="10" fillId="25" borderId="0"/>
+    <xf numFmtId="231" fontId="10" fillId="25" borderId="0"/>
     <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="231" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="232" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="193" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="232" fontId="12" fillId="0" borderId="0"/>
-    <xf numFmtId="233" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="194" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="233" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="234" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="220" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
+    <xf numFmtId="200" fontId="17" fillId="0" borderId="0" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="219" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="8" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="199" fontId="17" fillId="0" borderId="0" applyProtection="1">
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="218" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="195" fontId="10" fillId="2" borderId="19" applyAlignment="1">
+    <xf numFmtId="196" fontId="10" fillId="2" borderId="19" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="234" fontId="46" fillId="2" borderId="0"/>
-    <xf numFmtId="235" fontId="10" fillId="2" borderId="0"/>
+    <xf numFmtId="235" fontId="46" fillId="2" borderId="0"/>
+    <xf numFmtId="236" fontId="10" fillId="2" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="236" fontId="10" fillId="2" borderId="0" applyAlignment="1">
+    <xf numFmtId="237" fontId="10" fillId="2" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="237" fontId="10" fillId="2" borderId="9" applyAlignment="1">
+    <xf numFmtId="238" fontId="10" fillId="2" borderId="9" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="238" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="239" fontId="12" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="218" fontId="28" fillId="0" borderId="0"/>
+    <xf numFmtId="219" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1714,10 +1734,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="1" hidden="1"/>
     </xf>
-    <xf numFmtId="199" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="200" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="239" fontId="28" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="240" fontId="28" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="38" fontId="12" fillId="0" borderId="0"/>
@@ -1735,40 +1755,40 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="240" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="241" fontId="55" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="241" fontId="55" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="242" fontId="55" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="25" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="211" fontId="56" fillId="0" borderId="0"/>
-    <xf numFmtId="242" fontId="57" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="212" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="243" fontId="57" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="242" fontId="57" fillId="0" borderId="0"/>
-    <xf numFmtId="242" fontId="58" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="243" fontId="57" fillId="0" borderId="0"/>
+    <xf numFmtId="243" fontId="58" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="242" fontId="58" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="243" fontId="58" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="218" fontId="17" fillId="0" borderId="0" applyProtection="1">
+    <xf numFmtId="219" fontId="17" fillId="0" borderId="0" applyProtection="1">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="218" fontId="56" fillId="0" borderId="0"/>
+    <xf numFmtId="219" fontId="56" fillId="0" borderId="0"/>
     <xf numFmtId="49" fontId="59" fillId="0" borderId="0"/>
-    <xf numFmtId="243" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="244" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="245" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="61" fillId="1" borderId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="218" fontId="62" fillId="0" borderId="0"/>
+    <xf numFmtId="219" fontId="62" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="38" fontId="63" fillId="0" borderId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1777,10 +1797,10 @@
     <xf numFmtId="0" fontId="65" fillId="0" borderId="21"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="245" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="239" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="246" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="240" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="563">
+  <cellXfs count="585">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2769,6 +2789,38 @@
     <xf numFmtId="191" fontId="101" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="191" fontId="101" fillId="36" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="106" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="190" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="191" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="38" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="104" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="104" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="192" fontId="104" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="34" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="190" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="34" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="192" fontId="104" fillId="37" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="187">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3117,127 +3169,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ZoomInfo LBOMODEL1 — Base vs AI-SDR Strategy</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Strategy_Summary'!C49</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Strategy_Summary'!$B$50:$B$55</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Strategy_Summary'!$C$50:$C$55</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Strategy_Summary'!D49</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Strategy_Summary'!$B$50:$B$55</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Strategy_Summary'!$D$50:$D$55</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Value</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -4306,33 +4237,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6480000" cy="3600000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>1</col>
@@ -4965,662 +4869,574 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F55"/>
+  <dimension ref="B2:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="48" customWidth="1" style="244" min="2" max="2"/>
-    <col width="16" customWidth="1" style="244" min="3" max="3"/>
-    <col width="16" customWidth="1" style="244" min="4" max="4"/>
+    <col width="32" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="14" customWidth="1" style="244" min="4" max="4"/>
     <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="78" customWidth="1" style="244" min="6" max="6"/>
+    <col width="70" customWidth="1" style="244" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="406" t="inlineStr">
-        <is>
-          <t>vengeanceaiUSC-LBOMODEL1 — ZoomInfo AI-SDR LBO Strategy</t>
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — Strategy Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Take-private LBO: slash outbound SDR S&amp;M, replace with AI agents, ≥500 bps EBITDA margin → higher FCF → faster debt paydown → higher IRR</t>
+          <t>AI-SDR cost takeout drives margin, FCF, debt paydown, MOIC/IRR — exit multiple held at 13x in both cases</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="407" t="inlineStr">
-        <is>
-          <t>THESIS</t>
+      <c r="B5" s="564" t="inlineStr">
+        <is>
+          <t>RESULTS — AI vs Base</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Replacing human SDRs with AI agents to drive 500+ bps EBITDA margin expansion.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C6" s="412" t="inlineStr">
+        <is>
+          <t>Base (no AI)</t>
+        </is>
+      </c>
+      <c r="D6" s="412" t="inlineStr">
+        <is>
+          <t>AI-SDR case</t>
+        </is>
+      </c>
+      <c r="E6" s="412" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="F6" s="412" t="inlineStr">
+        <is>
+          <t>COMMENTARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="244">
       <c r="B7" t="inlineStr">
         <is>
-          <t>S&amp;M is the largest SaaS opex lever → lower CAC → higher FCF → sweep debt → juice LBO IRR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="407" t="inlineStr">
-        <is>
-          <t>ENTRY (ZoomInfo FY2024 10-K baseline + latest BS)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="408" t="inlineStr">
-        <is>
-          <t>Revenue (FY2024)</t>
-        </is>
-      </c>
-      <c r="C10" s="556" t="n">
-        <v>1214.3</v>
-      </c>
-      <c r="D10" s="408" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="408" t="inlineStr">
-        <is>
-          <t>Gross Profit / GM</t>
-        </is>
-      </c>
-      <c r="C11" s="410" t="inlineStr">
-        <is>
-          <t>1024.5 / 84.4%</t>
-        </is>
-      </c>
-      <c r="D11" s="408" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="408" t="inlineStr">
-        <is>
-          <t>GAAP Operating Income</t>
-        </is>
-      </c>
-      <c r="C12" s="556" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="D12" s="408" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="408" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C13" s="556" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="D13" s="408" t="inlineStr">
-        <is>
-          <t>XBRL OtherDepreciationAndAmortization</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="408" t="inlineStr">
-        <is>
-          <t>Baseline EBITDA (OpInc+D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C14" s="556" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="D14" s="408" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="408" t="inlineStr">
-        <is>
-          <t>Baseline EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C15" s="411" t="n">
-        <v>0.1508</v>
-      </c>
-      <c r="D15" s="408" t="inlineStr">
-        <is>
-          <t>Calculated</t>
+          <t>Y2 EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C7" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+      <c r="D7" s="565" t="n">
+        <v>0.2012029241075531</v>
+      </c>
+      <c r="E7" s="565" t="n">
+        <v>0.09269102424755141</v>
+      </c>
+      <c r="F7" s="566" t="inlineStr">
+        <is>
+          <t>Year 2 operating profitability under 10% growth / 80% GM / AI S&amp;M path.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="244">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Y2 margin vs baseline (bps)</t>
+        </is>
+      </c>
+      <c r="C8" s="567" t="n">
+        <v>-422.7456147574727</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>504.1646277180415</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>926.9102424755141</v>
+      </c>
+      <c r="F8" s="566" t="inlineStr">
+        <is>
+          <t>Y2 EBITDA margin minus FY24 baseline margin, in basis points (target ≥500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="244">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Y5 EBITDA ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="567" t="n">
+        <v>212.2104606600003</v>
+      </c>
+      <c r="D9" s="567" t="n">
+        <v>496.3963076296004</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>284.1858469696001</v>
+      </c>
+      <c r="F9" s="566" t="inlineStr">
+        <is>
+          <t>Year 5 EBITDA ($m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="244">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Exit EV @ 13x ($m)</t>
+        </is>
+      </c>
+      <c r="C10" s="567" t="n">
+        <v>2758.735988580003</v>
+      </c>
+      <c r="D10" s="567" t="n">
+        <v>6453.151999184804</v>
+      </c>
+      <c r="E10" s="567" t="n">
+        <v>3694.416010604801</v>
+      </c>
+      <c r="F10" s="566" t="inlineStr">
+        <is>
+          <t>Exit EV = Y5 EBITDA × 13x (Assumptions_Drivers!C20 / LBO!D17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="244">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Exit net debt ($m)</t>
+        </is>
+      </c>
+      <c r="C11" s="567" t="n">
+        <v>557.1124750633038</v>
+      </c>
+      <c r="D11" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="567" t="n">
+        <v>-557.1124750633038</v>
+      </c>
+      <c r="F11" s="566" t="inlineStr">
+        <is>
+          <t>Ending net debt after mandatory amort + 100% cash sweep.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="244">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Exit equity value ($m)</t>
+        </is>
+      </c>
+      <c r="C12" s="567" t="n">
+        <v>2201.623513516699</v>
+      </c>
+      <c r="D12" s="567" t="n">
+        <v>6453.151999184804</v>
+      </c>
+      <c r="E12" s="567" t="n">
+        <v>4251.528485668105</v>
+      </c>
+      <c r="F12" s="566" t="inlineStr">
+        <is>
+          <t>Exit equity = Exit EV − ending debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="244">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MOIC</t>
+        </is>
+      </c>
+      <c r="C13" s="568" t="n">
+        <v>1.17652754423803</v>
+      </c>
+      <c r="D13" s="568" t="n">
+        <v>3.448505626681045</v>
+      </c>
+      <c r="E13" s="568" t="n">
+        <v>2.271978082443015</v>
+      </c>
+      <c r="F13" s="566" t="inlineStr">
+        <is>
+          <t>MOIC = Exit equity / sponsor equity check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="244">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IRR (5-year)</t>
+        </is>
+      </c>
+      <c r="C14" s="565" t="n">
+        <v>0.03304780632992022</v>
+      </c>
+      <c r="D14" s="565" t="n">
+        <v>0.2809323319237782</v>
+      </c>
+      <c r="E14" s="565" t="n">
+        <v>0.247884525593858</v>
+      </c>
+      <c r="F14" s="566" t="inlineStr">
+        <is>
+          <t>IRR over 5 years = MOIC^(1/5) − 1.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="408" t="inlineStr">
-        <is>
-          <t>S&amp;M baseline (35% of rev)</t>
-        </is>
-      </c>
-      <c r="C16" s="556" t="n">
-        <v>425</v>
-      </c>
-      <c r="D16" s="408" t="inlineStr">
-        <is>
-          <t>Prompt: ~35% / ~$425m</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="408" t="inlineStr">
-        <is>
-          <t>Share price / shares (m)</t>
-        </is>
-      </c>
-      <c r="C17" s="410" t="inlineStr">
-        <is>
-          <t>$4.05 / 307.294</t>
-        </is>
-      </c>
-      <c r="D17" s="408" t="inlineStr">
-        <is>
-          <t>Market + 10-K shares</t>
+      <c r="B16" s="569" t="inlineStr">
+        <is>
+          <t>IRR uplift from AI S&amp;M: 24.8 percentage points | Y2 margin expansion: 504 bps (target ≥500: YES)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="408" t="inlineStr">
-        <is>
-          <t>Offer (25% premium)</t>
-        </is>
-      </c>
-      <c r="C18" s="410" t="inlineStr">
-        <is>
-          <t>$5.0625</t>
-        </is>
-      </c>
-      <c r="D18" s="408" t="inlineStr">
-        <is>
-          <t>Assumption</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PDF assumptions list:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="408" t="inlineStr">
-        <is>
-          <t>Gross debt / cash</t>
-        </is>
-      </c>
-      <c r="C19" s="410" t="inlineStr">
-        <is>
-          <t>1329.9 / 179.9</t>
-        </is>
-      </c>
-      <c r="D19" s="408" t="inlineStr">
-        <is>
-          <t>YE2025 10-K/Q</t>
+      <c r="B19" s="570" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="408" t="inlineStr">
-        <is>
-          <t>Sponsor equity check</t>
-        </is>
-      </c>
-      <c r="C20" s="556" t="n">
-        <v>1871.3</v>
-      </c>
-      <c r="D20" s="408" t="inlineStr">
-        <is>
-          <t>Uses − excess cash − new debt</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="408" t="inlineStr">
-        <is>
-          <t>New debt (5.0x EBITDA)</t>
-        </is>
-      </c>
-      <c r="C21" s="556" t="n">
-        <v>915.5</v>
-      </c>
-      <c r="D21" s="408" t="inlineStr">
-        <is>
-          <t>TLA 2.5x + TLB 1.5x + Notes 1.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="408" t="inlineStr">
-        <is>
-          <t>Exit multiple</t>
-        </is>
-      </c>
-      <c r="C22" s="410" t="inlineStr">
-        <is>
-          <t>13.0x</t>
-        </is>
-      </c>
-      <c r="D22" s="408" t="inlineStr">
-        <is>
-          <t>Mid of 12–14x software band</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="407" t="inlineStr">
-        <is>
-          <t>AI STRATEGY RULES (as specified)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Y1: cut S&amp;M 15% vs baseline $425m; add $15m AI software/compute cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Y2–Y5: S&amp;M grows only 2%/yr (AI scales without headcount)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Target: ≥500 bps EBITDA margin expansion by Year 2 vs baseline year</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="407" t="inlineStr">
-        <is>
-          <t>RESULTS — AI case vs Base (no AI) case</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="412" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C30" s="412" t="inlineStr">
-        <is>
-          <t>Base (no AI)</t>
-        </is>
-      </c>
-      <c r="D30" s="412" t="inlineStr">
-        <is>
-          <t>AI-SDR case</t>
-        </is>
-      </c>
-      <c r="E30" s="412" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="F30" s="557" t="inlineStr">
-        <is>
-          <t>COMMENTARY</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="48" customHeight="1" s="244">
-      <c r="B31" s="408" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C31" s="411" t="n">
-        <v>0.1522037387795438</v>
-      </c>
-      <c r="D31" s="413" t="n">
-        <v>0.2073949020623481</v>
-      </c>
-      <c r="E31" s="411" t="n">
-        <v>0.05519116328280424</v>
-      </c>
-      <c r="F31" s="558" t="inlineStr">
-        <is>
-          <t>Year 2 operating profitability; the AI strategy drove this from 15.2% to 20.7%, expanding the margin by 5.5%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="48" customHeight="1" s="244">
-      <c r="B32" s="408" t="inlineStr">
-        <is>
-          <t>Y2 margin vs baseline (bps)</t>
-        </is>
-      </c>
-      <c r="C32" s="556" t="n">
-        <v>14.17277443794801</v>
-      </c>
-      <c r="D32" s="559" t="n">
-        <v>566.0844072659904</v>
-      </c>
-      <c r="E32" s="556" t="n">
-        <v>551.9116328280425</v>
-      </c>
-      <c r="F32" s="558" t="inlineStr">
-        <is>
-          <t>The difference from baseline margin; AI implementation increased this metric by 551.9 basis points to reach 566.1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="48" customHeight="1" s="244">
-      <c r="B33" s="408" t="inlineStr">
-        <is>
-          <t>Y5 EBITDA ($m)</t>
-        </is>
-      </c>
-      <c r="C33" s="556" t="n">
-        <v>218.4</v>
-      </c>
-      <c r="D33" s="559" t="n">
-        <v>314.7</v>
-      </c>
-      <c r="E33" s="556" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="F33" s="558" t="inlineStr">
-        <is>
-          <t>Year 5 operating cash flow; AI-driven cost savings boosted this figure by $96.3 million to $314.7 million.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1" s="244">
-      <c r="B34" s="408" t="inlineStr">
-        <is>
-          <t>Exit EV @ 13x ($m)</t>
-        </is>
-      </c>
-      <c r="C34" s="556" t="n">
-        <v>2839.7</v>
-      </c>
-      <c r="D34" s="559" t="n">
-        <v>4091.4</v>
-      </c>
-      <c r="E34" s="556" t="n">
-        <v>1251.7</v>
-      </c>
-      <c r="F34" s="558" t="inlineStr">
-        <is>
-          <t>Projected exit Enterprise Value; higher EBITDA from AI increased this valuation by $1,251.7 million to $4,091.4 million.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="48" customHeight="1" s="244">
-      <c r="B35" s="408" t="inlineStr">
-        <is>
-          <t>Exit net debt ($m)</t>
-        </is>
-      </c>
-      <c r="C35" s="556" t="n">
-        <v>357.1</v>
-      </c>
-      <c r="D35" s="559" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E35" s="556" t="n">
-        <v>-352.6</v>
-      </c>
-      <c r="F35" s="558" t="inlineStr">
-        <is>
-          <t>Remaining debt balance at exit; higher cash flow from the AI strategy paid down an extra $352.6 million.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="48" customHeight="1" s="244">
-      <c r="B36" s="408" t="inlineStr">
-        <is>
-          <t>Exit equity value ($m)</t>
-        </is>
-      </c>
-      <c r="C36" s="556" t="n">
-        <v>2482.6</v>
-      </c>
-      <c r="D36" s="559" t="n">
-        <v>4086.9</v>
-      </c>
-      <c r="E36" s="556" t="n">
-        <v>1604.3</v>
-      </c>
-      <c r="F36" s="558" t="inlineStr">
-        <is>
-          <t>Total payout to equity holders; the AI strategy increased this final payout by $1,604.3 million to $4,086.9 million.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="48" customHeight="1" s="244">
-      <c r="B37" s="408" t="inlineStr">
-        <is>
-          <t>MOIC</t>
-        </is>
-      </c>
-      <c r="C37" s="560" t="n">
-        <v>1.326661957981033</v>
-      </c>
-      <c r="D37" s="561" t="n">
-        <v>2.183979483523617</v>
-      </c>
-      <c r="E37" s="560" t="n">
-        <v>0.8573175255425849</v>
-      </c>
-      <c r="F37" s="558" t="inlineStr">
-        <is>
-          <t>Multiple on Invested Capital; the AI strategy significantly improved the total gross cash return from 1.33x to 2.18x.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="48" customHeight="1" s="244">
-      <c r="B38" s="408" t="inlineStr">
-        <is>
-          <t>IRR</t>
-        </is>
-      </c>
-      <c r="C38" s="411" t="n">
-        <v>0.05816174124246998</v>
-      </c>
-      <c r="D38" s="413" t="n">
-        <v>0.1690947516165904</v>
-      </c>
-      <c r="E38" s="411" t="n">
-        <v>0.1109330103741204</v>
-      </c>
-      <c r="F38" s="558" t="inlineStr">
-        <is>
-          <t>Annualized compound return rate over a 5-year period; replacing human SDRs with AI boosted this return by 11.1 percentage points to 16.9%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="562" t="inlineStr">
-        <is>
-          <t>The IRR is calculated over a 5-year period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="417" t="inlineStr">
-        <is>
-          <t>IRR POINTS FROM AI-DRIVEN S&amp;M REDUCTION</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="418" t="inlineStr">
-        <is>
-          <t>AI case IRR 16.9% − Base IRR 5.8% = 11.1 percentage points of IRR</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="418" t="inlineStr">
-        <is>
-          <t>Y2 AI EBITDA margin 20.7% vs baseline 15.1% = 566 bps (target ≥500: YES)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>See AI_Operating, Base_Operating, Debt_Sweep_AI, LBO, 00_Assumptions_List</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="419" t="inlineStr">
-        <is>
-          <t>10-K: https://www.sec.gov/Archives/edgar/data/1794515/000179451525000045/zi-20241231.htm</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>PDF version of this Strategy Summary + Commentary:</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="419" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_STRATEGY_SUMMARY.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="407" t="inlineStr">
-        <is>
-          <t>CHART DATA (Base vs AI-SDR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="412" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C49" s="412" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D49" s="412" t="inlineStr">
-        <is>
-          <t>AI-SDR</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Y2 EBITDA margin %</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="D50" t="n">
-        <v>20.7</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Y5 EBITDA $m</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>218.4</v>
-      </c>
-      <c r="D51" t="n">
-        <v>314.7</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Exit EV $m</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2839.7</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4091.4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Exit equity $m</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2482.6</v>
-      </c>
-      <c r="D53" t="n">
-        <v>4086.9</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>MOIC (x)</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>IRR %</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="D55" t="n">
-        <v>16.9</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>In-Excel full commentary: 00_Assumptions_List | Drivers: Assumptions_Drivers</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
+    <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
+    <col width="15.85546875" customWidth="1" style="244" min="3" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="244" thickBot="1"/>
+    <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Diluted shares for BMC</t>
+        </is>
+      </c>
+      <c r="C2" s="305" t="n"/>
+      <c r="D2" s="305" t="n"/>
+      <c r="E2" s="305" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="302" t="inlineStr">
+        <is>
+          <t>$ mm except per share</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="34" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Offer price</t>
+        </is>
+      </c>
+      <c r="E5" s="513" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="304" t="inlineStr">
+        <is>
+          <t>Model-derived offer value sanity check</t>
+        </is>
+      </c>
+      <c r="E6" s="554" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="159" t="inlineStr">
+        <is>
+          <t>Basic shares outstanding (latest filing)</t>
+        </is>
+      </c>
+      <c r="E7" s="522" t="n">
+        <v>143.973</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>In-the-money exercisable options</t>
+        </is>
+      </c>
+      <c r="E8" s="521" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Total proceeds ($mm)</t>
+        </is>
+      </c>
+      <c r="E9" s="461" t="n">
+        <v>411.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Total shares repurchased (mm)</t>
+        </is>
+      </c>
+      <c r="E10" s="461" t="n">
+        <v>8.901621621621622</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Net dilutive options</t>
+        </is>
+      </c>
+      <c r="E11" s="461" t="n">
+        <v>1.798378378378377</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dilutive impact of shares from other securities </t>
+        </is>
+      </c>
+      <c r="E12" s="522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="34" t="n"/>
+      <c r="E13" s="522" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="147" t="inlineStr">
+        <is>
+          <t>Net diluted shares outstanding</t>
+        </is>
+      </c>
+      <c r="D14" s="434" t="n"/>
+      <c r="E14" s="461" t="n">
+        <v>145.7713783783784</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="147" t="n"/>
+      <c r="D15" s="434" t="n"/>
+      <c r="E15" s="461" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="312" t="inlineStr">
+        <is>
+          <t>Options outstanding</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="445" t="n"/>
+      <c r="E16" s="518" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="242" t="inlineStr">
+        <is>
+          <t>Out. shares</t>
+        </is>
+      </c>
+      <c r="D17" s="242" t="inlineStr">
+        <is>
+          <t>Exercise price</t>
+        </is>
+      </c>
+      <c r="E17" s="242" t="inlineStr">
+        <is>
+          <t>In-the-$-shares</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="555" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="298" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D18" s="298" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="299" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="555" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="298" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D19" s="298" t="n">
+        <v>18</v>
+      </c>
+      <c r="E19" s="299" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="555" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="298" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="298" t="n">
+        <v>22</v>
+      </c>
+      <c r="E20" s="299" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="555" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="298" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D21" s="298" t="n">
+        <v>28</v>
+      </c>
+      <c r="E21" s="299" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="555" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="298" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D22" s="298" t="n">
+        <v>32</v>
+      </c>
+      <c r="E22" s="299" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="555" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" s="298" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D23" s="298" t="n">
+        <v>36</v>
+      </c>
+      <c r="E23" s="299" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="555" t="n">
+        <v>7</v>
+      </c>
+      <c r="C24" s="298" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D24" s="298" t="n">
+        <v>39</v>
+      </c>
+      <c r="E24" s="299" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="555" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="298" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D25" s="298" t="n">
+        <v>42</v>
+      </c>
+      <c r="E25" s="299" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="555" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" s="298" t="n"/>
+      <c r="D26" s="298" t="n"/>
+      <c r="E26" s="299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="555" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="298" t="n"/>
+      <c r="D27" s="298" t="n"/>
+      <c r="E27" s="300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="301" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10930,669 +10746,1059 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="4" customWidth="1" style="244" min="2" max="2"/>
-    <col width="18" customWidth="1" style="244" min="3" max="3"/>
-    <col width="22" customWidth="1" style="244" min="4" max="4"/>
-    <col width="22" customWidth="1" style="244" min="5" max="5"/>
-    <col width="28" customWidth="1" style="244" min="6" max="6"/>
-    <col width="28" customWidth="1" style="244" min="7" max="7"/>
+    <col width="22" customWidth="1" style="244" min="3" max="3"/>
+    <col width="26" customWidth="1" style="244" min="4" max="4"/>
+    <col width="18" customWidth="1" style="244" min="5" max="5"/>
+    <col width="20" customWidth="1" style="244" min="6" max="6"/>
+    <col width="12" customWidth="1" style="244" min="7" max="7"/>
     <col width="28" customWidth="1" style="244" min="8" max="8"/>
-    <col width="22" customWidth="1" style="244" min="9" max="9"/>
+    <col width="16" customWidth="1" style="244" min="9" max="9"/>
+    <col width="32" customWidth="1" style="244" min="10" max="10"/>
+    <col width="28" customWidth="1" style="244" min="11" max="11"/>
+    <col width="40" customWidth="1" style="244" min="12" max="12"/>
+    <col width="70" customWidth="1" style="244" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="406" t="inlineStr">
-        <is>
-          <t>Assumptions List — every key driver (What / How / Why / Source)</t>
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>vengeanceaiUSC-LBOMODEL1 — Assumptions List (commentary + Tab/Cell map)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Each row states Where (Tab!Cell), the math location, commentary, and the formula meaning. Not DCF-primary — LBO/operating engine.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="412" t="inlineStr">
+      <c r="B4" s="570" t="inlineStr">
+        <is>
+          <t>PDF: https://raw.githubusercontent.com/vengeanceaiUSC/Rainmaker/cursor/vengeanceaiusclbomodel1-44dc/LBO/output/LBOMODEL1_ASSUMPTIONS_LIST.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="557" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C4" s="412" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="D4" s="412" t="inlineStr">
+      <c r="C6" s="557" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="E4" s="412" t="inlineStr">
+      <c r="D6" s="557" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F4" s="412" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="G4" s="412" t="inlineStr">
-        <is>
-          <t>How</t>
-        </is>
-      </c>
-      <c r="H4" s="412" t="inlineStr">
-        <is>
-          <t>Why</t>
-        </is>
-      </c>
-      <c r="I4" s="412" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" s="244">
-      <c r="B5" s="420" t="n">
+      <c r="E6" s="557" t="inlineStr">
+        <is>
+          <t>Engine (Ex LBO / DCF)</t>
+        </is>
+      </c>
+      <c r="F6" s="557" t="inlineStr">
+        <is>
+          <t>Input Tab</t>
+        </is>
+      </c>
+      <c r="G6" s="557" t="inlineStr">
+        <is>
+          <t>Input Cell</t>
+        </is>
+      </c>
+      <c r="H6" s="557" t="inlineStr">
+        <is>
+          <t>Jump → Input</t>
+        </is>
+      </c>
+      <c r="I6" s="557" t="inlineStr">
+        <is>
+          <t>Math Tab</t>
+        </is>
+      </c>
+      <c r="J6" s="557" t="inlineStr">
+        <is>
+          <t>Math Cell / Row</t>
+        </is>
+      </c>
+      <c r="K6" s="557" t="inlineStr">
+        <is>
+          <t>Jump → Math</t>
+        </is>
+      </c>
+      <c r="L6" s="557" t="inlineStr">
+        <is>
+          <t>What the math does</t>
+        </is>
+      </c>
+      <c r="M6" s="557" t="inlineStr">
+        <is>
+          <t>Commentary (Why / What changed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1" s="244">
+      <c r="B7" s="571" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D5" s="420" t="inlineStr">
-        <is>
-          <t>Baseline year</t>
-        </is>
-      </c>
-      <c r="E5" s="420" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F5" s="420" t="inlineStr">
-        <is>
-          <t>Entry operating year</t>
-        </is>
-      </c>
-      <c r="G5" s="420" t="inlineStr">
-        <is>
-          <t>Prompt + 10-K</t>
-        </is>
-      </c>
-      <c r="H5" s="420" t="inlineStr">
-        <is>
-          <t>User-specified baseline</t>
-        </is>
-      </c>
-      <c r="I5" s="420" t="inlineStr">
-        <is>
-          <t>FY2024 10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" s="244">
-      <c r="B6" s="420" t="n">
+      <c r="C7" s="571" t="inlineStr">
+        <is>
+          <t>Revenue Growth</t>
+        </is>
+      </c>
+      <c r="D7" s="571" t="inlineStr">
+        <is>
+          <t>10% per year (unchanged by AI)</t>
+        </is>
+      </c>
+      <c r="E7" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F7" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G7" s="571" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="H7" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C5</t>
+        </is>
+      </c>
+      <c r="I7" s="571" t="inlineStr">
+        <is>
+          <t>AI_Operating</t>
+        </is>
+      </c>
+      <c r="J7" s="571" t="inlineStr">
+        <is>
+          <t>D5:H5</t>
+        </is>
+      </c>
+      <c r="K7" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D5</t>
+        </is>
+      </c>
+      <c r="L7" s="571" t="inlineStr">
+        <is>
+          <t>Revenue_t = Revenue_{t-1} × (1 + Assumptions_Drivers!C5). Same growth in AI and Base cases.</t>
+        </is>
+      </c>
+      <c r="M7" s="573" t="inlineStr">
+        <is>
+          <t>Annual growth remains stable at ten percent. We kept this assumption unchanged because our AI strategy focuses purely on cost reduction rather than artificially inflating top line projections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1" s="244">
+      <c r="B8" s="571" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D6" s="420" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="E6" s="420" t="inlineStr">
-        <is>
-          <t>$1214.3m</t>
-        </is>
-      </c>
-      <c r="F6" s="420" t="inlineStr">
-        <is>
-          <t>FY2024 revenue</t>
-        </is>
-      </c>
-      <c r="G6" s="420" t="inlineStr">
-        <is>
-          <t>10-K XBRL</t>
-        </is>
-      </c>
-      <c r="H6" s="420" t="inlineStr">
-        <is>
-          <t>Historical anchor</t>
-        </is>
-      </c>
-      <c r="I6" s="420" t="inlineStr">
-        <is>
-          <t>SEC 10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" s="244">
-      <c r="B7" s="420" t="n">
+      <c r="C8" s="571" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="D8" s="571" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="E8" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F8" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G8" s="571" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="H8" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C6</t>
+        </is>
+      </c>
+      <c r="I8" s="571" t="inlineStr">
+        <is>
+          <t>AI_Operating</t>
+        </is>
+      </c>
+      <c r="J8" s="571" t="inlineStr">
+        <is>
+          <t>D6:H6 (COGS)</t>
+        </is>
+      </c>
+      <c r="K8" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D6</t>
+        </is>
+      </c>
+      <c r="L8" s="571" t="inlineStr">
+        <is>
+          <t>COGS_t = Revenue_t × (1 − Assumptions_Drivers!C6); Gross Profit_t = Revenue_t × C6.</t>
+        </is>
+      </c>
+      <c r="M8" s="573" t="inlineStr">
+        <is>
+          <t>Expansion reached precisely eighty percent. We changed this because deploying automated AI agents streamlined initial customer onboarding, directly reducing the human technical support hours required per new user.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1" s="244">
+      <c r="B9" s="571" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D7" s="420" t="inlineStr">
-        <is>
-          <t>Gross profit / GM</t>
-        </is>
-      </c>
-      <c r="E7" s="420" t="inlineStr">
-        <is>
-          <t>$1024.5m / 84%</t>
-        </is>
-      </c>
-      <c r="F7" s="420" t="inlineStr">
-        <is>
-          <t>FY2024 GP</t>
-        </is>
-      </c>
-      <c r="G7" s="420" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="H7" s="420" t="inlineStr">
-        <is>
-          <t>Software GM</t>
-        </is>
-      </c>
-      <c r="I7" s="420" t="inlineStr">
-        <is>
-          <t>SEC 10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" s="244">
-      <c r="B8" s="420" t="n">
+      <c r="C9" s="571" t="inlineStr">
+        <is>
+          <t>Sales Payroll</t>
+        </is>
+      </c>
+      <c r="D9" s="571" t="inlineStr">
+        <is>
+          <t>−15% in Year 1</t>
+        </is>
+      </c>
+      <c r="E9" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F9" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G9" s="571" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="H9" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C7</t>
+        </is>
+      </c>
+      <c r="I9" s="571" t="inlineStr">
+        <is>
+          <t>AI_Operating</t>
+        </is>
+      </c>
+      <c r="J9" s="571" t="inlineStr">
+        <is>
+          <t>D7 (Sales payroll Y1)</t>
+        </is>
+      </c>
+      <c r="K9" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D7</t>
+        </is>
+      </c>
+      <c r="L9" s="571" t="inlineStr">
+        <is>
+          <t>Payroll_Y1 = Assumptions_Drivers!C22 × (1 − C7). Baseline payroll = C22.</t>
+        </is>
+      </c>
+      <c r="M9" s="573" t="inlineStr">
+        <is>
+          <t>Baseline costs dropped by fifteen percent immediately. We changed this to reflect the aggressive termination of outbound human development representatives, instantly eliminating their recurring annual base salary expenses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1" s="244">
+      <c r="B10" s="571" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D8" s="420" t="inlineStr">
-        <is>
-          <t>OpInc / D&amp;A / EBITDA</t>
-        </is>
-      </c>
-      <c r="E8" s="420" t="inlineStr">
-        <is>
-          <t>97.4 / 85.7 / 183.10000000000002</t>
-        </is>
-      </c>
-      <c r="F8" s="420" t="inlineStr">
-        <is>
-          <t>Baseline earnings</t>
-        </is>
-      </c>
-      <c r="G8" s="420" t="inlineStr">
-        <is>
-          <t>OpInc+D&amp;A</t>
-        </is>
-      </c>
-      <c r="H8" s="420" t="inlineStr">
-        <is>
-          <t>Standard add-back</t>
-        </is>
-      </c>
-      <c r="I8" s="420" t="inlineStr">
-        <is>
-          <t>SEC XBRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" s="244">
-      <c r="B9" s="420" t="n">
+      <c r="C10" s="571" t="inlineStr">
+        <is>
+          <t>Variable Commissions</t>
+        </is>
+      </c>
+      <c r="D10" s="571" t="inlineStr">
+        <is>
+          <t>−20% of baseline commission pool from Y1</t>
+        </is>
+      </c>
+      <c r="E10" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F10" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G10" s="571" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="H10" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C8</t>
+        </is>
+      </c>
+      <c r="I10" s="571" t="inlineStr">
+        <is>
+          <t>AI_Operating</t>
+        </is>
+      </c>
+      <c r="J10" s="571" t="inlineStr">
+        <is>
+          <t>D8:H8 (Commissions)</t>
+        </is>
+      </c>
+      <c r="K10" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D8</t>
+        </is>
+      </c>
+      <c r="L10" s="571" t="inlineStr">
+        <is>
+          <t>Commissions_AI = Assumptions_Drivers!C23 × (1 − C8); Base keeps full C23 pool scaled with revenue.</t>
+        </is>
+      </c>
+      <c r="M10" s="573" t="inlineStr">
+        <is>
+          <t>Rates decreased significantly starting in year one. Replacing human representatives with AI meant fewer outbound deals required traditional payouts, allowing the company to retain higher profit per sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1" s="244">
+      <c r="B11" s="571" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D9" s="420" t="inlineStr">
-        <is>
-          <t>S&amp;M baseline</t>
-        </is>
-      </c>
-      <c r="E9" s="420" t="inlineStr">
-        <is>
-          <t>$425.0m (35% rev)</t>
-        </is>
-      </c>
-      <c r="F9" s="420" t="inlineStr">
-        <is>
-          <t>Bloated S&amp;M</t>
-        </is>
-      </c>
-      <c r="G9" s="420" t="inlineStr">
-        <is>
-          <t>35% × revenue</t>
-        </is>
-      </c>
-      <c r="H9" s="420" t="inlineStr">
-        <is>
-          <t>Prompt ~$425m</t>
-        </is>
-      </c>
-      <c r="I9" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" s="244">
-      <c r="B10" s="420" t="n">
+      <c r="C11" s="571" t="inlineStr">
+        <is>
+          <t>AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D11" s="571" t="inlineStr">
+        <is>
+          <t>$15 million fixed / year</t>
+        </is>
+      </c>
+      <c r="E11" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F11" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G11" s="571" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="H11" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C9</t>
+        </is>
+      </c>
+      <c r="I11" s="571" t="inlineStr">
+        <is>
+          <t>AI_Operating</t>
+        </is>
+      </c>
+      <c r="J11" s="571" t="inlineStr">
+        <is>
+          <t>D10:H10 (AI infrastructure)</t>
+        </is>
+      </c>
+      <c r="K11" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D10</t>
+        </is>
+      </c>
+      <c r="L11" s="571" t="inlineStr">
+        <is>
+          <t>AI_cost_t = Assumptions_Drivers!C9 each forecast year (AI case only). EBITDA reduces by this amount.</t>
+        </is>
+      </c>
+      <c r="M11" s="573" t="inlineStr">
+        <is>
+          <t>A new fixed fifteen million dollar expense was added. We included this vital change to cover enterprise software licenses, API usage limits, and compute power running the AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1" s="244">
+      <c r="B12" s="571" t="n">
         <v>6</v>
       </c>
-      <c r="C10" s="420" t="inlineStr">
+      <c r="C12" s="571" t="inlineStr">
+        <is>
+          <t>Sales Growth (S&amp;M expense growth)</t>
+        </is>
+      </c>
+      <c r="D12" s="571" t="inlineStr">
+        <is>
+          <t>2% per year from Year 2</t>
+        </is>
+      </c>
+      <c r="E12" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F12" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G12" s="571" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="H12" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C10</t>
+        </is>
+      </c>
+      <c r="I12" s="571" t="inlineStr">
         <is>
           <t>AI_Operating</t>
         </is>
       </c>
-      <c r="D10" s="420" t="inlineStr">
-        <is>
-          <t>Y1 S&amp;M cut</t>
-        </is>
-      </c>
-      <c r="E10" s="420" t="inlineStr">
-        <is>
-          <t>−15%</t>
-        </is>
-      </c>
-      <c r="F10" s="420" t="inlineStr">
-        <is>
-          <t>Terminate outbound SDRs</t>
-        </is>
-      </c>
-      <c r="G10" s="420" t="inlineStr">
-        <is>
-          <t>SM1=SM0×0.85</t>
-        </is>
-      </c>
-      <c r="H10" s="420" t="inlineStr">
-        <is>
-          <t>Remove SDR comp/seats</t>
-        </is>
-      </c>
-      <c r="I10" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" s="244">
-      <c r="B11" s="420" t="n">
+      <c r="J12" s="571" t="inlineStr">
+        <is>
+          <t>E7:H7 / E8:H8 (payroll &amp; commissions Y2–Y5)</t>
+        </is>
+      </c>
+      <c r="K12" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!E7</t>
+        </is>
+      </c>
+      <c r="L12" s="571" t="inlineStr">
+        <is>
+          <t>For t≥2: Payroll_t = Payroll_{t-1} × (1 + Assumptions_Drivers!C10); same for commissions.</t>
+        </is>
+      </c>
+      <c r="M12" s="573" t="inlineStr">
+        <is>
+          <t>Expense growth was permanently capped at two percent. We altered this because automated agents scale infinitely, entirely severing the historical link between revenue growth and proportional human additions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1" s="244">
+      <c r="B13" s="571" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="420" t="inlineStr">
+      <c r="C13" s="571" t="inlineStr">
+        <is>
+          <t>Administrative Costs (G&amp;A)</t>
+        </is>
+      </c>
+      <c r="D13" s="571" t="inlineStr">
+        <is>
+          <t>Locked at baseline % of revenue</t>
+        </is>
+      </c>
+      <c r="E13" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F13" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G13" s="571" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="H13" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C11</t>
+        </is>
+      </c>
+      <c r="I13" s="571" t="inlineStr">
         <is>
           <t>AI_Operating</t>
         </is>
       </c>
-      <c r="D11" s="420" t="inlineStr">
-        <is>
-          <t>AI replacement cost</t>
-        </is>
-      </c>
-      <c r="E11" s="420" t="inlineStr">
-        <is>
-          <t>$15m / yr</t>
-        </is>
-      </c>
-      <c r="F11" s="420" t="inlineStr">
-        <is>
-          <t>AI compute/software</t>
-        </is>
-      </c>
-      <c r="G11" s="420" t="inlineStr">
-        <is>
-          <t>Fixed +$15m from Y1</t>
-        </is>
-      </c>
-      <c r="H11" s="420" t="inlineStr">
-        <is>
-          <t>Agent infrastructure</t>
-        </is>
-      </c>
-      <c r="I11" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" s="244">
-      <c r="B12" s="420" t="n">
+      <c r="J13" s="571" t="inlineStr">
+        <is>
+          <t>D12:H12 (G&amp;A)</t>
+        </is>
+      </c>
+      <c r="K13" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D12</t>
+        </is>
+      </c>
+      <c r="L13" s="571" t="inlineStr">
+        <is>
+          <t>G&amp;A_t = Revenue_t × Assumptions_Drivers!C11. Identical % in AI and Base cases.</t>
+        </is>
+      </c>
+      <c r="M13" s="573" t="inlineStr">
+        <is>
+          <t>General overhead remained locked at baseline percentages. We avoided changing this because the value creation strategy strictly impacts the active sales floor without altering corporate finance or compensation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="78" customHeight="1" s="244">
+      <c r="B14" s="571" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="420" t="inlineStr">
+      <c r="C14" s="571" t="inlineStr">
+        <is>
+          <t>Capital Expenditures</t>
+        </is>
+      </c>
+      <c r="D14" s="571" t="inlineStr">
+        <is>
+          <t>−5% vs baseline CapEx rate</t>
+        </is>
+      </c>
+      <c r="E14" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F14" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G14" s="571" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="H14" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C12</t>
+        </is>
+      </c>
+      <c r="I14" s="571" t="inlineStr">
         <is>
           <t>AI_Operating</t>
         </is>
       </c>
-      <c r="D12" s="420" t="inlineStr">
-        <is>
-          <t>S&amp;M growth Y2+</t>
-        </is>
-      </c>
-      <c r="E12" s="420" t="inlineStr">
-        <is>
-          <t>2% / yr</t>
-        </is>
-      </c>
-      <c r="F12" s="420" t="inlineStr">
-        <is>
-          <t>Cap S&amp;M after cut</t>
-        </is>
-      </c>
-      <c r="G12" s="420" t="inlineStr">
-        <is>
-          <t>SM_t=SM_t-1×1.02</t>
-        </is>
-      </c>
-      <c r="H12" s="420" t="inlineStr">
-        <is>
-          <t>AI scales without HC</t>
-        </is>
-      </c>
-      <c r="I12" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" s="244">
-      <c r="B13" s="420" t="n">
+      <c r="J14" s="571" t="inlineStr">
+        <is>
+          <t>D19:H19 (CapEx)</t>
+        </is>
+      </c>
+      <c r="K14" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D19</t>
+        </is>
+      </c>
+      <c r="L14" s="571" t="inlineStr">
+        <is>
+          <t>CapEx_AI = Revenue_t × Assumptions_Drivers!C24 × (1 − C12); Base uses C24 only.</t>
+        </is>
+      </c>
+      <c r="M14" s="573" t="inlineStr">
+        <is>
+          <t>Hardware spending was reduced by five percent. We made this change because terminating the human sales team immediately eliminated the constant need for purchasing physical laptops and equipment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="78" customHeight="1" s="244">
+      <c r="B15" s="571" t="n">
         <v>9</v>
       </c>
-      <c r="C13" s="420" t="inlineStr">
+      <c r="C15" s="571" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="D15" s="571" t="inlineStr">
+        <is>
+          <t>Receivables / WC requirement −10% vs base</t>
+        </is>
+      </c>
+      <c r="E15" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F15" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G15" s="571" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="H15" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C13</t>
+        </is>
+      </c>
+      <c r="I15" s="571" t="inlineStr">
         <is>
           <t>AI_Operating</t>
         </is>
       </c>
-      <c r="D13" s="420" t="inlineStr">
-        <is>
-          <t>Margin target</t>
-        </is>
-      </c>
-      <c r="E13" s="420" t="inlineStr">
-        <is>
-          <t>≥500 bps by Y2</t>
-        </is>
-      </c>
-      <c r="F13" s="420" t="inlineStr">
-        <is>
-          <t>EBITDA margin expansion</t>
-        </is>
-      </c>
-      <c r="G13" s="420" t="inlineStr">
-        <is>
-          <t>Y2 margin − baseline</t>
-        </is>
-      </c>
-      <c r="H13" s="420" t="inlineStr">
-        <is>
-          <t>Value-creation hurdle</t>
-        </is>
-      </c>
-      <c r="I13" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" s="244">
-      <c r="B14" s="420" t="n">
+      <c r="J15" s="571" t="inlineStr">
+        <is>
+          <t>D20:H20 (ΔNWC)</t>
+        </is>
+      </c>
+      <c r="K15" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D20</t>
+        </is>
+      </c>
+      <c r="L15" s="571" t="inlineStr">
+        <is>
+          <t>ΔNWC_AI = ΔRevenue_t × Assumptions_Drivers!C25 × (1 − C13).</t>
+        </is>
+      </c>
+      <c r="M15" s="573" t="inlineStr">
+        <is>
+          <t>Receivables collection periods improved slightly overall. Implementing automated AI billing reminders accelerated cash collections from late customers, lowering total working capital requirements and freeing extra cash for debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="78" customHeight="1" s="244">
+      <c r="B16" s="571" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="420" t="inlineStr">
-        <is>
-          <t>Base_Operating</t>
-        </is>
-      </c>
-      <c r="D14" s="420" t="inlineStr">
-        <is>
-          <t>Base S&amp;M policy</t>
-        </is>
-      </c>
-      <c r="E14" s="420" t="inlineStr">
-        <is>
-          <t>35% of revenue</t>
-        </is>
-      </c>
-      <c r="F14" s="420" t="inlineStr">
-        <is>
-          <t>No AI transformation</t>
-        </is>
-      </c>
-      <c r="G14" s="420" t="inlineStr">
-        <is>
-          <t>SM=0.35×Rev</t>
-        </is>
-      </c>
-      <c r="H14" s="420" t="inlineStr">
-        <is>
-          <t>Counterfactual</t>
-        </is>
-      </c>
-      <c r="I14" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" s="244">
-      <c r="B15" s="420" t="n">
+      <c r="C16" s="571" t="inlineStr">
+        <is>
+          <t>Term Loan A interest</t>
+        </is>
+      </c>
+      <c r="D16" s="571" t="inlineStr">
+        <is>
+          <t>SOFR + 4.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F16" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G16" s="571" t="inlineStr">
+        <is>
+          <t>C14 / C15</t>
+        </is>
+      </c>
+      <c r="H16" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C14</t>
+        </is>
+      </c>
+      <c r="I16" s="571" t="inlineStr">
+        <is>
+          <t>Debt_Sweep_AI</t>
+        </is>
+      </c>
+      <c r="J16" s="571" t="inlineStr">
+        <is>
+          <t>C12 (TLA rate); Interest on AI_Operating!D17:H17</t>
+        </is>
+      </c>
+      <c r="K16" s="572" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!C12</t>
+        </is>
+      </c>
+      <c r="L16" s="571" t="inlineStr">
+        <is>
+          <t>TLA_rate = Assumptions_Drivers!C14 + C15 (=C27). Interest_TLA = TLA_beg × TLA_rate.</t>
+        </is>
+      </c>
+      <c r="M16" s="573" t="inlineStr">
+        <is>
+          <t>The interest rate remained static at SOFR plus four. This was unchanged because the macroeconomic lending environment and the base company credit profile strictly dictate senior pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="78" customHeight="1" s="244">
+      <c r="B17" s="571" t="n">
         <v>11</v>
       </c>
-      <c r="C15" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D15" s="420" t="inlineStr">
-        <is>
-          <t>Exit multiple</t>
-        </is>
-      </c>
-      <c r="E15" s="420" t="inlineStr">
-        <is>
-          <t>13.0x</t>
-        </is>
-      </c>
-      <c r="F15" s="420" t="inlineStr">
-        <is>
-          <t>Software exit EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="G15" s="420" t="inlineStr">
-        <is>
-          <t>Mid 12–14x band</t>
-        </is>
-      </c>
-      <c r="H15" s="420" t="inlineStr">
-        <is>
-          <t>PE exit assumption</t>
-        </is>
-      </c>
-      <c r="I15" s="420" t="inlineStr">
-        <is>
-          <t>User prompt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" s="244">
-      <c r="B16" s="420" t="n">
+      <c r="C17" s="571" t="inlineStr">
+        <is>
+          <t>Term Loan B interest</t>
+        </is>
+      </c>
+      <c r="D17" s="571" t="inlineStr">
+        <is>
+          <t>SOFR + 5.00%</t>
+        </is>
+      </c>
+      <c r="E17" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F17" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G17" s="571" t="inlineStr">
+        <is>
+          <t>C14 / C16</t>
+        </is>
+      </c>
+      <c r="H17" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C14</t>
+        </is>
+      </c>
+      <c r="I17" s="571" t="inlineStr">
+        <is>
+          <t>Debt_Sweep_AI</t>
+        </is>
+      </c>
+      <c r="J17" s="571" t="inlineStr">
+        <is>
+          <t>D12 (TLB rate); Interest on AI_Operating!D17:H17</t>
+        </is>
+      </c>
+      <c r="K17" s="572" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!D12</t>
+        </is>
+      </c>
+      <c r="L17" s="571" t="inlineStr">
+        <is>
+          <t>TLB_rate = Assumptions_Drivers!C14 + C16 (=C28). Interest_TLB = TLB_beg × TLB_rate.</t>
+        </is>
+      </c>
+      <c r="M17" s="573" t="inlineStr">
+        <is>
+          <t>Pricing was maintained exactly at SOFR plus five. We did not alter this input since institutional syndicated loan markets price risk completely independent of internal software strategies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="78" customHeight="1" s="244">
+      <c r="B18" s="571" t="n">
         <v>12</v>
       </c>
-      <c r="C16" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D16" s="420" t="inlineStr">
-        <is>
-          <t>New leverage</t>
-        </is>
-      </c>
-      <c r="E16" s="420" t="inlineStr">
-        <is>
-          <t>5.0x EBITDA</t>
-        </is>
-      </c>
-      <c r="F16" s="420" t="inlineStr">
-        <is>
-          <t>TLA/TLB/Notes</t>
-        </is>
-      </c>
-      <c r="G16" s="420" t="inlineStr">
-        <is>
-          <t>2.5+1.5+1.0 turns</t>
-        </is>
-      </c>
-      <c r="H16" s="420" t="inlineStr">
-        <is>
-          <t>Financing structure</t>
-        </is>
-      </c>
-      <c r="I16" s="420" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1" s="244">
-      <c r="B17" s="420" t="n">
+      <c r="C18" s="571" t="inlineStr">
+        <is>
+          <t>Mandatory Amortization</t>
+        </is>
+      </c>
+      <c r="D18" s="571" t="inlineStr">
+        <is>
+          <t>1% of initial principal / year</t>
+        </is>
+      </c>
+      <c r="E18" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F18" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G18" s="571" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="H18" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C17</t>
+        </is>
+      </c>
+      <c r="I18" s="571" t="inlineStr">
+        <is>
+          <t>Debt_Sweep_AI</t>
+        </is>
+      </c>
+      <c r="J18" s="571" t="inlineStr">
+        <is>
+          <t>D5:D9 (Mandatory 1%)</t>
+        </is>
+      </c>
+      <c r="K18" s="572" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!D5</t>
+        </is>
+      </c>
+      <c r="L18" s="571" t="inlineStr">
+        <is>
+          <t>Mandatory_t = Initial_Debt × Assumptions_Drivers!C17 (floor paydown before optional sweep).</t>
+        </is>
+      </c>
+      <c r="M18" s="573" t="inlineStr">
+        <is>
+          <t>Principal repayment schedules were held constant at one percent. We kept this standard because syndicated loans strictly mandate minimum amortization regardless of how much extra cash AI generates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="78" customHeight="1" s="244">
+      <c r="B19" s="571" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="420" t="inlineStr">
+      <c r="C19" s="571" t="inlineStr">
+        <is>
+          <t>Cash Sweep</t>
+        </is>
+      </c>
+      <c r="D19" s="571" t="inlineStr">
+        <is>
+          <t>100% of excess cash to debt</t>
+        </is>
+      </c>
+      <c r="E19" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F19" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G19" s="571" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="H19" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C18</t>
+        </is>
+      </c>
+      <c r="I19" s="571" t="inlineStr">
         <is>
           <t>Debt_Sweep_AI</t>
         </is>
       </c>
-      <c r="D17" s="420" t="inlineStr">
-        <is>
-          <t>Cash sweep</t>
-        </is>
-      </c>
-      <c r="E17" s="420" t="inlineStr">
-        <is>
-          <t>Max FCF to debt</t>
-        </is>
-      </c>
-      <c r="F17" s="420" t="inlineStr">
-        <is>
-          <t>Accelerated paydown</t>
-        </is>
-      </c>
-      <c r="G17" s="420" t="inlineStr">
-        <is>
-          <t>min(debt, max(0,FCF))</t>
-        </is>
-      </c>
-      <c r="H17" s="420" t="inlineStr">
-        <is>
-          <t>IRR via lower exit debt</t>
-        </is>
-      </c>
-      <c r="I17" s="420" t="inlineStr">
-        <is>
-          <t>LBO mechanics</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1" s="244">
-      <c r="B18" s="420" t="n">
+      <c r="J19" s="571" t="inlineStr">
+        <is>
+          <t>E5:E9 (Total paydown)</t>
+        </is>
+      </c>
+      <c r="K19" s="572" t="inlineStr">
+        <is>
+          <t>Go to Debt_Sweep_AI!E5</t>
+        </is>
+      </c>
+      <c r="L19" s="571" t="inlineStr">
+        <is>
+          <t>Optional_sweep_t = C18 × max(0, FCF_t − Mandatory_t); Debt_end = Debt_beg − Mandatory − Optional_sweep.</t>
+        </is>
+      </c>
+      <c r="M19" s="573" t="inlineStr">
+        <is>
+          <t>One hundred percent of excess cash targets debt paydown. This remained unchanged to ensure all newly generated margins from AI savings aggressively reduce leverage and maximize sponsor returns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="78" customHeight="1" s="244">
+      <c r="B20" s="571" t="n">
         <v>14</v>
       </c>
-      <c r="C18" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D18" s="420" t="inlineStr">
-        <is>
-          <t>Offer premium</t>
-        </is>
-      </c>
-      <c r="E18" s="420" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="F18" s="420" t="inlineStr">
-        <is>
-          <t>Take-private premium</t>
-        </is>
-      </c>
-      <c r="G18" s="420" t="inlineStr">
-        <is>
-          <t>Offer=Px1.25</t>
-        </is>
-      </c>
-      <c r="H18" s="420" t="inlineStr">
-        <is>
-          <t>Deal assumption</t>
-        </is>
-      </c>
-      <c r="I18" s="420" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="244">
-      <c r="B19" s="420" t="n">
+      <c r="C20" s="571" t="inlineStr">
+        <is>
+          <t>Tax Rate</t>
+        </is>
+      </c>
+      <c r="D20" s="571" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="E20" s="571" t="inlineStr">
+        <is>
+          <t>LBO (not DCF)</t>
+        </is>
+      </c>
+      <c r="F20" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G20" s="571" t="inlineStr">
+        <is>
+          <t>C19</t>
+        </is>
+      </c>
+      <c r="H20" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C19</t>
+        </is>
+      </c>
+      <c r="I20" s="571" t="inlineStr">
+        <is>
+          <t>AI_Operating</t>
+        </is>
+      </c>
+      <c r="J20" s="571" t="inlineStr">
+        <is>
+          <t>D18:H18 (Net income)</t>
+        </is>
+      </c>
+      <c r="K20" s="572" t="inlineStr">
+        <is>
+          <t>Go to AI_Operating!D18</t>
+        </is>
+      </c>
+      <c r="L20" s="571" t="inlineStr">
+        <is>
+          <t>Tax_t = max(0, EBIT_t − Interest_t) × Assumptions_Drivers!C19; NI_t = EBT_t − Tax_t.</t>
+        </is>
+      </c>
+      <c r="M20" s="573" t="inlineStr">
+        <is>
+          <t>The corporate tax rate remained steady at twenty one percent. We did not change this assumption because federal statutory tax obligations remain unaffected by internal operating margin improvements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="78" customHeight="1" s="244">
+      <c r="B21" s="571" t="n">
         <v>15</v>
       </c>
-      <c r="C19" s="420" t="inlineStr">
-        <is>
-          <t>Strategy_Summary</t>
-        </is>
-      </c>
-      <c r="D19" s="420" t="inlineStr">
-        <is>
-          <t>IRR uplift metric</t>
-        </is>
-      </c>
-      <c r="E19" s="420" t="inlineStr">
-        <is>
-          <t>11.1 ppt</t>
-        </is>
-      </c>
-      <c r="F19" s="420" t="inlineStr">
-        <is>
-          <t>AI vs Base IRR</t>
-        </is>
-      </c>
-      <c r="G19" s="420" t="inlineStr">
-        <is>
-          <t>IRR_AI − IRR_Base</t>
-        </is>
-      </c>
-      <c r="H19" s="420" t="inlineStr">
-        <is>
-          <t>Isolates AI S&amp;M value</t>
-        </is>
-      </c>
-      <c r="I19" s="420" t="inlineStr">
-        <is>
-          <t>Calculated</t>
-        </is>
-      </c>
-    </row>
+      <c r="C21" s="571" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="D21" s="571" t="inlineStr">
+        <is>
+          <t>13.0x EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="E21" s="571" t="inlineStr">
+        <is>
+          <t>LBO (Ex LBO!D17; not DCF)</t>
+        </is>
+      </c>
+      <c r="F21" s="571" t="inlineStr">
+        <is>
+          <t>Assumptions_Drivers</t>
+        </is>
+      </c>
+      <c r="G21" s="571" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="H21" s="572" t="inlineStr">
+        <is>
+          <t>Go to Assumptions_Drivers!C20</t>
+        </is>
+      </c>
+      <c r="I21" s="571" t="inlineStr">
+        <is>
+          <t>LBO</t>
+        </is>
+      </c>
+      <c r="J21" s="571" t="inlineStr">
+        <is>
+          <t>D17 (also Strategy_Summary!D10)</t>
+        </is>
+      </c>
+      <c r="K21" s="572" t="inlineStr">
+        <is>
+          <t>Go to LBO!D17</t>
+        </is>
+      </c>
+      <c r="L21" s="571" t="inlineStr">
+        <is>
+          <t>Exit_EV = Y5_EBITDA × Assumptions_Drivers!C20; Exit_Equity = Exit_EV − Debt_end; MOIC / IRR from that.</t>
+        </is>
+      </c>
+      <c r="M21" s="573" t="inlineStr">
+        <is>
+          <t>The valuation multiple was securely locked at thirteen. We kept this exact multiple consistent across scenarios to prove equity value creation stemmed purely from AI operational improvements alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="564" t="inlineStr">
+        <is>
+          <t>NOTE ON DCF TAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="574" t="inlineStr">
+        <is>
+          <t>These AI-SDR operating assumptions are NOT the primary drivers of the DCF tab. IRR/MOIC value-creation math is on Strategy_Summary, AI_Operating, Base_Operating, Debt_Sweep_AI, and LBO!D17/J275. DCF remains a secondary WSP shell for football-field context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
   </sheetData>
+  <autoFilter ref="B6:M21"/>
+  <mergeCells count="1">
+    <mergeCell ref="B24:M25"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11603,174 +11809,380 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G12"/>
+  <dimension ref="B2:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="12" customWidth="1" style="244" min="4" max="4"/>
-    <col width="14" customWidth="1" style="244" min="5" max="5"/>
-    <col width="14" customWidth="1" style="244" min="6" max="6"/>
-    <col width="18" customWidth="1" style="244" min="7" max="7"/>
+    <col width="36" customWidth="1" style="244" min="2" max="2"/>
+    <col width="14" customWidth="1" style="244" min="3" max="3"/>
+    <col width="36" customWidth="1" style="244" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="406" t="inlineStr">
-        <is>
-          <t>Debt schedule — AI case cash sweep (vs base ending debt)</t>
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>Assumptions Drivers (yellow = inputs used by AI / Base operating math)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>These cells are the single source of truth for the commentary list. Operating tabs read these values.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="412" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Driver</t>
         </is>
       </c>
       <c r="C4" s="412" t="inlineStr">
         <is>
-          <t>AI FCF</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="D4" s="412" t="inlineStr">
         <is>
-          <t>AI paydown</t>
-        </is>
-      </c>
-      <c r="E4" s="412" t="inlineStr">
-        <is>
-          <t>AI debt end</t>
-        </is>
-      </c>
-      <c r="F4" s="412" t="inlineStr">
-        <is>
-          <t>Base debt end</t>
-        </is>
-      </c>
-      <c r="G4" s="412" t="inlineStr">
-        <is>
-          <t>Extra paydown vs base</t>
+          <t>Feeds</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="421" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C5" s="556" t="n">
-        <v>137.5282912000001</v>
-      </c>
-      <c r="D5" s="556" t="n">
-        <v>137.5282912000001</v>
-      </c>
-      <c r="E5" s="559" t="n">
-        <v>777.9717088</v>
-      </c>
-      <c r="F5" s="556" t="n">
-        <v>826.5607773</v>
-      </c>
-      <c r="G5" s="559" t="n">
-        <v>48.58906850000005</v>
+      <c r="B5" s="575" t="inlineStr">
+        <is>
+          <t>Revenue growth</t>
+        </is>
+      </c>
+      <c r="C5" s="422" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating!C5:G5</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="421" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C6" s="556" t="n">
-        <v>159.2865991016001</v>
-      </c>
-      <c r="D6" s="556" t="n">
-        <v>159.2865991016001</v>
-      </c>
-      <c r="E6" s="559" t="n">
-        <v>618.6851096983999</v>
-      </c>
-      <c r="F6" s="556" t="n">
-        <v>726.867461747025</v>
-      </c>
-      <c r="G6" s="559" t="n">
-        <v>108.1823520486251</v>
+      <c r="B6" s="575" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C6" s="422" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating COGS row</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="421" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C7" s="556" t="n">
-        <v>183.23549201229</v>
-      </c>
-      <c r="D7" s="556" t="n">
-        <v>183.23549201229</v>
-      </c>
-      <c r="E7" s="559" t="n">
-        <v>435.4496176861098</v>
-      </c>
-      <c r="F7" s="556" t="n">
-        <v>615.320635583216</v>
-      </c>
-      <c r="G7" s="559" t="n">
-        <v>179.8710178971062</v>
+      <c r="B7" s="575" t="inlineStr">
+        <is>
+          <t>Sales payroll cut (Y1)</t>
+        </is>
+      </c>
+      <c r="C7" s="422" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating S&amp;M Y1</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="421" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C8" s="556" t="n">
-        <v>204.2737956388759</v>
-      </c>
-      <c r="D8" s="556" t="n">
-        <v>204.2737956388759</v>
-      </c>
-      <c r="E8" s="559" t="n">
-        <v>231.1758220472339</v>
-      </c>
-      <c r="F8" s="556" t="n">
-        <v>492.2660966390317</v>
-      </c>
-      <c r="G8" s="559" t="n">
-        <v>261.0902745917978</v>
+      <c r="B8" s="575" t="inlineStr">
+        <is>
+          <t>Variable commission cut</t>
+        </is>
+      </c>
+      <c r="C8" s="422" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating Commissions</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="421" t="n">
-        <v>2029</v>
-      </c>
-      <c r="C9" s="556" t="n">
-        <v>226.6632985760825</v>
-      </c>
-      <c r="D9" s="556" t="n">
-        <v>226.6632985760825</v>
-      </c>
-      <c r="E9" s="559" t="n">
-        <v>4.512523471151439</v>
-      </c>
-      <c r="F9" s="556" t="n">
-        <v>357.1352076643299</v>
-      </c>
-      <c r="G9" s="559" t="n">
-        <v>352.6226841931785</v>
+      <c r="B9" s="575" t="inlineStr">
+        <is>
+          <t>AI infrastructure ($m)</t>
+        </is>
+      </c>
+      <c r="C9" s="576" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating AI cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M expense growth Y2+</t>
+        </is>
+      </c>
+      <c r="C10" s="422" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D10" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating S&amp;M Y2+</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="408" t="inlineStr">
-        <is>
-          <t>New debt at close</t>
-        </is>
-      </c>
-      <c r="C11" s="556" t="n">
-        <v>915.5000000000001</v>
+      <c r="B11" s="575" t="inlineStr">
+        <is>
+          <t>G&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="422" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D11" s="575" t="inlineStr">
+        <is>
+          <t>AI_Operating G&amp;A</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="408" t="inlineStr">
-        <is>
-          <t>Blended interest rate</t>
+      <c r="B12" s="575" t="inlineStr">
+        <is>
+          <t>CapEx reduction vs base</t>
         </is>
       </c>
       <c r="C12" s="422" t="n">
-        <v>0.075</v>
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="575" t="inlineStr">
+        <is>
+          <t>FCF CapEx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="575" t="inlineStr">
+        <is>
+          <t>WC / receivables improvement</t>
+        </is>
+      </c>
+      <c r="C13" s="422" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" s="575" t="inlineStr">
+        <is>
+          <t>FCF ΔNWC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="575" t="inlineStr">
+        <is>
+          <t>SOFR</t>
+        </is>
+      </c>
+      <c r="C14" s="577" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D14" s="575" t="inlineStr">
+        <is>
+          <t>Debt interest</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="575" t="inlineStr">
+        <is>
+          <t>Term Loan A spread</t>
+        </is>
+      </c>
+      <c r="C15" s="577" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D15" s="575" t="inlineStr">
+        <is>
+          <t>TLA rate = SOFR+spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="575" t="inlineStr">
+        <is>
+          <t>Term Loan B spread</t>
+        </is>
+      </c>
+      <c r="C16" s="577" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D16" s="575" t="inlineStr">
+        <is>
+          <t>TLB rate = SOFR+spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="575" t="inlineStr">
+        <is>
+          <t>Mandatory amortization</t>
+        </is>
+      </c>
+      <c r="C17" s="422" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D17" s="575" t="inlineStr">
+        <is>
+          <t>% of initial new debt / yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="575" t="inlineStr">
+        <is>
+          <t>Cash sweep %</t>
+        </is>
+      </c>
+      <c r="C18" s="422" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="575" t="inlineStr">
+        <is>
+          <t>Debt_Sweep_AI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="575" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C19" s="422" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D19" s="575" t="inlineStr">
+        <is>
+          <t>NI tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="575" t="inlineStr">
+        <is>
+          <t>Exit EV/EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="C20" s="584" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="575" t="inlineStr">
+        <is>
+          <t>LBO!D17 / Strategy_Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C21" s="576" t="n">
+        <v>425</v>
+      </c>
+      <c r="D21" s="575" t="inlineStr">
+        <is>
+          <t>35% × FY24 revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="575" t="inlineStr">
+        <is>
+          <t>Payroll baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C22" s="576" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D22" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M − commission pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="575" t="inlineStr">
+        <is>
+          <t>Commission baseline ($m)</t>
+        </is>
+      </c>
+      <c r="C23" s="576" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D23" s="575" t="inlineStr">
+        <is>
+          <t>25% of S&amp;M baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="575" t="inlineStr">
+        <is>
+          <t>CapEx base % of rev</t>
+        </is>
+      </c>
+      <c r="C24" s="422" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="575" t="inlineStr">
+        <is>
+          <t>Before AI −5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="575" t="inlineStr">
+        <is>
+          <t>WC base % of Δrev</t>
+        </is>
+      </c>
+      <c r="C25" s="422" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D25" s="575" t="inlineStr">
+        <is>
+          <t>Before AI improvement</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TLA rate (SOFR+4)</t>
+        </is>
+      </c>
+      <c r="C27" s="579">
+        <f>C14+C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TLB rate (SOFR+5)</t>
+        </is>
+      </c>
+      <c r="C28" s="579">
+        <f>C14+C16</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -11784,420 +12196,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="22" customWidth="1" style="244" min="2" max="2"/>
-    <col width="12" customWidth="1" style="244" min="3" max="3"/>
-    <col width="12" customWidth="1" style="244" min="4" max="4"/>
-    <col width="12" customWidth="1" style="244" min="5" max="5"/>
-    <col width="12" customWidth="1" style="244" min="6" max="6"/>
-    <col width="12" customWidth="1" style="244" min="7" max="7"/>
-    <col width="12" customWidth="1" style="244" min="8" max="8"/>
-    <col width="12" customWidth="1" style="244" min="9" max="9"/>
-  </cols>
+  <dimension ref="B2:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
-      <c r="B2" s="406" t="inlineStr">
-        <is>
-          <t>Base case — S&amp;M stays ~35% of revenue (no AI transformation)</t>
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>Debt sweep — TLA/TLB priced at SOFR+4 / SOFR+5; 1% mandatory + 100% cash sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rates from Assumptions_Drivers!C14:C18</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="412" t="inlineStr"/>
+      <c r="B4" s="412" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
       <c r="C4" s="412" t="inlineStr">
         <is>
-          <t>FY2024A</t>
+          <t>FCF</t>
         </is>
       </c>
       <c r="D4" s="412" t="inlineStr">
         <is>
-          <t>Y1 2025</t>
+          <t>Mandatory 1%</t>
         </is>
       </c>
       <c r="E4" s="412" t="inlineStr">
         <is>
-          <t>Y2 2026</t>
+          <t>Total paydown</t>
         </is>
       </c>
       <c r="F4" s="412" t="inlineStr">
         <is>
-          <t>Y3 2027</t>
+          <t>AI debt end</t>
         </is>
       </c>
       <c r="G4" s="412" t="inlineStr">
         <is>
-          <t>Y4 2028</t>
+          <t>Base debt end</t>
         </is>
       </c>
       <c r="H4" s="412" t="inlineStr">
         <is>
-          <t>Y5 2029</t>
+          <t>Extra paydown vs base</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="408" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C5" s="556" t="n">
-        <v>1214.3</v>
-      </c>
-      <c r="D5" s="556" t="n">
-        <v>1250.729</v>
-      </c>
-      <c r="E5" s="556" t="n">
-        <v>1300.75816</v>
-      </c>
-      <c r="F5" s="556" t="n">
-        <v>1352.7884864</v>
-      </c>
-      <c r="G5" s="556" t="n">
-        <v>1393.372140992</v>
-      </c>
-      <c r="H5" s="556" t="n">
-        <v>1435.173305221761</v>
+      <c r="B5" s="580" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C5" s="567" t="n">
+        <v>121.543319</v>
+      </c>
+      <c r="D5" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E5" s="567" t="n">
+        <v>121.543319</v>
+      </c>
+      <c r="F5" s="567" t="n">
+        <v>793.956681</v>
+      </c>
+      <c r="G5" s="567" t="n">
+        <v>877.5180999999999</v>
+      </c>
+      <c r="H5" s="567" t="n">
+        <v>83.56141899999989</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="408" t="inlineStr">
-        <is>
-          <t>COGS</t>
-        </is>
-      </c>
-      <c r="C6" s="556" t="n">
-        <v>189.8</v>
-      </c>
-      <c r="D6" s="556" t="n">
-        <v>195.4939999999999</v>
-      </c>
-      <c r="E6" s="556" t="n">
-        <v>203.31376</v>
-      </c>
-      <c r="F6" s="556" t="n">
-        <v>211.4463104</v>
-      </c>
-      <c r="G6" s="556" t="n">
-        <v>217.789699712</v>
-      </c>
-      <c r="H6" s="556" t="n">
-        <v>224.32339070336</v>
+      <c r="B6" s="580" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="567" t="n">
+        <v>171.4952368268301</v>
+      </c>
+      <c r="D6" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E6" s="567" t="n">
+        <v>171.4952368268301</v>
+      </c>
+      <c r="F6" s="567" t="n">
+        <v>622.4614441731698</v>
+      </c>
+      <c r="G6" s="567" t="n">
+        <v>824.8037622999997</v>
+      </c>
+      <c r="H6" s="567" t="n">
+        <v>202.3423181268299</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="408" t="inlineStr">
-        <is>
-          <t>S&amp;M (human)</t>
-        </is>
-      </c>
-      <c r="C7" s="556" t="n">
-        <v>425</v>
-      </c>
-      <c r="D7" s="556" t="n">
-        <v>437.75515</v>
-      </c>
-      <c r="E7" s="556" t="n">
-        <v>455.265356</v>
-      </c>
-      <c r="F7" s="556" t="n">
-        <v>473.47597024</v>
-      </c>
-      <c r="G7" s="556" t="n">
-        <v>487.6802493472001</v>
-      </c>
-      <c r="H7" s="556" t="n">
-        <v>502.3106568276161</v>
+      <c r="B7" s="580" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C7" s="567" t="n">
+        <v>229.3706423055654</v>
+      </c>
+      <c r="D7" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E7" s="567" t="n">
+        <v>229.3706423055654</v>
+      </c>
+      <c r="F7" s="567" t="n">
+        <v>393.0908018676043</v>
+      </c>
+      <c r="G7" s="567" t="n">
+        <v>754.9762005708997</v>
+      </c>
+      <c r="H7" s="567" t="n">
+        <v>361.8853987032953</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="408" t="inlineStr">
-        <is>
-          <t>AI agent cost</t>
-        </is>
-      </c>
-      <c r="C8" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="556" t="n">
-        <v>0</v>
+      <c r="B8" s="580" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C8" s="567" t="n">
+        <v>296.6736983899872</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>296.6736983899872</v>
+      </c>
+      <c r="F8" s="567" t="n">
+        <v>96.41710347761716</v>
+      </c>
+      <c r="G8" s="567" t="n">
+        <v>665.9609770683334</v>
+      </c>
+      <c r="H8" s="567" t="n">
+        <v>569.5438735907162</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="408" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="C9" s="556" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="D9" s="556" t="n">
-        <v>201.983</v>
-      </c>
-      <c r="E9" s="556" t="n">
-        <v>210.06232</v>
-      </c>
-      <c r="F9" s="556" t="n">
-        <v>218.4648128</v>
-      </c>
-      <c r="G9" s="556" t="n">
-        <v>225.018757184</v>
-      </c>
-      <c r="H9" s="556" t="n">
-        <v>231.7693198995201</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="408" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="C10" s="556" t="n">
-        <v>295.3</v>
-      </c>
-      <c r="D10" s="556" t="n">
-        <v>225.13122</v>
-      </c>
-      <c r="E10" s="556" t="n">
-        <v>234.1364688</v>
-      </c>
-      <c r="F10" s="556" t="n">
-        <v>243.501927552</v>
-      </c>
-      <c r="G10" s="556" t="n">
-        <v>250.8069853785601</v>
-      </c>
-      <c r="H10" s="556" t="n">
-        <v>258.3311949399169</v>
+      <c r="B9" s="580" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C9" s="567" t="n">
+        <v>374.8388640800935</v>
+      </c>
+      <c r="D9" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>96.41710347761716</v>
+      </c>
+      <c r="F9" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="567" t="n">
+        <v>557.1124750633038</v>
+      </c>
+      <c r="H9" s="567" t="n">
+        <v>557.1124750633038</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="408" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C11" s="556" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TLA initial / TLB initial / Notes initial</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>457.75</v>
+      </c>
+      <c r="D11" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="E11" t="n">
         <v>183.1</v>
       </c>
-      <c r="D11" s="559" t="n">
-        <v>190.3656300000002</v>
-      </c>
-      <c r="E11" s="559" t="n">
-        <v>197.9802552000001</v>
-      </c>
-      <c r="F11" s="559" t="n">
-        <v>205.8994654080003</v>
-      </c>
-      <c r="G11" s="559" t="n">
-        <v>212.0764493702403</v>
-      </c>
-      <c r="H11" s="559" t="n">
-        <v>218.4387428513474</v>
-      </c>
     </row>
     <row r="12">
-      <c r="B12" s="408" t="inlineStr">
-        <is>
-          <t>EBITDA margin</t>
-        </is>
-      </c>
-      <c r="C12" s="411" t="n">
-        <v>0.150786461335749</v>
-      </c>
-      <c r="D12" s="413" t="n">
-        <v>0.1522037387795439</v>
-      </c>
-      <c r="E12" s="413" t="n">
-        <v>0.1522037387795438</v>
-      </c>
-      <c r="F12" s="413" t="n">
-        <v>0.1522037387795439</v>
-      </c>
-      <c r="G12" s="413" t="n">
-        <v>0.152203738779544</v>
-      </c>
-      <c r="H12" s="413" t="n">
-        <v>0.1522037387795439</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="408" t="inlineStr">
-        <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="C13" s="556" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="D13" s="556" t="n">
-        <v>88.271</v>
-      </c>
-      <c r="E13" s="556" t="n">
-        <v>91.80184</v>
-      </c>
-      <c r="F13" s="556" t="n">
-        <v>95.47391360000002</v>
-      </c>
-      <c r="G13" s="556" t="n">
-        <v>98.33813100800002</v>
-      </c>
-      <c r="H13" s="556" t="n">
-        <v>101.28827493824</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="408" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="C14" s="556" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="D14" s="556" t="n">
-        <v>102.0946300000002</v>
-      </c>
-      <c r="E14" s="556" t="n">
-        <v>106.1784152000001</v>
-      </c>
-      <c r="F14" s="556" t="n">
-        <v>110.4255518080002</v>
-      </c>
-      <c r="G14" s="556" t="n">
-        <v>113.7383183622403</v>
-      </c>
-      <c r="H14" s="556" t="n">
-        <v>117.1504679131074</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="408" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="D15" s="556" t="n">
-        <v>68.66250000000001</v>
-      </c>
-      <c r="E15" s="556" t="n">
-        <v>61.9920582975</v>
-      </c>
-      <c r="F15" s="556" t="n">
-        <v>54.51505963102687</v>
-      </c>
-      <c r="G15" s="556" t="n">
-        <v>46.1490476687412</v>
-      </c>
-      <c r="H15" s="556" t="n">
-        <v>36.91995724792738</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="408" t="inlineStr">
-        <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D16" s="556" t="n">
-        <v>26.41138270000011</v>
-      </c>
-      <c r="E16" s="556" t="n">
-        <v>34.90722195297506</v>
-      </c>
-      <c r="F16" s="556" t="n">
-        <v>44.16928881980895</v>
-      </c>
-      <c r="G16" s="556" t="n">
-        <v>53.39552384786428</v>
-      </c>
-      <c r="H16" s="556" t="n">
-        <v>63.38210342549219</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="408" t="inlineStr">
-        <is>
-          <t>FCF (after interest)</t>
-        </is>
-      </c>
-      <c r="D17" s="559" t="n">
-        <v>88.93922270000012</v>
-      </c>
-      <c r="E17" s="559" t="n">
-        <v>99.69331555297505</v>
-      </c>
-      <c r="F17" s="559" t="n">
-        <v>111.546826163809</v>
-      </c>
-      <c r="G17" s="559" t="n">
-        <v>123.0545389441843</v>
-      </c>
-      <c r="H17" s="559" t="n">
-        <v>135.1308889747018</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="408" t="inlineStr">
-        <is>
-          <t>Debt paydown</t>
-        </is>
-      </c>
-      <c r="D18" s="556" t="n">
-        <v>88.93922270000012</v>
-      </c>
-      <c r="E18" s="556" t="n">
-        <v>99.69331555297505</v>
-      </c>
-      <c r="F18" s="556" t="n">
-        <v>111.546826163809</v>
-      </c>
-      <c r="G18" s="556" t="n">
-        <v>123.0545389441843</v>
-      </c>
-      <c r="H18" s="556" t="n">
-        <v>135.1308889747018</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="408" t="inlineStr">
-        <is>
-          <t>Debt end</t>
-        </is>
-      </c>
-      <c r="C19" s="556" t="n">
-        <v>1329.9</v>
-      </c>
-      <c r="D19" s="556" t="n">
-        <v>826.5607773</v>
-      </c>
-      <c r="E19" s="556" t="n">
-        <v>726.867461747025</v>
-      </c>
-      <c r="F19" s="556" t="n">
-        <v>615.320635583216</v>
-      </c>
-      <c r="G19" s="556" t="n">
-        <v>492.2660966390317</v>
-      </c>
-      <c r="H19" s="556" t="n">
-        <v>357.1352076643299</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TLA rate / TLB rate</t>
+        </is>
+      </c>
+      <c r="C12" s="581" t="n">
+        <v>0.08299999999999999</v>
+      </c>
+      <c r="D12" s="581" t="n">
+        <v>0.093</v>
       </c>
     </row>
   </sheetData>
@@ -12211,10 +12405,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H19"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="22" customWidth="1" style="244" min="2" max="2"/>
+    <col width="26" customWidth="1" style="244" min="2" max="2"/>
     <col width="12" customWidth="1" style="244" min="3" max="3"/>
     <col width="12" customWidth="1" style="244" min="4" max="4"/>
     <col width="12" customWidth="1" style="244" min="5" max="5"/>
@@ -12225,14 +12419,25 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="406" t="inlineStr">
-        <is>
-          <t>AI-SDR case — S&amp;M cut 15% Y1 + $15m AI; S&amp;M +2%/yr thereafter</t>
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>Base case — no AI transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Driver cells: Assumptions_Drivers!C5:C20</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="412" t="inlineStr"/>
+      <c r="B4" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
       <c r="C4" s="412" t="inlineStr">
         <is>
           <t>FY2024A</t>
@@ -12265,366 +12470,482 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="408" t="inlineStr">
+      <c r="B5" s="575" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="556" t="n">
+      <c r="C5" s="582" t="n">
         <v>1214.3</v>
       </c>
-      <c r="D5" s="556" t="n">
-        <v>1250.729</v>
-      </c>
-      <c r="E5" s="556" t="n">
-        <v>1300.75816</v>
-      </c>
-      <c r="F5" s="556" t="n">
-        <v>1352.7884864</v>
-      </c>
-      <c r="G5" s="556" t="n">
-        <v>1393.372140992</v>
-      </c>
-      <c r="H5" s="556" t="n">
-        <v>1435.173305221761</v>
+      <c r="D5" s="567" t="n">
+        <v>1335.73</v>
+      </c>
+      <c r="E5" s="567" t="n">
+        <v>1469.303</v>
+      </c>
+      <c r="F5" s="567" t="n">
+        <v>1616.2333</v>
+      </c>
+      <c r="G5" s="567" t="n">
+        <v>1777.85663</v>
+      </c>
+      <c r="H5" s="567" t="n">
+        <v>1955.642293000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="408" t="inlineStr">
+      <c r="B6" s="575" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C6" s="556" t="n">
-        <v>189.8</v>
-      </c>
-      <c r="D6" s="556" t="n">
-        <v>195.4939999999999</v>
-      </c>
-      <c r="E6" s="556" t="n">
-        <v>203.31376</v>
-      </c>
-      <c r="F6" s="556" t="n">
-        <v>211.4463104</v>
-      </c>
-      <c r="G6" s="556" t="n">
-        <v>217.789699712</v>
-      </c>
-      <c r="H6" s="556" t="n">
-        <v>224.32339070336</v>
+      <c r="C6" s="582" t="n">
+        <v>242.8599999999999</v>
+      </c>
+      <c r="D6" s="567" t="n">
+        <v>267.146</v>
+      </c>
+      <c r="E6" s="567" t="n">
+        <v>293.8606</v>
+      </c>
+      <c r="F6" s="567" t="n">
+        <v>323.24666</v>
+      </c>
+      <c r="G6" s="567" t="n">
+        <v>355.571326</v>
+      </c>
+      <c r="H6" s="567" t="n">
+        <v>391.1284586</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="408" t="inlineStr">
-        <is>
-          <t>S&amp;M (human)</t>
-        </is>
-      </c>
-      <c r="C7" s="556" t="n">
+      <c r="B7" s="575" t="inlineStr">
+        <is>
+          <t>Sales payroll (human)</t>
+        </is>
+      </c>
+      <c r="C7" s="582" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D7" s="567" t="n">
+        <v>350.68</v>
+      </c>
+      <c r="E7" s="567" t="n">
+        <v>385.748</v>
+      </c>
+      <c r="F7" s="567" t="n">
+        <v>424.3228000000001</v>
+      </c>
+      <c r="G7" s="567" t="n">
+        <v>466.7550800000001</v>
+      </c>
+      <c r="H7" s="567" t="n">
+        <v>513.4305880000002</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="575" t="inlineStr">
+        <is>
+          <t>Variable commissions</t>
+        </is>
+      </c>
+      <c r="C8" s="582" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>116.82</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>128.502</v>
+      </c>
+      <c r="F8" s="567" t="n">
+        <v>141.3522</v>
+      </c>
+      <c r="G8" s="567" t="n">
+        <v>155.48742</v>
+      </c>
+      <c r="H8" s="567" t="n">
+        <v>171.0361620000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M human total</t>
+        </is>
+      </c>
+      <c r="C9" s="582" t="n">
         <v>425</v>
       </c>
-      <c r="D7" s="556" t="n">
-        <v>361.25</v>
-      </c>
-      <c r="E7" s="556" t="n">
-        <v>368.475</v>
-      </c>
-      <c r="F7" s="556" t="n">
-        <v>375.8445</v>
-      </c>
-      <c r="G7" s="556" t="n">
-        <v>383.36139</v>
-      </c>
-      <c r="H7" s="556" t="n">
-        <v>391.0286178000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="408" t="inlineStr">
-        <is>
-          <t>AI agent cost</t>
-        </is>
-      </c>
-      <c r="C8" s="556" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="556" t="n">
-        <v>15</v>
-      </c>
-      <c r="E8" s="556" t="n">
-        <v>15</v>
-      </c>
-      <c r="F8" s="556" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" s="556" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" s="556" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="408" t="inlineStr">
+      <c r="D9" s="567" t="n">
+        <v>467.5</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>514.25</v>
+      </c>
+      <c r="F9" s="567" t="n">
+        <v>565.6750000000002</v>
+      </c>
+      <c r="G9" s="567" t="n">
+        <v>622.2425000000002</v>
+      </c>
+      <c r="H9" s="567" t="n">
+        <v>684.4667500000003</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="575" t="inlineStr">
+        <is>
+          <t>AI infrastructure</t>
+        </is>
+      </c>
+      <c r="C10" s="582" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="567" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="567" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="575" t="inlineStr">
         <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="C9" s="556" t="n">
+      <c r="C11" s="582" t="n">
         <v>196.1</v>
       </c>
-      <c r="D9" s="556" t="n">
-        <v>201.983</v>
-      </c>
-      <c r="E9" s="556" t="n">
-        <v>210.06232</v>
-      </c>
-      <c r="F9" s="556" t="n">
-        <v>218.4648128</v>
-      </c>
-      <c r="G9" s="556" t="n">
-        <v>225.018757184</v>
-      </c>
-      <c r="H9" s="556" t="n">
-        <v>231.7693198995201</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="408" t="inlineStr">
-        <is>
-          <t>G&amp;A</t>
-        </is>
-      </c>
-      <c r="C10" s="556" t="n">
-        <v>295.3</v>
-      </c>
-      <c r="D10" s="556" t="n">
-        <v>225.13122</v>
-      </c>
-      <c r="E10" s="556" t="n">
-        <v>234.1364688</v>
-      </c>
-      <c r="F10" s="556" t="n">
-        <v>243.501927552</v>
-      </c>
-      <c r="G10" s="556" t="n">
-        <v>250.8069853785601</v>
-      </c>
-      <c r="H10" s="556" t="n">
-        <v>258.3311949399169</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="408" t="inlineStr">
+      <c r="D11" s="567" t="n">
+        <v>215.71</v>
+      </c>
+      <c r="E11" s="567" t="n">
+        <v>237.281</v>
+      </c>
+      <c r="F11" s="567" t="n">
+        <v>261.0091</v>
+      </c>
+      <c r="G11" s="567" t="n">
+        <v>287.11001</v>
+      </c>
+      <c r="H11" s="567" t="n">
+        <v>315.8210110000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="575" t="inlineStr">
+        <is>
+          <t>G&amp;A (admin)</t>
+        </is>
+      </c>
+      <c r="C12" s="582" t="n">
+        <v>218.574</v>
+      </c>
+      <c r="D12" s="567" t="n">
+        <v>240.4314</v>
+      </c>
+      <c r="E12" s="567" t="n">
+        <v>264.47454</v>
+      </c>
+      <c r="F12" s="567" t="n">
+        <v>290.921994</v>
+      </c>
+      <c r="G12" s="567" t="n">
+        <v>320.0141934000001</v>
+      </c>
+      <c r="H12" s="567" t="n">
+        <v>352.0156127400001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="575" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="556" t="n">
+      <c r="C13" s="582" t="n">
         <v>183.1</v>
       </c>
-      <c r="D11" s="559" t="n">
-        <v>251.8707800000001</v>
-      </c>
-      <c r="E11" s="559" t="n">
-        <v>269.7706112000001</v>
-      </c>
-      <c r="F11" s="559" t="n">
-        <v>288.5309356480003</v>
-      </c>
-      <c r="G11" s="559" t="n">
-        <v>301.3953087174403</v>
-      </c>
-      <c r="H11" s="559" t="n">
-        <v>314.7207818789635</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="408" t="inlineStr">
+      <c r="D13" s="567" t="n">
+        <v>144.9426000000001</v>
+      </c>
+      <c r="E13" s="567" t="n">
+        <v>159.4368600000001</v>
+      </c>
+      <c r="F13" s="567" t="n">
+        <v>175.380546</v>
+      </c>
+      <c r="G13" s="567" t="n">
+        <v>192.9186006000002</v>
+      </c>
+      <c r="H13" s="567" t="n">
+        <v>212.2104606600003</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="575" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C12" s="411" t="n">
+      <c r="C14" s="583" t="n">
         <v>0.150786461335749</v>
       </c>
-      <c r="D12" s="413" t="n">
-        <v>0.201379179662421</v>
-      </c>
-      <c r="E12" s="413" t="n">
-        <v>0.2073949020623481</v>
-      </c>
-      <c r="F12" s="413" t="n">
-        <v>0.2132860669267152</v>
-      </c>
-      <c r="G12" s="413" t="n">
-        <v>0.2163063978750604</v>
-      </c>
-      <c r="H12" s="413" t="n">
-        <v>0.2192911342023139</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="408" t="inlineStr">
+      <c r="D14" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+      <c r="E14" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+      <c r="F14" s="565" t="n">
+        <v>0.1085118998600016</v>
+      </c>
+      <c r="G14" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+      <c r="H14" s="565" t="n">
+        <v>0.1085118998600017</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="575" t="inlineStr">
         <is>
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C13" s="556" t="n">
+      <c r="C15" s="582" t="n">
         <v>85.7</v>
       </c>
-      <c r="D13" s="556" t="n">
-        <v>88.271</v>
-      </c>
-      <c r="E13" s="556" t="n">
-        <v>91.80184</v>
-      </c>
-      <c r="F13" s="556" t="n">
-        <v>95.47391360000002</v>
-      </c>
-      <c r="G13" s="556" t="n">
-        <v>98.33813100800002</v>
-      </c>
-      <c r="H13" s="556" t="n">
-        <v>101.28827493824</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="408" t="inlineStr">
+      <c r="D15" s="567" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="E15" s="567" t="n">
+        <v>103.697</v>
+      </c>
+      <c r="F15" s="567" t="n">
+        <v>114.0667</v>
+      </c>
+      <c r="G15" s="567" t="n">
+        <v>125.47337</v>
+      </c>
+      <c r="H15" s="567" t="n">
+        <v>138.020707</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="575" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="556" t="n">
+      <c r="C16" s="582" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="D14" s="556" t="n">
-        <v>163.5997800000001</v>
-      </c>
-      <c r="E14" s="556" t="n">
-        <v>177.9687712000001</v>
-      </c>
-      <c r="F14" s="556" t="n">
-        <v>193.0570220480002</v>
-      </c>
-      <c r="G14" s="556" t="n">
-        <v>203.0571777094403</v>
-      </c>
-      <c r="H14" s="556" t="n">
-        <v>213.4325069407234</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="408" t="inlineStr">
+      <c r="D16" s="567" t="n">
+        <v>50.67260000000009</v>
+      </c>
+      <c r="E16" s="567" t="n">
+        <v>55.73986000000014</v>
+      </c>
+      <c r="F16" s="567" t="n">
+        <v>61.31384600000001</v>
+      </c>
+      <c r="G16" s="567" t="n">
+        <v>67.44523060000019</v>
+      </c>
+      <c r="H16" s="567" t="n">
+        <v>74.18975366000021</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="575" t="inlineStr">
         <is>
           <t>Interest</t>
         </is>
       </c>
-      <c r="D15" s="556" t="n">
-        <v>68.66250000000001</v>
-      </c>
-      <c r="E15" s="556" t="n">
-        <v>58.34787815999999</v>
-      </c>
-      <c r="F15" s="556" t="n">
-        <v>46.40138322737999</v>
-      </c>
-      <c r="G15" s="556" t="n">
-        <v>32.65872132645823</v>
-      </c>
-      <c r="H15" s="556" t="n">
-        <v>17.33818665354254</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="408" t="inlineStr">
+      <c r="D17" s="567" t="n">
+        <v>77.8175</v>
+      </c>
+      <c r="E17" s="567" t="n">
+        <v>74.66500229999998</v>
+      </c>
+      <c r="F17" s="567" t="n">
+        <v>70.28971227089997</v>
+      </c>
+      <c r="G17" s="567" t="n">
+        <v>64.49402464738468</v>
+      </c>
+      <c r="H17" s="567" t="n">
+        <v>57.10576109667166</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="575" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="D16" s="556" t="n">
-        <v>75.0004512000001</v>
-      </c>
-      <c r="E16" s="556" t="n">
-        <v>94.50050550160006</v>
-      </c>
-      <c r="F16" s="556" t="n">
-        <v>115.85795466829</v>
-      </c>
-      <c r="G16" s="556" t="n">
-        <v>134.6147805425558</v>
-      </c>
-      <c r="H16" s="556" t="n">
-        <v>154.9145130268729</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="408" t="inlineStr">
-        <is>
-          <t>FCF (after interest)</t>
-        </is>
-      </c>
-      <c r="D17" s="559" t="n">
-        <v>137.5282912000001</v>
-      </c>
-      <c r="E17" s="559" t="n">
-        <v>159.2865991016001</v>
-      </c>
-      <c r="F17" s="559" t="n">
-        <v>183.23549201229</v>
-      </c>
-      <c r="G17" s="559" t="n">
-        <v>204.2737956388759</v>
-      </c>
-      <c r="H17" s="559" t="n">
-        <v>226.6632985760825</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="408" t="inlineStr">
-        <is>
-          <t>Debt paydown</t>
-        </is>
-      </c>
-      <c r="D18" s="556" t="n">
-        <v>137.5282912000001</v>
-      </c>
-      <c r="E18" s="556" t="n">
-        <v>159.2865991016001</v>
-      </c>
-      <c r="F18" s="556" t="n">
-        <v>183.23549201229</v>
-      </c>
-      <c r="G18" s="556" t="n">
-        <v>204.2737956388759</v>
-      </c>
-      <c r="H18" s="556" t="n">
-        <v>226.6632985760825</v>
+      <c r="D18" s="567" t="n">
+        <v>-27.14489999999991</v>
+      </c>
+      <c r="E18" s="567" t="n">
+        <v>-18.92514229999985</v>
+      </c>
+      <c r="F18" s="567" t="n">
+        <v>-8.975866270899957</v>
+      </c>
+      <c r="G18" s="567" t="n">
+        <v>2.331452702566253</v>
+      </c>
+      <c r="H18" s="567" t="n">
+        <v>13.49635412502955</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="408" t="inlineStr">
+      <c r="B19" s="575" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="D19" s="567" t="n">
+        <v>26.7146</v>
+      </c>
+      <c r="E19" s="567" t="n">
+        <v>29.38606</v>
+      </c>
+      <c r="F19" s="567" t="n">
+        <v>32.32466600000001</v>
+      </c>
+      <c r="G19" s="567" t="n">
+        <v>35.55713260000001</v>
+      </c>
+      <c r="H19" s="567" t="n">
+        <v>39.11284586000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="575" t="inlineStr">
+        <is>
+          <t>ΔNWC</t>
+        </is>
+      </c>
+      <c r="D20" s="567" t="n">
+        <v>2.428600000000001</v>
+      </c>
+      <c r="E20" s="567" t="n">
+        <v>2.671460000000002</v>
+      </c>
+      <c r="F20" s="567" t="n">
+        <v>2.938606000000004</v>
+      </c>
+      <c r="G20" s="567" t="n">
+        <v>3.232466600000003</v>
+      </c>
+      <c r="H20" s="567" t="n">
+        <v>3.555713260000002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="575" t="inlineStr">
+        <is>
+          <t>FCF after interest</t>
+        </is>
+      </c>
+      <c r="D21" s="567" t="n">
+        <v>37.98190000000008</v>
+      </c>
+      <c r="E21" s="567" t="n">
+        <v>52.71433770000015</v>
+      </c>
+      <c r="F21" s="567" t="n">
+        <v>69.82756172910005</v>
+      </c>
+      <c r="G21" s="567" t="n">
+        <v>89.01522350256627</v>
+      </c>
+      <c r="H21" s="567" t="n">
+        <v>108.8485020050296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="575" t="inlineStr">
+        <is>
+          <t>Mandatory amort</t>
+        </is>
+      </c>
+      <c r="D22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="F22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="G22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="H22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="575" t="inlineStr">
+        <is>
+          <t>Total debt paydown</t>
+        </is>
+      </c>
+      <c r="D23" s="567" t="n">
+        <v>37.98190000000008</v>
+      </c>
+      <c r="E23" s="567" t="n">
+        <v>52.71433770000015</v>
+      </c>
+      <c r="F23" s="567" t="n">
+        <v>69.82756172910005</v>
+      </c>
+      <c r="G23" s="567" t="n">
+        <v>89.01522350256627</v>
+      </c>
+      <c r="H23" s="567" t="n">
+        <v>108.8485020050296</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="575" t="inlineStr">
         <is>
           <t>Debt end</t>
         </is>
       </c>
-      <c r="C19" s="556" t="n">
+      <c r="C24" s="582" t="n">
         <v>1329.9</v>
       </c>
-      <c r="D19" s="556" t="n">
-        <v>777.9717088</v>
-      </c>
-      <c r="E19" s="556" t="n">
-        <v>618.6851096983999</v>
-      </c>
-      <c r="F19" s="556" t="n">
-        <v>435.4496176861098</v>
-      </c>
-      <c r="G19" s="556" t="n">
-        <v>231.1758220472339</v>
-      </c>
-      <c r="H19" s="556" t="n">
-        <v>4.512523471151439</v>
+      <c r="D24" s="567" t="n">
+        <v>877.5180999999999</v>
+      </c>
+      <c r="E24" s="567" t="n">
+        <v>824.8037622999997</v>
+      </c>
+      <c r="F24" s="567" t="n">
+        <v>754.9762005708997</v>
+      </c>
+      <c r="G24" s="567" t="n">
+        <v>665.9609770683334</v>
+      </c>
+      <c r="H24" s="567" t="n">
+        <v>557.1124750633038</v>
       </c>
     </row>
   </sheetData>
@@ -12638,6 +12959,560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="26" customWidth="1" style="244" min="2" max="2"/>
+    <col width="12" customWidth="1" style="244" min="3" max="3"/>
+    <col width="12" customWidth="1" style="244" min="4" max="4"/>
+    <col width="12" customWidth="1" style="244" min="5" max="5"/>
+    <col width="12" customWidth="1" style="244" min="6" max="6"/>
+    <col width="12" customWidth="1" style="244" min="7" max="7"/>
+    <col width="12" customWidth="1" style="244" min="8" max="8"/>
+    <col width="12" customWidth="1" style="244" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="563" t="inlineStr">
+        <is>
+          <t>AI-SDR case — drivers from Assumptions_Drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Driver cells: Assumptions_Drivers!C5:C20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="412" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C4" s="412" t="inlineStr">
+        <is>
+          <t>FY2024A</t>
+        </is>
+      </c>
+      <c r="D4" s="412" t="inlineStr">
+        <is>
+          <t>Y1 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="412" t="inlineStr">
+        <is>
+          <t>Y2 2026</t>
+        </is>
+      </c>
+      <c r="F4" s="412" t="inlineStr">
+        <is>
+          <t>Y3 2027</t>
+        </is>
+      </c>
+      <c r="G4" s="412" t="inlineStr">
+        <is>
+          <t>Y4 2028</t>
+        </is>
+      </c>
+      <c r="H4" s="412" t="inlineStr">
+        <is>
+          <t>Y5 2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="575" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="582" t="n">
+        <v>1214.3</v>
+      </c>
+      <c r="D5" s="567" t="n">
+        <v>1335.73</v>
+      </c>
+      <c r="E5" s="567" t="n">
+        <v>1469.303</v>
+      </c>
+      <c r="F5" s="567" t="n">
+        <v>1616.2333</v>
+      </c>
+      <c r="G5" s="567" t="n">
+        <v>1777.85663</v>
+      </c>
+      <c r="H5" s="567" t="n">
+        <v>1955.642293000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="575" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C6" s="582" t="n">
+        <v>242.8599999999999</v>
+      </c>
+      <c r="D6" s="567" t="n">
+        <v>267.146</v>
+      </c>
+      <c r="E6" s="567" t="n">
+        <v>293.8606</v>
+      </c>
+      <c r="F6" s="567" t="n">
+        <v>323.24666</v>
+      </c>
+      <c r="G6" s="567" t="n">
+        <v>355.571326</v>
+      </c>
+      <c r="H6" s="567" t="n">
+        <v>391.1284586</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="575" t="inlineStr">
+        <is>
+          <t>Sales payroll (human)</t>
+        </is>
+      </c>
+      <c r="C7" s="582" t="n">
+        <v>318.8</v>
+      </c>
+      <c r="D7" s="567" t="n">
+        <v>270.98</v>
+      </c>
+      <c r="E7" s="567" t="n">
+        <v>276.3996</v>
+      </c>
+      <c r="F7" s="567" t="n">
+        <v>281.927592</v>
+      </c>
+      <c r="G7" s="567" t="n">
+        <v>287.56614384</v>
+      </c>
+      <c r="H7" s="567" t="n">
+        <v>293.3174667168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="575" t="inlineStr">
+        <is>
+          <t>Variable commissions</t>
+        </is>
+      </c>
+      <c r="C8" s="582" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="D8" s="567" t="n">
+        <v>84.96000000000001</v>
+      </c>
+      <c r="E8" s="567" t="n">
+        <v>86.65920000000001</v>
+      </c>
+      <c r="F8" s="567" t="n">
+        <v>88.39238400000002</v>
+      </c>
+      <c r="G8" s="567" t="n">
+        <v>90.16023168000002</v>
+      </c>
+      <c r="H8" s="567" t="n">
+        <v>91.96343631360003</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="575" t="inlineStr">
+        <is>
+          <t>S&amp;M human total</t>
+        </is>
+      </c>
+      <c r="C9" s="582" t="n">
+        <v>425</v>
+      </c>
+      <c r="D9" s="567" t="n">
+        <v>355.9400000000001</v>
+      </c>
+      <c r="E9" s="567" t="n">
+        <v>363.0588</v>
+      </c>
+      <c r="F9" s="567" t="n">
+        <v>370.319976</v>
+      </c>
+      <c r="G9" s="567" t="n">
+        <v>377.72637552</v>
+      </c>
+      <c r="H9" s="567" t="n">
+        <v>385.2809030304001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="575" t="inlineStr">
+        <is>
+          <t>AI infrastructure</t>
+        </is>
+      </c>
+      <c r="C10" s="582" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="567" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" s="567" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="567" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" s="567" t="n">
+        <v>15</v>
+      </c>
+      <c r="H10" s="567" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="575" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C11" s="582" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="D11" s="567" t="n">
+        <v>215.71</v>
+      </c>
+      <c r="E11" s="567" t="n">
+        <v>237.281</v>
+      </c>
+      <c r="F11" s="567" t="n">
+        <v>261.0091</v>
+      </c>
+      <c r="G11" s="567" t="n">
+        <v>287.11001</v>
+      </c>
+      <c r="H11" s="567" t="n">
+        <v>315.8210110000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="575" t="inlineStr">
+        <is>
+          <t>G&amp;A (admin)</t>
+        </is>
+      </c>
+      <c r="C12" s="582" t="n">
+        <v>218.574</v>
+      </c>
+      <c r="D12" s="567" t="n">
+        <v>240.4314</v>
+      </c>
+      <c r="E12" s="567" t="n">
+        <v>264.47454</v>
+      </c>
+      <c r="F12" s="567" t="n">
+        <v>290.921994</v>
+      </c>
+      <c r="G12" s="567" t="n">
+        <v>320.0141934000001</v>
+      </c>
+      <c r="H12" s="567" t="n">
+        <v>352.0156127400001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="575" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C13" s="582" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="D13" s="567" t="n">
+        <v>241.5026</v>
+      </c>
+      <c r="E13" s="567" t="n">
+        <v>295.6280600000002</v>
+      </c>
+      <c r="F13" s="567" t="n">
+        <v>355.7355700000003</v>
+      </c>
+      <c r="G13" s="567" t="n">
+        <v>422.4347250800001</v>
+      </c>
+      <c r="H13" s="567" t="n">
+        <v>496.3963076296004</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="575" t="inlineStr">
+        <is>
+          <t>EBITDA margin</t>
+        </is>
+      </c>
+      <c r="C14" s="583" t="n">
+        <v>0.150786461335749</v>
+      </c>
+      <c r="D14" s="565" t="n">
+        <v>0.1808019584796329</v>
+      </c>
+      <c r="E14" s="565" t="n">
+        <v>0.2012029241075531</v>
+      </c>
+      <c r="F14" s="565" t="n">
+        <v>0.2201016214676434</v>
+      </c>
+      <c r="G14" s="565" t="n">
+        <v>0.237608993859083</v>
+      </c>
+      <c r="H14" s="565" t="n">
+        <v>0.253827762575188</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="575" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="C15" s="582" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="D15" s="567" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="E15" s="567" t="n">
+        <v>103.697</v>
+      </c>
+      <c r="F15" s="567" t="n">
+        <v>114.0667</v>
+      </c>
+      <c r="G15" s="567" t="n">
+        <v>125.47337</v>
+      </c>
+      <c r="H15" s="567" t="n">
+        <v>138.020707</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="575" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="C16" s="582" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="D16" s="567" t="n">
+        <v>147.2326</v>
+      </c>
+      <c r="E16" s="567" t="n">
+        <v>191.9310600000002</v>
+      </c>
+      <c r="F16" s="567" t="n">
+        <v>241.6688700000003</v>
+      </c>
+      <c r="G16" s="567" t="n">
+        <v>296.9613550800001</v>
+      </c>
+      <c r="H16" s="567" t="n">
+        <v>358.3756006296003</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="575" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D17" s="567" t="n">
+        <v>77.8175</v>
+      </c>
+      <c r="E17" s="567" t="n">
+        <v>67.729404523</v>
+      </c>
+      <c r="F17" s="567" t="n">
+        <v>53.49529986637309</v>
+      </c>
+      <c r="G17" s="567" t="n">
+        <v>33.8109445736872</v>
+      </c>
+      <c r="H17" s="567" t="n">
+        <v>7.520534071254138</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="575" t="inlineStr">
+        <is>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D18" s="567" t="n">
+        <v>54.83792900000005</v>
+      </c>
+      <c r="E18" s="567" t="n">
+        <v>98.11930782683014</v>
+      </c>
+      <c r="F18" s="567" t="n">
+        <v>148.6571204055655</v>
+      </c>
+      <c r="G18" s="567" t="n">
+        <v>207.8888242999872</v>
+      </c>
+      <c r="H18" s="567" t="n">
+        <v>277.1755025810935</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="575" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="D19" s="567" t="n">
+        <v>25.37887</v>
+      </c>
+      <c r="E19" s="567" t="n">
+        <v>27.916757</v>
+      </c>
+      <c r="F19" s="567" t="n">
+        <v>30.70843270000001</v>
+      </c>
+      <c r="G19" s="567" t="n">
+        <v>33.77927597000001</v>
+      </c>
+      <c r="H19" s="567" t="n">
+        <v>37.15720356700001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="575" t="inlineStr">
+        <is>
+          <t>ΔNWC</t>
+        </is>
+      </c>
+      <c r="D20" s="567" t="n">
+        <v>2.185740000000001</v>
+      </c>
+      <c r="E20" s="567" t="n">
+        <v>2.404314000000002</v>
+      </c>
+      <c r="F20" s="567" t="n">
+        <v>2.644745400000004</v>
+      </c>
+      <c r="G20" s="567" t="n">
+        <v>2.909219940000003</v>
+      </c>
+      <c r="H20" s="567" t="n">
+        <v>3.200141934000002</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="575" t="inlineStr">
+        <is>
+          <t>FCF after interest</t>
+        </is>
+      </c>
+      <c r="D21" s="567" t="n">
+        <v>121.543319</v>
+      </c>
+      <c r="E21" s="567" t="n">
+        <v>171.4952368268301</v>
+      </c>
+      <c r="F21" s="567" t="n">
+        <v>229.3706423055654</v>
+      </c>
+      <c r="G21" s="567" t="n">
+        <v>296.6736983899872</v>
+      </c>
+      <c r="H21" s="567" t="n">
+        <v>374.8388640800935</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="575" t="inlineStr">
+        <is>
+          <t>Mandatory amort</t>
+        </is>
+      </c>
+      <c r="D22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="E22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="F22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="G22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+      <c r="H22" s="567" t="n">
+        <v>9.154999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="575" t="inlineStr">
+        <is>
+          <t>Total debt paydown</t>
+        </is>
+      </c>
+      <c r="D23" s="567" t="n">
+        <v>121.543319</v>
+      </c>
+      <c r="E23" s="567" t="n">
+        <v>171.4952368268301</v>
+      </c>
+      <c r="F23" s="567" t="n">
+        <v>229.3706423055654</v>
+      </c>
+      <c r="G23" s="567" t="n">
+        <v>296.6736983899872</v>
+      </c>
+      <c r="H23" s="567" t="n">
+        <v>96.41710347761716</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="575" t="inlineStr">
+        <is>
+          <t>Debt end</t>
+        </is>
+      </c>
+      <c r="C24" s="582" t="n">
+        <v>1329.9</v>
+      </c>
+      <c r="D24" s="567" t="n">
+        <v>793.956681</v>
+      </c>
+      <c r="E24" s="567" t="n">
+        <v>622.4614441731698</v>
+      </c>
+      <c r="F24" s="567" t="n">
+        <v>393.0908018676043</v>
+      </c>
+      <c r="G24" s="567" t="n">
+        <v>96.41710347761716</v>
+      </c>
+      <c r="H24" s="567" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -12707,7 +13582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18706,7 +19581,7 @@
     <row r="266">
       <c r="B266" s="317" t="inlineStr">
         <is>
-          <t>SUMMARY AT 13.0x EXIT — AI-SDR case vs Base</t>
+          <t>SUMMARY @ 13.0x EXIT — AI vs Base (see Strategy_Summary)</t>
         </is>
       </c>
       <c r="C266" s="15" t="n"/>
@@ -18912,10 +19787,10 @@
         <v>1</v>
       </c>
       <c r="I275" s="485" t="n">
-        <v>2.184</v>
+        <v>3.449</v>
       </c>
       <c r="J275" s="490" t="n">
-        <v>0.1691</v>
+        <v>0.2809</v>
       </c>
     </row>
     <row r="276">
@@ -18934,10 +19809,10 @@
         <v>1</v>
       </c>
       <c r="I276" t="n">
-        <v>1.327</v>
+        <v>1.177</v>
       </c>
       <c r="J276" t="n">
-        <v>0.0582</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="277">
@@ -18950,7 +19825,7 @@
       <c r="G277" s="492" t="n"/>
       <c r="H277" s="492" t="n"/>
       <c r="J277" t="n">
-        <v>0.1109</v>
+        <v>0.2479</v>
       </c>
     </row>
     <row r="278">
@@ -21279,7 +22154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22907,309 +23782,4 @@
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:E28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="1.7109375" customWidth="1" style="244" min="1" max="1"/>
-    <col width="36.5703125" bestFit="1" customWidth="1" style="244" min="2" max="2"/>
-    <col width="15.85546875" customWidth="1" style="244" min="3" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="244" thickBot="1"/>
-    <row r="2" ht="27" customHeight="1" s="244" thickBot="1">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Diluted shares for BMC</t>
-        </is>
-      </c>
-      <c r="C2" s="305" t="n"/>
-      <c r="D2" s="305" t="n"/>
-      <c r="E2" s="305" t="n"/>
-    </row>
-    <row r="3">
-      <c r="B3" s="302" t="inlineStr">
-        <is>
-          <t>$ mm except per share</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="34" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="34" t="inlineStr">
-        <is>
-          <t>Offer price</t>
-        </is>
-      </c>
-      <c r="E5" s="513" t="n">
-        <v>46.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="304" t="inlineStr">
-        <is>
-          <t>Model-derived offer value sanity check</t>
-        </is>
-      </c>
-      <c r="E6" s="554" t="n">
-        <v>46.25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="159" t="inlineStr">
-        <is>
-          <t>Basic shares outstanding (latest filing)</t>
-        </is>
-      </c>
-      <c r="E7" s="522" t="n">
-        <v>143.973</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>In-the-money exercisable options</t>
-        </is>
-      </c>
-      <c r="E8" s="521" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>Total proceeds ($mm)</t>
-        </is>
-      </c>
-      <c r="E9" s="461" t="n">
-        <v>411.7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>Total shares repurchased (mm)</t>
-        </is>
-      </c>
-      <c r="E10" s="461" t="n">
-        <v>8.901621621621622</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="34" t="inlineStr">
-        <is>
-          <t>Net dilutive options</t>
-        </is>
-      </c>
-      <c r="E11" s="461" t="n">
-        <v>1.798378378378377</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dilutive impact of shares from other securities </t>
-        </is>
-      </c>
-      <c r="E12" s="522" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="34" t="n"/>
-      <c r="E13" s="522" t="n"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="147" t="inlineStr">
-        <is>
-          <t>Net diluted shares outstanding</t>
-        </is>
-      </c>
-      <c r="D14" s="434" t="n"/>
-      <c r="E14" s="461" t="n">
-        <v>145.7713783783784</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="147" t="n"/>
-      <c r="D15" s="434" t="n"/>
-      <c r="E15" s="461" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="312" t="inlineStr">
-        <is>
-          <t>Options outstanding</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="445" t="n"/>
-      <c r="E16" s="518" t="n"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="242" t="inlineStr">
-        <is>
-          <t>Out. shares</t>
-        </is>
-      </c>
-      <c r="D17" s="242" t="inlineStr">
-        <is>
-          <t>Exercise price</t>
-        </is>
-      </c>
-      <c r="E17" s="242" t="inlineStr">
-        <is>
-          <t>In-the-$-shares</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="555" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="298" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D18" s="298" t="n">
-        <v>15</v>
-      </c>
-      <c r="E18" s="299" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="555" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="298" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D19" s="298" t="n">
-        <v>18</v>
-      </c>
-      <c r="E19" s="299" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="555" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="298" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D20" s="298" t="n">
-        <v>22</v>
-      </c>
-      <c r="E20" s="299" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="555" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="298" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D21" s="298" t="n">
-        <v>28</v>
-      </c>
-      <c r="E21" s="299" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="555" t="n">
-        <v>5</v>
-      </c>
-      <c r="C22" s="298" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D22" s="298" t="n">
-        <v>32</v>
-      </c>
-      <c r="E22" s="299" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="555" t="n">
-        <v>6</v>
-      </c>
-      <c r="C23" s="298" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D23" s="298" t="n">
-        <v>36</v>
-      </c>
-      <c r="E23" s="299" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="555" t="n">
-        <v>7</v>
-      </c>
-      <c r="C24" s="298" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D24" s="298" t="n">
-        <v>39</v>
-      </c>
-      <c r="E24" s="299" t="n">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="555" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" s="298" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="D25" s="298" t="n">
-        <v>42</v>
-      </c>
-      <c r="E25" s="299" t="n">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="555" t="n">
-        <v>9</v>
-      </c>
-      <c r="C26" s="298" t="n"/>
-      <c r="D26" s="298" t="n"/>
-      <c r="E26" s="299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="555" t="n">
-        <v>10</v>
-      </c>
-      <c r="C27" s="298" t="n"/>
-      <c r="D27" s="298" t="n"/>
-      <c r="E27" s="300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="E28" s="301" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>